--- a/docs/103_RIME對照工具【台語注音二式】.xlsx
+++ b/docs/103_RIME對照工具【台語注音二式】.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E850434A-BD9C-4E6F-AED6-50315E8898CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF67B216-5A14-4C9C-A696-6AAC6E029705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="聲調標置" sheetId="1" r:id="rId1"/>
     <sheet name="【聲】聲母對照表 (台語注音二式)" sheetId="2" r:id="rId2"/>
     <sheet name="【韻】韻母清單（台語注音二式==&gt;閩拼方案）" sheetId="8" r:id="rId3"/>
     <sheet name="【韻】韻母清單（台語注音二式==&gt;閩拼方案）【右欄】" sheetId="4" r:id="rId4"/>
@@ -63,7 +63,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -2972,6 +2972,51 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{390CC109-95F1-4DC2-9F45-F0836FB44517}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;2c156645-14aa-4eff-b865-470dec0c7766&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{8892AA9B-2C9C-4745-B151-7E7AE196CCA8}">
+  <we:reference id="wa200007447" version="1.1.6.7" store="zh-TW" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200007447" version="1.1.6.7" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_BOARDFLARE_RUNPY</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A11"/>
@@ -4938,51 +4983,49 @@
     </row>
     <row r="4" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A4" s="19">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>29</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>26</v>
+        <v>387</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="J4" s="19"/>
       <c r="K4" s="23">
         <f>LEN(E4)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L4" s="24"/>
       <c r="M4" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uainnh</v>
+        <v>a</v>
       </c>
       <c r="N4" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>nuaih</v>
+        <v>a</v>
       </c>
       <c r="P4" s="3" t="str">
         <f>_xlfn.CONCAT(M4, "(\d)")</f>
-        <v>uainnh(\d)</v>
+        <v>a(\d)</v>
       </c>
       <c r="Q4" s="5" t="str" cm="1">
         <f t="array" ref="Q4:Q85">_xlfn._xlws.PY(0,0,F4:F85)</f>
@@ -4990,16 +5033,16 @@
       </c>
       <c r="R4" s="5">
         <f>IFERROR( IF(Q4="", "", SEARCH(Q4, $N4)), "")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4" s="3" t="str">
         <f>IFERROR( _xlfn.CONCAT(LEFT(N4,R4-1), "@", MID(N4,R4,1), "${1}", RIGHT(N4, LEN(N4)-R4)), "" )</f>
-        <v>nu@a${1}ih</v>
+        <v>@a${1}</v>
       </c>
       <c r="T4" s="25"/>
       <c r="U4" s="26" t="str">
         <f>IF(AND(N4&lt;&gt;"", M4&lt;&gt;""), "    - xform/@" &amp; P4 &amp;  "/"  &amp; S4 &amp;  "/", "")</f>
-        <v xml:space="preserve">    - xform/@uainnh(\d)/nu@a${1}ih/</v>
+        <v xml:space="preserve">    - xform/@a(\d)/@a${1}/</v>
       </c>
       <c r="W4" s="7" t="s">
         <v>29</v>
@@ -5090,67 +5133,65 @@
     </row>
     <row r="5" spans="1:47" ht="30.75" customHeight="1" thickBot="1">
       <c r="A5" s="19">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>30</v>
+        <v>280</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="J5" s="19"/>
       <c r="K5" s="23">
         <f>LEN(E5)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5" s="24"/>
       <c r="M5" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iannh</v>
+        <v>ah</v>
       </c>
       <c r="N5" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>niah</v>
+        <v>ah</v>
       </c>
       <c r="P5" s="3" t="str">
         <f t="shared" ref="P5:P68" si="3">_xlfn.CONCAT(M5, "(\d)")</f>
-        <v>iannh(\d)</v>
+        <v>ah(\d)</v>
       </c>
       <c r="Q5" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" ref="R5:R68" si="4">IFERROR( IF(Q5="", "", SEARCH(Q5, $N5)), "")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S5" s="3" t="str">
         <f t="shared" ref="S5:S68" si="5">IFERROR( _xlfn.CONCAT(LEFT(N5,R5-1), "@", MID(N5,R5,1), "${1}", RIGHT(N5, LEN(N5)-R5)), "" )</f>
-        <v>ni@a${1}h</v>
+        <v>@a${1}h</v>
       </c>
       <c r="T5" s="25"/>
       <c r="U5" s="26" t="str">
         <f t="shared" ref="U5:U68" si="6">IF(AND(N5&lt;&gt;"", M5&lt;&gt;""), "    - xform/@" &amp; P5 &amp;  "/"  &amp; S5 &amp;  "/", "")</f>
-        <v xml:space="preserve">    - xform/@iannh(\d)/ni@a${1}h/</v>
+        <v xml:space="preserve">    - xform/@ah(\d)/@a${1}h/</v>
       </c>
       <c r="W5" s="7" t="s">
         <v>36</v>
@@ -5241,67 +5282,65 @@
     </row>
     <row r="6" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A6" s="19">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>37</v>
+        <v>302</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>38</v>
+        <v>303</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>38</v>
+        <v>303</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>38</v>
+        <v>303</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>39</v>
+        <v>303</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>40</v>
+        <v>303</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>41</v>
+        <v>304</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="J6" s="19"/>
       <c r="K6" s="23">
         <f>LEN(E6)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L6" s="24"/>
       <c r="M6" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iaunn</v>
+        <v>ai</v>
       </c>
       <c r="N6" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>niao</v>
+        <v>ai</v>
       </c>
       <c r="P6" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iaunn(\d)</v>
+        <v>ai(\d)</v>
       </c>
       <c r="Q6" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S6" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>ni@a${1}o</v>
+        <v>@a${1}i</v>
       </c>
       <c r="T6" s="25"/>
       <c r="U6" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iaunn(\d)/ni@a${1}o/</v>
+        <v xml:space="preserve">    - xform/@ai(\d)/@a${1}i/</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>43</v>
@@ -5392,67 +5431,65 @@
     </row>
     <row r="7" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A7" s="19">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>44</v>
+        <v>182</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="J7" s="19"/>
       <c r="K7" s="23">
         <f>LEN(E7)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L7" s="24"/>
       <c r="M7" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ioonn</v>
+        <v>aih</v>
       </c>
       <c r="N7" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>nioo</v>
+        <v>aih</v>
       </c>
       <c r="P7" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ioonn(\d)</v>
+        <v>aih(\d)</v>
       </c>
       <c r="Q7" s="5" t="str">
-        <v>o</v>
+        <v>a</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S7" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>ni@o${1}o</v>
+        <v>@a${1}ih</v>
       </c>
       <c r="T7" s="25"/>
       <c r="U7" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ioonn(\d)/ni@o${1}o/</v>
+        <v xml:space="preserve">    - xform/@aih(\d)/@a${1}ih/</v>
       </c>
       <c r="W7" s="7" t="s">
         <v>51</v>
@@ -5543,54 +5580,54 @@
     </row>
     <row r="8" spans="1:47" ht="30.75" customHeight="1" thickBot="1">
       <c r="A8" s="19">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="33" t="s">
-        <v>57</v>
+        <v>75</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="J8" s="29" t="s">
         <v>28</v>
       </c>
       <c r="K8" s="23">
         <f>LEN(E8)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="24"/>
       <c r="M8" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iunnh</v>
+        <v>ainn</v>
       </c>
       <c r="N8" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>niuh</v>
+        <v>nai</v>
       </c>
       <c r="P8" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iunnh(\d)</v>
+        <v>ainn(\d)</v>
       </c>
       <c r="Q8" s="5" t="str">
-        <v>i</v>
+        <v>a</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="4"/>
@@ -5598,12 +5635,12 @@
       </c>
       <c r="S8" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@i${1}uh</v>
+        <v>n@a${1}i</v>
       </c>
       <c r="T8" s="25"/>
       <c r="U8" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iunnh(\d)/n@i${1}uh/</v>
+        <v xml:space="preserve">    - xform/@ainn(\d)/n@a${1}i/</v>
       </c>
       <c r="W8" s="7" t="s">
         <v>58</v>
@@ -5694,67 +5731,65 @@
     </row>
     <row r="9" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A9" s="19">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>59</v>
+        <v>298</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>60</v>
+        <v>299</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>60</v>
+        <v>299</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>60</v>
+        <v>299</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>61</v>
+        <v>299</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>62</v>
+        <v>299</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="J9" s="19"/>
       <c r="K9" s="23">
         <f>LEN(E9)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L9" s="24"/>
       <c r="M9" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uainn</v>
+        <v>ak</v>
       </c>
       <c r="N9" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>nuai</v>
+        <v>ak</v>
       </c>
       <c r="P9" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uainn(\d)</v>
+        <v>ak(\d)</v>
       </c>
       <c r="Q9" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S9" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>nu@a${1}i</v>
+        <v>@a${1}k</v>
       </c>
       <c r="T9" s="25"/>
       <c r="U9" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uainn(\d)/nu@a${1}i/</v>
+        <v xml:space="preserve">    - xform/@ak(\d)/@a${1}k/</v>
       </c>
       <c r="W9" s="7" t="s">
         <v>65</v>
@@ -5845,67 +5880,65 @@
     </row>
     <row r="10" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A10" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>66</v>
+        <v>284</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>67</v>
+        <v>284</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>68</v>
+        <v>284</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>69</v>
+        <v>284</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>284</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>70</v>
+        <v>284</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>71</v>
+        <v>285</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="J10" s="19"/>
       <c r="K10" s="23">
         <f>LEN(E10)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L10" s="24"/>
       <c r="M10" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>annh</v>
+        <v>am</v>
       </c>
       <c r="N10" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>nah</v>
+        <v>am</v>
       </c>
       <c r="P10" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>annh(\d)</v>
+        <v>am(\d)</v>
       </c>
       <c r="Q10" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S10" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@a${1}h</v>
+        <v>@a${1}m</v>
       </c>
       <c r="T10" s="25"/>
       <c r="U10" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@annh(\d)/n@a${1}h/</v>
+        <v xml:space="preserve">    - xform/@am(\d)/@a${1}m/</v>
       </c>
       <c r="W10" s="7" t="s">
         <v>73</v>
@@ -5996,226 +6029,222 @@
     </row>
     <row r="11" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A11" s="19">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>74</v>
+        <v>287</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>75</v>
+        <v>287</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>75</v>
+        <v>287</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>75</v>
+        <v>287</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>76</v>
+        <v>287</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>78</v>
+        <v>288</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="J11" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="J11" s="19"/>
       <c r="K11" s="23">
         <f>LEN(E11)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11" s="24"/>
       <c r="M11" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ainn</v>
+        <v>an</v>
       </c>
       <c r="N11" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>nai</v>
+        <v>an</v>
       </c>
       <c r="P11" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ainn(\d)</v>
+        <v>an(\d)</v>
       </c>
       <c r="Q11" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@a${1}i</v>
+        <v>@a${1}n</v>
       </c>
       <c r="T11" s="25"/>
       <c r="U11" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ainn(\d)/n@a${1}i/</v>
+        <v xml:space="preserve">    - xform/@an(\d)/@a${1}n/</v>
       </c>
     </row>
     <row r="12" spans="1:47" ht="30.75" customHeight="1" thickBot="1">
       <c r="A12" s="19">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="J12" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="J12" s="19"/>
       <c r="K12" s="23">
         <f>LEN(E12)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L12" s="24"/>
       <c r="M12" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ennh</v>
+        <v>ang</v>
       </c>
       <c r="N12" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>neh</v>
+        <v>ang</v>
       </c>
       <c r="P12" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ennh(\d)</v>
+        <v>ang(\d)</v>
       </c>
       <c r="Q12" s="5" t="str">
-        <v>e</v>
+        <v>a</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@e${1}h</v>
+        <v>@a${1}ng</v>
       </c>
       <c r="T12" s="25"/>
       <c r="U12" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ennh(\d)/n@e${1}h/</v>
+        <v xml:space="preserve">    - xform/@ang(\d)/@a${1}ng/</v>
       </c>
     </row>
     <row r="13" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A13" s="19">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="J13" s="29" t="s">
         <v>28</v>
       </c>
       <c r="K13" s="23">
         <f>LEN(E13)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13" s="24"/>
       <c r="M13" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iann</v>
+        <v>ann</v>
       </c>
       <c r="N13" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>nia</v>
+        <v>na</v>
       </c>
       <c r="P13" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iann(\d)</v>
+        <v>ann(\d)</v>
       </c>
       <c r="Q13" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R13" s="5">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S13" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>ni@a${1}</v>
+        <v>n@a${1}</v>
       </c>
       <c r="T13" s="25"/>
       <c r="U13" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iann(\d)/ni@a${1}/</v>
+        <v xml:space="preserve">    - xform/@ann(\d)/n@a${1}/</v>
       </c>
     </row>
     <row r="14" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A14" s="19">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>94</v>
+        <v>67</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>69</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="J14" s="29" t="s">
         <v>28</v>
@@ -6227,18 +6256,18 @@
       <c r="L14" s="24"/>
       <c r="M14" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iunn</v>
+        <v>annh</v>
       </c>
       <c r="N14" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>niu</v>
+        <v>nah</v>
       </c>
       <c r="P14" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iunn(\d)</v>
+        <v>annh(\d)</v>
       </c>
       <c r="Q14" s="5" t="str">
-        <v>i</v>
+        <v>a</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="4"/>
@@ -6246,240 +6275,232 @@
       </c>
       <c r="S14" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@i${1}u</v>
+        <v>n@a${1}h</v>
       </c>
       <c r="T14" s="25"/>
       <c r="U14" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iunn(\d)/n@i${1}u/</v>
+        <v xml:space="preserve">    - xform/@annh(\d)/n@a${1}h/</v>
       </c>
     </row>
     <row r="15" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A15" s="19">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>98</v>
+        <v>290</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>99</v>
+        <v>291</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>100</v>
+        <v>291</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>99</v>
+        <v>291</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>54</v>
+        <v>291</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>101</v>
+        <v>291</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>102</v>
+        <v>292</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="J15" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="J15" s="19"/>
       <c r="K15" s="23">
         <f>LEN(E15)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15" s="24"/>
       <c r="M15" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>onnh</v>
+        <v>ap</v>
       </c>
       <c r="N15" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>niuh</v>
+        <v>ap</v>
       </c>
       <c r="P15" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>onnh(\d)</v>
+        <v>ap(\d)</v>
       </c>
       <c r="Q15" s="5" t="str">
-        <v>i</v>
+        <v>a</v>
       </c>
       <c r="R15" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@i${1}uh</v>
+        <v>@a${1}p</v>
       </c>
       <c r="T15" s="25"/>
       <c r="U15" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@onnh(\d)/n@i${1}uh/</v>
+        <v xml:space="preserve">    - xform/@ap(\d)/@a${1}p/</v>
       </c>
     </row>
     <row r="16" spans="1:47" ht="27.75" customHeight="1" thickBot="1">
       <c r="A16" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>104</v>
+        <v>294</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>105</v>
+        <v>295</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>105</v>
+        <v>295</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>105</v>
+        <v>295</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>106</v>
+        <v>295</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>107</v>
+        <v>295</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>108</v>
+        <v>296</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="J16" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="J16" s="19"/>
       <c r="K16" s="23">
         <f>LEN(E16)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" s="24"/>
       <c r="M16" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ann</v>
+        <v>at</v>
       </c>
       <c r="N16" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>na</v>
+        <v>at</v>
       </c>
       <c r="P16" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ann(\d)</v>
+        <v>at(\d)</v>
       </c>
       <c r="Q16" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R16" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@a${1}</v>
+        <v>@a${1}t</v>
       </c>
       <c r="T16" s="25"/>
       <c r="U16" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ann(\d)/n@a${1}/</v>
+        <v xml:space="preserve">    - xform/@at(\d)/@a${1}t/</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A17" s="19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>110</v>
+        <v>306</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>111</v>
+        <v>306</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>111</v>
+        <v>306</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>111</v>
+        <v>306</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>113</v>
+        <v>306</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>114</v>
+        <v>308</v>
       </c>
       <c r="I17" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="J17" s="19"/>
       <c r="K17" s="23">
         <f>LEN(E17)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" s="24"/>
       <c r="M17" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>enn</v>
+        <v>au</v>
       </c>
       <c r="N17" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ne</v>
+        <v>ao</v>
       </c>
       <c r="P17" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>enn(\d)</v>
+        <v>au(\d)</v>
       </c>
       <c r="Q17" s="5" t="str">
-        <v>e</v>
+        <v>a</v>
       </c>
       <c r="R17" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@e${1}</v>
+        <v>@a${1}o</v>
       </c>
       <c r="T17" s="25"/>
       <c r="U17" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@enn(\d)/n@e${1}/</v>
+        <v xml:space="preserve">    - xform/@au(\d)/@a${1}o/</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A18" s="19">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="J18" s="29" t="s">
-        <v>28</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="J18" s="19"/>
       <c r="K18" s="23">
         <f>LEN(E18)</f>
         <v>3</v>
@@ -6487,207 +6508,209 @@
       <c r="L18" s="24"/>
       <c r="M18" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>inn</v>
+        <v>auh</v>
       </c>
       <c r="N18" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ni</v>
+        <v>aoh</v>
       </c>
       <c r="P18" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>inn(\d)</v>
+        <v>auh(\d)</v>
       </c>
       <c r="Q18" s="5" t="str">
-        <v>i</v>
+        <v>a</v>
       </c>
       <c r="R18" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@i${1}</v>
+        <v>@a${1}oh</v>
       </c>
       <c r="T18" s="25"/>
       <c r="U18" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@inn(\d)/n@i${1}/</v>
+        <v xml:space="preserve">    - xform/@auh(\d)/@a${1}oh/</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A19" s="19">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>127</v>
+        <v>389</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>129</v>
+        <v>391</v>
       </c>
       <c r="J19" s="19"/>
       <c r="K19" s="23">
         <f>LEN(E19)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L19" s="24"/>
       <c r="M19" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iang</v>
+        <v>e</v>
       </c>
       <c r="N19" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iang</v>
+        <v>e</v>
       </c>
       <c r="P19" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iang(\d)</v>
+        <v>e(\d)</v>
       </c>
       <c r="Q19" s="5" t="str">
-        <v>a</v>
+        <v>e</v>
       </c>
       <c r="R19" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}ng</v>
+        <v>@e${1}</v>
       </c>
       <c r="T19" s="25"/>
       <c r="U19" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iang(\d)/i@a${1}ng/</v>
+        <v xml:space="preserve">    - xform/@e(\d)/@e${1}/</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A20" s="19">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>131</v>
+        <v>311</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>131</v>
+        <v>311</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>131</v>
+        <v>311</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>131</v>
+        <v>311</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>133</v>
+        <v>312</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>134</v>
+        <v>313</v>
       </c>
       <c r="J20" s="19"/>
       <c r="K20" s="23">
         <f>LEN(E20)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L20" s="24"/>
       <c r="M20" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iauh</v>
+        <v>eh</v>
       </c>
       <c r="N20" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iaoh</v>
+        <v>eh</v>
       </c>
       <c r="P20" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iauh(\d)</v>
+        <v>eh(\d)</v>
       </c>
       <c r="Q20" s="5" t="str">
-        <v>a</v>
+        <v>e</v>
       </c>
       <c r="R20" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}oh</v>
+        <v>@e${1}h</v>
       </c>
       <c r="T20" s="25"/>
       <c r="U20" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iauh(\d)/i@a${1}oh/</v>
+        <v xml:space="preserve">    - xform/@eh(\d)/@e${1}h/</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A21" s="19">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="J21" s="19"/>
+        <v>115</v>
+      </c>
+      <c r="J21" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K21" s="23">
         <f>LEN(E21)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21" s="24"/>
       <c r="M21" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iorh</v>
+        <v>enn</v>
       </c>
       <c r="N21" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ioh</v>
+        <v>ne</v>
       </c>
       <c r="P21" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iorh(\d)</v>
+        <v>enn(\d)</v>
       </c>
       <c r="Q21" s="5" t="str">
-        <v>o</v>
+        <v>e</v>
       </c>
       <c r="R21" s="5">
         <f t="shared" si="4"/>
@@ -6695,43 +6718,45 @@
       </c>
       <c r="S21" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@o${1}h</v>
+        <v>n@e${1}</v>
       </c>
       <c r="T21" s="25"/>
       <c r="U21" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iorh(\d)/i@o${1}h/</v>
+        <v xml:space="preserve">    - xform/@enn(\d)/n@e${1}/</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A22" s="19">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="J22" s="19"/>
+        <v>81</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="J22" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K22" s="23">
         <f>LEN(E22)</f>
         <v>4</v>
@@ -6739,18 +6764,18 @@
       <c r="L22" s="24"/>
       <c r="M22" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iong</v>
+        <v>ennh</v>
       </c>
       <c r="N22" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iong</v>
+        <v>neh</v>
       </c>
       <c r="P22" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iong(\d)</v>
+        <v>ennh(\d)</v>
       </c>
       <c r="Q22" s="5" t="str">
-        <v>o</v>
+        <v>e</v>
       </c>
       <c r="R22" s="5">
         <f t="shared" si="4"/>
@@ -6758,125 +6783,125 @@
       </c>
       <c r="S22" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@o${1}ng</v>
+        <v>n@e${1}h</v>
       </c>
       <c r="T22" s="25"/>
       <c r="U22" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iong(\d)/i@o${1}ng/</v>
+        <v xml:space="preserve">    - xform/@ennh(\d)/n@e${1}h/</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A23" s="19">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>147</v>
+        <v>392</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>148</v>
+        <v>393</v>
       </c>
       <c r="J23" s="19"/>
       <c r="K23" s="23">
         <f>LEN(E23)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L23" s="24"/>
       <c r="M23" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iook</v>
+        <v>i</v>
       </c>
       <c r="N23" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iok</v>
+        <v>i</v>
       </c>
       <c r="P23" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iook(\d)</v>
+        <v>i(\d)</v>
       </c>
       <c r="Q23" s="5" t="str">
-        <v>o</v>
+        <v>i</v>
       </c>
       <c r="R23" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@o${1}k</v>
+        <v>@i${1}</v>
       </c>
       <c r="T23" s="25"/>
       <c r="U23" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iook(\d)/i@o${1}k/</v>
+        <v xml:space="preserve">    - xform/@i(\d)/@i${1}/</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A24" s="19">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>149</v>
+        <v>337</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>150</v>
+        <v>338</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>150</v>
+        <v>338</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>151</v>
+        <v>338</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>152</v>
+        <v>338</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>153</v>
+        <v>338</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>154</v>
+        <v>339</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>155</v>
+        <v>340</v>
       </c>
       <c r="J24" s="19"/>
       <c r="K24" s="23">
         <f>LEN(E24)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L24" s="24"/>
       <c r="M24" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>oonn</v>
+        <v>ia</v>
       </c>
       <c r="N24" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>noo</v>
+        <v>ia</v>
       </c>
       <c r="P24" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>oonn(\d)</v>
+        <v>ia(\d)</v>
       </c>
       <c r="Q24" s="5" t="str">
-        <v>o</v>
+        <v>a</v>
       </c>
       <c r="R24" s="5">
         <f t="shared" si="4"/>
@@ -6884,122 +6909,122 @@
       </c>
       <c r="S24" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@o${1}o</v>
+        <v>i@a${1}</v>
       </c>
       <c r="T24" s="25"/>
       <c r="U24" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@oonn(\d)/n@o${1}o/</v>
+        <v xml:space="preserve">    - xform/@ia(\d)/i@a${1}/</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A25" s="19">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="23">
         <f>LEN(E25)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L25" s="24"/>
       <c r="M25" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uann</v>
+        <v>iah</v>
       </c>
       <c r="N25" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>nua</v>
+        <v>iah</v>
       </c>
       <c r="P25" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uann(\d)</v>
+        <v>iah(\d)</v>
       </c>
       <c r="Q25" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R25" s="5">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S25" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>nu@a${1}</v>
+        <v>i@a${1}h</v>
       </c>
       <c r="T25" s="25"/>
       <c r="U25" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uann(\d)/nu@a${1}/</v>
+        <v xml:space="preserve">    - xform/@iah(\d)/i@a${1}h/</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A26" s="19">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>166</v>
+        <v>218</v>
       </c>
       <c r="J26" s="19"/>
       <c r="K26" s="23">
         <f>LEN(E26)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L26" s="24"/>
       <c r="M26" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uang</v>
+        <v>iak</v>
       </c>
       <c r="N26" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uang</v>
+        <v>iak</v>
       </c>
       <c r="P26" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uang(\d)</v>
+        <v>iak(\d)</v>
       </c>
       <c r="Q26" s="5" t="str">
         <v>a</v>
@@ -7010,59 +7035,59 @@
       </c>
       <c r="S26" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>u@a${1}ng</v>
+        <v>i@a${1}k</v>
       </c>
       <c r="T26" s="25"/>
       <c r="U26" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uang(\d)/u@a${1}ng/</v>
+        <v xml:space="preserve">    - xform/@iak(\d)/i@a${1}k/</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A27" s="19">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="J27" s="19"/>
       <c r="K27" s="23">
         <f>LEN(E27)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L27" s="24"/>
       <c r="M27" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uaih</v>
+        <v>iam</v>
       </c>
       <c r="N27" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uaih</v>
+        <v>iam</v>
       </c>
       <c r="P27" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uaih(\d)</v>
+        <v>iam(\d)</v>
       </c>
       <c r="Q27" s="5" t="str">
         <v>a</v>
@@ -7073,62 +7098,62 @@
       </c>
       <c r="S27" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>u@a${1}ih</v>
+        <v>i@a${1}m</v>
       </c>
       <c r="T27" s="25"/>
       <c r="U27" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uaih(\d)/u@a${1}ih/</v>
+        <v xml:space="preserve">    - xform/@iam(\d)/i@a${1}m/</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A28" s="19">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="J28" s="19"/>
       <c r="K28" s="23">
         <f>LEN(E28)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L28" s="24"/>
       <c r="M28" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uinn</v>
+        <v>ian</v>
       </c>
       <c r="N28" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>nui</v>
+        <v>ian</v>
       </c>
       <c r="P28" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uinn(\d)</v>
+        <v>ian(\d)</v>
       </c>
       <c r="Q28" s="5" t="str">
-        <v>u</v>
+        <v>a</v>
       </c>
       <c r="R28" s="5">
         <f t="shared" si="4"/>
@@ -7136,230 +7161,234 @@
       </c>
       <c r="S28" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>n@u${1}i</v>
+        <v>i@a${1}n</v>
       </c>
       <c r="T28" s="25"/>
       <c r="U28" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uinn(\d)/n@u${1}i/</v>
+        <v xml:space="preserve">    - xform/@ian(\d)/i@a${1}n/</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A29" s="19">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F29" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G29" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="H29" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="I29" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="J29" s="29"/>
+        <v>127</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="J29" s="19"/>
       <c r="K29" s="23">
         <f>LEN(E29)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="24"/>
       <c r="M29" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uih</v>
+        <v>iang</v>
       </c>
       <c r="N29" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>uih</v>
+        <v>iang</v>
       </c>
       <c r="P29" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uih(\d)</v>
+        <v>iang(\d)</v>
       </c>
       <c r="Q29" s="5" t="str">
-        <v>u</v>
+        <v>a</v>
       </c>
       <c r="R29" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S29" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@u${1}ih</v>
+        <v>i@a${1}ng</v>
       </c>
       <c r="T29" s="25"/>
       <c r="U29" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uih(\d)/@u${1}ih/</v>
+        <v xml:space="preserve">    - xform/@iang(\d)/i@a${1}ng/</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A30" s="19">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>178</v>
+        <v>86</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="J30" s="19"/>
+        <v>91</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K30" s="23">
         <f>LEN(E30)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="24"/>
       <c r="M30" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ang</v>
+        <v>iann</v>
       </c>
       <c r="N30" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ang</v>
+        <v>nia</v>
       </c>
       <c r="P30" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ang(\d)</v>
+        <v>iann(\d)</v>
       </c>
       <c r="Q30" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R30" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S30" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}ng</v>
+        <v>ni@a${1}</v>
       </c>
       <c r="T30" s="25"/>
       <c r="U30" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ang(\d)/@a${1}ng/</v>
+        <v xml:space="preserve">    - xform/@iann(\d)/ni@a${1}/</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="30.75" customHeight="1" thickBot="1">
       <c r="A31" s="19">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="I31" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="J31" s="19"/>
+        <v>35</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K31" s="23">
         <f>LEN(E31)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L31" s="24"/>
       <c r="M31" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>aih</v>
+        <v>iannh</v>
       </c>
       <c r="N31" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>aih</v>
+        <v>niah</v>
       </c>
       <c r="P31" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>aih(\d)</v>
+        <v>iannh(\d)</v>
       </c>
       <c r="Q31" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R31" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S31" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}ih</v>
+        <v>ni@a${1}h</v>
       </c>
       <c r="T31" s="25"/>
       <c r="U31" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@aih(\d)/@a${1}ih/</v>
+        <v xml:space="preserve">    - xform/@iannh(\d)/ni@a${1}h/</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A32" s="19">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="J32" s="19"/>
       <c r="K32" s="23">
@@ -7369,60 +7398,60 @@
       <c r="L32" s="24"/>
       <c r="M32" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>auh</v>
+        <v>iap</v>
       </c>
       <c r="N32" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>aoh</v>
+        <v>iap</v>
       </c>
       <c r="P32" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>auh(\d)</v>
+        <v>iap(\d)</v>
       </c>
       <c r="Q32" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R32" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S32" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}oh</v>
+        <v>i@a${1}p</v>
       </c>
       <c r="T32" s="25"/>
       <c r="U32" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@auh(\d)/@a${1}oh/</v>
+        <v xml:space="preserve">    - xform/@iap(\d)/i@a${1}p/</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A33" s="19">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="J33" s="19"/>
       <c r="K33" s="23">
@@ -7432,60 +7461,60 @@
       <c r="L33" s="24"/>
       <c r="M33" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ing</v>
+        <v>iat</v>
       </c>
       <c r="N33" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>ing</v>
+        <v>iat</v>
       </c>
       <c r="P33" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ing(\d)</v>
+        <v>iat(\d)</v>
       </c>
       <c r="Q33" s="5" t="str">
-        <v>i</v>
+        <v>a</v>
       </c>
       <c r="R33" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S33" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@i${1}ng</v>
+        <v>i@a${1}t</v>
       </c>
       <c r="T33" s="25"/>
       <c r="U33" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ing(\d)/@i${1}ng/</v>
+        <v xml:space="preserve">    - xform/@iat(\d)/i@a${1}t/</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A34" s="19">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>34</v>
+        <v>222</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="J34" s="19"/>
       <c r="K34" s="23">
@@ -7495,15 +7524,15 @@
       <c r="L34" s="24"/>
       <c r="M34" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iah</v>
+        <v>iau</v>
       </c>
       <c r="N34" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>iah</v>
+        <v>iao</v>
       </c>
       <c r="P34" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iah(\d)</v>
+        <v>iau(\d)</v>
       </c>
       <c r="Q34" s="5" t="str">
         <v>a</v>
@@ -7514,59 +7543,59 @@
       </c>
       <c r="S34" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}h</v>
+        <v>i@a${1}o</v>
       </c>
       <c r="T34" s="25"/>
       <c r="U34" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iah(\d)/i@a${1}h/</v>
+        <v xml:space="preserve">    - xform/@iau(\d)/i@a${1}o/</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A35" s="19">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>199</v>
+        <v>130</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>200</v>
+        <v>131</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>200</v>
+        <v>131</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>200</v>
+        <v>131</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>200</v>
+        <v>131</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>201</v>
+        <v>133</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="J35" s="19"/>
       <c r="K35" s="23">
         <f>LEN(E35)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35" s="24"/>
       <c r="M35" s="11" t="str">
         <f t="shared" ref="M35:N66" si="7">E35</f>
-        <v>iam</v>
+        <v>iauh</v>
       </c>
       <c r="N35" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>iam</v>
+        <v>iaoh</v>
       </c>
       <c r="P35" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iam(\d)</v>
+        <v>iauh(\d)</v>
       </c>
       <c r="Q35" s="5" t="str">
         <v>a</v>
@@ -7577,356 +7606,358 @@
       </c>
       <c r="S35" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}m</v>
+        <v>i@a${1}oh</v>
       </c>
       <c r="T35" s="25"/>
       <c r="U35" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iam(\d)/i@a${1}m/</v>
+        <v xml:space="preserve">    - xform/@iauh(\d)/i@a${1}oh/</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A36" s="19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>203</v>
+        <v>37</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>204</v>
+        <v>38</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>204</v>
+        <v>38</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>204</v>
+        <v>38</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>204</v>
+        <v>39</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>205</v>
+        <v>41</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="J36" s="19"/>
+        <v>42</v>
+      </c>
+      <c r="J36" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K36" s="23">
         <f>LEN(E36)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L36" s="24"/>
       <c r="M36" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ian</v>
+        <v>iaunn</v>
       </c>
       <c r="N36" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ian</v>
+        <v>niao</v>
       </c>
       <c r="P36" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ian(\d)</v>
+        <v>iaunn(\d)</v>
       </c>
       <c r="Q36" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R36" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}n</v>
+        <v>ni@a${1}o</v>
       </c>
       <c r="T36" s="25"/>
       <c r="U36" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ian(\d)/i@a${1}n/</v>
+        <v xml:space="preserve">    - xform/@iaunn(\d)/ni@a${1}o/</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A37" s="19">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>207</v>
+        <v>314</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>209</v>
+        <v>316</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>210</v>
+        <v>317</v>
       </c>
       <c r="J37" s="19"/>
       <c r="K37" s="23">
         <f>LEN(E37)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L37" s="24"/>
       <c r="M37" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>iap</v>
+        <v>ih</v>
       </c>
       <c r="N37" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>iap</v>
+        <v>ih</v>
       </c>
       <c r="P37" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iap(\d)</v>
+        <v>ih(\d)</v>
       </c>
       <c r="Q37" s="5" t="str">
-        <v>a</v>
+        <v>i</v>
       </c>
       <c r="R37" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S37" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}p</v>
+        <v>@i${1}h</v>
       </c>
       <c r="T37" s="25"/>
       <c r="U37" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iap(\d)/i@a${1}p/</v>
+        <v xml:space="preserve">    - xform/@ih(\d)/@i${1}h/</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A38" s="19">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>211</v>
+        <v>332</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>212</v>
+        <v>334</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>213</v>
+        <v>335</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>214</v>
+        <v>336</v>
       </c>
       <c r="J38" s="19"/>
       <c r="K38" s="23">
         <f>LEN(E38)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" s="24"/>
       <c r="M38" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>iat</v>
+        <v>ik</v>
       </c>
       <c r="N38" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>iat</v>
+        <v>ik</v>
       </c>
       <c r="P38" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iat(\d)</v>
+        <v>ik(\d)</v>
       </c>
       <c r="Q38" s="5" t="str">
-        <v>a</v>
+        <v>i</v>
       </c>
       <c r="R38" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S38" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}t</v>
+        <v>@i${1}k</v>
       </c>
       <c r="T38" s="25"/>
       <c r="U38" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iat(\d)/i@a${1}t/</v>
+        <v xml:space="preserve">    - xform/@ik(\d)/@i${1}k/</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A39" s="19">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>215</v>
+        <v>318</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>216</v>
+        <v>318</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>216</v>
+        <v>318</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>216</v>
+        <v>318</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>216</v>
+        <v>318</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>216</v>
+        <v>318</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>217</v>
+        <v>319</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>218</v>
+        <v>320</v>
       </c>
       <c r="J39" s="19"/>
       <c r="K39" s="23">
         <f>LEN(E39)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L39" s="24"/>
       <c r="M39" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>iak</v>
+        <v>im</v>
       </c>
       <c r="N39" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>iak</v>
+        <v>im</v>
       </c>
       <c r="P39" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iak(\d)</v>
+        <v>im(\d)</v>
       </c>
       <c r="Q39" s="5" t="str">
-        <v>a</v>
+        <v>i</v>
       </c>
       <c r="R39" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S39" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}k</v>
+        <v>@i${1}m</v>
       </c>
       <c r="T39" s="25"/>
       <c r="U39" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iak(\d)/i@a${1}k/</v>
+        <v xml:space="preserve">    - xform/@im(\d)/@i${1}m/</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A40" s="19">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>219</v>
+        <v>321</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>221</v>
+        <v>321</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>222</v>
+        <v>322</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>223</v>
+        <v>323</v>
       </c>
       <c r="J40" s="19"/>
       <c r="K40" s="23">
         <f>LEN(E40)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" s="24"/>
       <c r="M40" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>iau</v>
+        <v>in</v>
       </c>
       <c r="N40" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>iao</v>
+        <v>in</v>
       </c>
       <c r="P40" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>iau(\d)</v>
+        <v>in(\d)</v>
       </c>
       <c r="Q40" s="5" t="str">
-        <v>a</v>
+        <v>i</v>
       </c>
       <c r="R40" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S40" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}o</v>
+        <v>@i${1}n</v>
       </c>
       <c r="T40" s="25"/>
       <c r="U40" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@iau(\d)/i@a${1}o/</v>
+        <v xml:space="preserve">    - xform/@in(\d)/@i${1}n/</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A41" s="19">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="J41" s="19"/>
       <c r="K41" s="23">
@@ -7936,62 +7967,64 @@
       <c r="L41" s="24"/>
       <c r="M41" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ior</v>
+        <v>ing</v>
       </c>
       <c r="N41" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>io</v>
+        <v>ing</v>
       </c>
       <c r="P41" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ior(\d)</v>
+        <v>ing(\d)</v>
       </c>
       <c r="Q41" s="5" t="str">
-        <v>o</v>
+        <v>i</v>
       </c>
       <c r="R41" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S41" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@o${1}</v>
+        <v>@i${1}ng</v>
       </c>
       <c r="T41" s="25"/>
       <c r="U41" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ior(\d)/i@o${1}/</v>
+        <v xml:space="preserve">    - xform/@ing(\d)/@i${1}ng/</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A42" s="19">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>229</v>
+        <v>116</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>230</v>
+        <v>117</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>230</v>
+        <v>117</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>231</v>
+        <v>117</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>230</v>
+        <v>118</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>230</v>
+        <v>119</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>232</v>
+        <v>120</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="J42" s="19"/>
+        <v>121</v>
+      </c>
+      <c r="J42" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K42" s="23">
         <f>LEN(E42)</f>
         <v>3</v>
@@ -7999,249 +8032,251 @@
       <c r="L42" s="24"/>
       <c r="M42" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>orh</v>
+        <v>inn</v>
       </c>
       <c r="N42" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>oh</v>
+        <v>ni</v>
       </c>
       <c r="P42" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>orh(\d)</v>
+        <v>inn(\d)</v>
       </c>
       <c r="Q42" s="5" t="str">
-        <v>o</v>
+        <v>i</v>
       </c>
       <c r="R42" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S42" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@o${1}h</v>
+        <v>n@i${1}</v>
       </c>
       <c r="T42" s="25"/>
       <c r="U42" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@orh(\d)/@o${1}h/</v>
+        <v xml:space="preserve">    - xform/@inn(\d)/n@i${1}/</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="30.75" customHeight="1" thickBot="1">
       <c r="A43" s="19">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="E43" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="G43" s="31" t="s">
-        <v>236</v>
-      </c>
-      <c r="H43" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="I43" s="34" t="s">
-        <v>238</v>
+        <v>141</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="G43" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="H43" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>143</v>
       </c>
       <c r="J43" s="19"/>
       <c r="K43" s="23">
         <f>LEN(E43)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L43" s="24"/>
       <c r="M43" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ooh</v>
+        <v>iong</v>
       </c>
       <c r="N43" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ooh</v>
+        <v>iong</v>
       </c>
       <c r="P43" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ooh(\d)</v>
+        <v>iong(\d)</v>
       </c>
       <c r="Q43" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R43" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S43" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@o${1}oh</v>
+        <v>i@o${1}ng</v>
       </c>
       <c r="T43" s="25"/>
       <c r="U43" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ooh(\d)/@o${1}oh/</v>
+        <v xml:space="preserve">    - xform/@iong(\d)/i@o${1}ng/</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A44" s="19">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>239</v>
+        <v>144</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>242</v>
+        <v>147</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>243</v>
+        <v>148</v>
       </c>
       <c r="J44" s="19"/>
       <c r="K44" s="23">
         <f>LEN(E44)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L44" s="24"/>
       <c r="M44" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>oom</v>
+        <v>iook</v>
       </c>
       <c r="N44" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>om</v>
+        <v>iok</v>
       </c>
       <c r="P44" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>oom(\d)</v>
+        <v>iook(\d)</v>
       </c>
       <c r="Q44" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R44" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S44" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@o${1}m</v>
+        <v>i@o${1}k</v>
       </c>
       <c r="T44" s="25"/>
       <c r="U44" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@oom(\d)/@o${1}m/</v>
+        <v xml:space="preserve">    - xform/@iook(\d)/i@o${1}k/</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A45" s="19">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>245</v>
+        <v>45</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>245</v>
+        <v>45</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>245</v>
+        <v>46</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>246</v>
+        <v>49</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="J45" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="J45" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K45" s="23">
         <f>LEN(E45)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L45" s="24"/>
       <c r="M45" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ong</v>
+        <v>ioonn</v>
       </c>
       <c r="N45" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ong</v>
+        <v>nioo</v>
       </c>
       <c r="P45" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ong(\d)</v>
+        <v>ioonn(\d)</v>
       </c>
       <c r="Q45" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R45" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S45" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@o${1}ng</v>
+        <v>ni@o${1}o</v>
       </c>
       <c r="T45" s="25"/>
       <c r="U45" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ong(\d)/@o${1}ng/</v>
+        <v xml:space="preserve">    - xform/@ioonn(\d)/ni@o${1}o/</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A46" s="19">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="J46" s="19"/>
       <c r="K46" s="23">
@@ -8251,81 +8286,81 @@
       <c r="L46" s="24"/>
       <c r="M46" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>oop</v>
+        <v>ior</v>
       </c>
       <c r="N46" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>op</v>
+        <v>io</v>
       </c>
       <c r="P46" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>oop(\d)</v>
+        <v>ior(\d)</v>
       </c>
       <c r="Q46" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R46" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S46" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@o${1}p</v>
+        <v>i@o${1}</v>
       </c>
       <c r="T46" s="25"/>
       <c r="U46" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@oop(\d)/@o${1}p/</v>
+        <v xml:space="preserve">    - xform/@ior(\d)/i@o${1}/</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A47" s="19">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>253</v>
+        <v>135</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>254</v>
+        <v>137</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>255</v>
+        <v>136</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>256</v>
+        <v>138</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c r="J47" s="19"/>
       <c r="K47" s="23">
         <f>LEN(E47)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L47" s="24"/>
       <c r="M47" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>uah</v>
+        <v>iorh</v>
       </c>
       <c r="N47" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>uah</v>
+        <v>ioh</v>
       </c>
       <c r="P47" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uah(\d)</v>
+        <v>iorh(\d)</v>
       </c>
       <c r="Q47" s="49" t="str">
-        <v>a</v>
+        <v>o</v>
       </c>
       <c r="R47" s="5">
         <f t="shared" si="4"/>
@@ -8333,251 +8368,253 @@
       </c>
       <c r="S47" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>u@a${1}h</v>
+        <v>i@o${1}h</v>
       </c>
       <c r="T47" s="25"/>
       <c r="U47" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uah(\d)/u@a${1}h/</v>
+        <v xml:space="preserve">    - xform/@iorh(\d)/i@o${1}h/</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A48" s="19">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>258</v>
+        <v>324</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>259</v>
+        <v>325</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>260</v>
+        <v>326</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>261</v>
+        <v>327</v>
       </c>
       <c r="J48" s="19"/>
       <c r="K48" s="23">
         <f>LEN(E48)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L48" s="24"/>
       <c r="M48" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>uan</v>
+        <v>ip</v>
       </c>
       <c r="N48" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>uan</v>
+        <v>ip</v>
       </c>
       <c r="P48" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uan(\d)</v>
+        <v>ip(\d)</v>
       </c>
       <c r="Q48" s="5" t="str">
-        <v>a</v>
+        <v>i</v>
       </c>
       <c r="R48" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S48" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>u@a${1}n</v>
+        <v>@i${1}p</v>
       </c>
       <c r="T48" s="25"/>
       <c r="U48" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uan(\d)/u@a${1}n/</v>
+        <v xml:space="preserve">    - xform/@ip(\d)/@i${1}p/</v>
       </c>
     </row>
     <row r="49" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A49" s="19">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>262</v>
+        <v>328</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>263</v>
+        <v>329</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>263</v>
+        <v>329</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>263</v>
+        <v>329</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>263</v>
+        <v>329</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>264</v>
+        <v>329</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>265</v>
+        <v>330</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>266</v>
+        <v>331</v>
       </c>
       <c r="J49" s="19"/>
       <c r="K49" s="23">
         <f>LEN(E49)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="24"/>
       <c r="M49" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>uat</v>
+        <v>it</v>
       </c>
       <c r="N49" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>uat</v>
+        <v>it</v>
       </c>
       <c r="P49" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uat(\d)</v>
+        <v>it(\d)</v>
       </c>
       <c r="Q49" s="5" t="str">
-        <v>a</v>
+        <v>i</v>
       </c>
       <c r="R49" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S49" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>u@a${1}t</v>
+        <v>@i${1}t</v>
       </c>
       <c r="T49" s="25"/>
       <c r="U49" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uat(\d)/u@a${1}t/</v>
+        <v xml:space="preserve">    - xform/@it(\d)/@i${1}t/</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A50" s="19">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>267</v>
+        <v>341</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>267</v>
+        <v>341</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>267</v>
+        <v>341</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>267</v>
+        <v>341</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>267</v>
+        <v>341</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>268</v>
+        <v>341</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>269</v>
+        <v>342</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>270</v>
+        <v>343</v>
       </c>
       <c r="J50" s="19"/>
       <c r="K50" s="23">
         <f>LEN(E50)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="24"/>
       <c r="M50" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>uai</v>
+        <v>iu</v>
       </c>
       <c r="N50" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>uai</v>
+        <v>iu</v>
       </c>
       <c r="P50" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>uai(\d)</v>
+        <v>iu(\d)</v>
       </c>
       <c r="Q50" s="5" t="str">
-        <v>a</v>
+        <v>i</v>
       </c>
       <c r="R50" s="5">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S50" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>u@a${1}i</v>
+        <v>@i${1}u</v>
       </c>
       <c r="T50" s="25"/>
       <c r="U50" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@uai(\d)/u@a${1}i/</v>
+        <v xml:space="preserve">    - xform/@iu(\d)/@i${1}u/</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A51" s="19">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>271</v>
+        <v>92</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>272</v>
+        <v>93</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>272</v>
+        <v>93</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>272</v>
+        <v>93</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>272</v>
+        <v>94</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>273</v>
+        <v>95</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>274</v>
+        <v>96</v>
       </c>
       <c r="I51" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="J51" s="19"/>
+        <v>97</v>
+      </c>
+      <c r="J51" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K51" s="23">
         <f>LEN(E51)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51" s="24"/>
       <c r="M51" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ueh</v>
+        <v>iunn</v>
       </c>
       <c r="N51" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ueh</v>
+        <v>niu</v>
       </c>
       <c r="P51" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ueh(\d)</v>
+        <v>iunn(\d)</v>
       </c>
       <c r="Q51" s="5" t="str">
-        <v>e</v>
+        <v>i</v>
       </c>
       <c r="R51" s="5">
         <f t="shared" si="4"/>
@@ -8585,125 +8622,127 @@
       </c>
       <c r="S51" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>u@e${1}h</v>
+        <v>n@i${1}u</v>
       </c>
       <c r="T51" s="25"/>
       <c r="U51" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ueh(\d)/u@e${1}h/</v>
+        <v xml:space="preserve">    - xform/@iunn(\d)/n@i${1}u/</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A52" s="19">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>276</v>
+        <v>52</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="D52" s="31" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="E52" s="31" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>277</v>
+        <v>54</v>
       </c>
       <c r="G52" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="H52" s="35" t="s">
-        <v>278</v>
-      </c>
-      <c r="I52" s="34" t="s">
-        <v>279</v>
-      </c>
-      <c r="J52" s="19"/>
+        <v>55</v>
+      </c>
+      <c r="H52" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="I52" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="J52" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K52" s="23">
         <f>LEN(E52)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L52" s="24"/>
       <c r="M52" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ngh</v>
+        <v>iunnh</v>
       </c>
       <c r="N52" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ngh</v>
+        <v>niuh</v>
       </c>
       <c r="P52" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ngh(\d)</v>
+        <v>iunnh(\d)</v>
       </c>
       <c r="Q52" s="5" t="str">
-        <v>n</v>
+        <v>i</v>
       </c>
       <c r="R52" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S52" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@n${1}gh</v>
+        <v>n@i${1}uh</v>
       </c>
       <c r="T52" s="25"/>
       <c r="U52" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ngh(\d)/@n${1}gh/</v>
+        <v xml:space="preserve">    - xform/@iunnh(\d)/n@i${1}uh/</v>
       </c>
     </row>
     <row r="53" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A53" s="19">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>280</v>
+        <v>396</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>281</v>
+        <v>65</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>281</v>
+        <v>65</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>281</v>
+        <v>65</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>281</v>
+        <v>65</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>281</v>
+        <v>65</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>282</v>
+        <v>397</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>283</v>
+        <v>398</v>
       </c>
       <c r="J53" s="19"/>
       <c r="K53" s="23">
         <f>LEN(E53)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="24"/>
       <c r="M53" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ah</v>
+        <v>m</v>
       </c>
       <c r="N53" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ah</v>
+        <v>m</v>
       </c>
       <c r="P53" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ah(\d)</v>
+        <v>m(\d)</v>
       </c>
       <c r="Q53" s="5" t="str">
-        <v>a</v>
+        <v>m</v>
       </c>
       <c r="R53" s="5">
         <f t="shared" si="4"/>
@@ -8711,41 +8750,41 @@
       </c>
       <c r="S53" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}h</v>
+        <v>@m${1}</v>
       </c>
       <c r="T53" s="25"/>
       <c r="U53" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ah(\d)/@a${1}h/</v>
+        <v xml:space="preserve">    - xform/@m(\d)/@m${1}/</v>
       </c>
     </row>
     <row r="54" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A54" s="19">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>284</v>
+        <v>379</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="G54" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="I54" s="19" t="s">
-        <v>286</v>
+        <v>380</v>
+      </c>
+      <c r="D54" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="E54" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="G54" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="H54" s="35" t="s">
+        <v>381</v>
+      </c>
+      <c r="I54" s="34" t="s">
+        <v>382</v>
       </c>
       <c r="J54" s="19"/>
       <c r="K54" s="23">
@@ -8755,18 +8794,18 @@
       <c r="L54" s="24"/>
       <c r="M54" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>am</v>
+        <v>mh</v>
       </c>
       <c r="N54" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>am</v>
+        <v>mh</v>
       </c>
       <c r="P54" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>am(\d)</v>
+        <v>mh(\d)</v>
       </c>
       <c r="Q54" s="5" t="str">
-        <v>a</v>
+        <v>m</v>
       </c>
       <c r="R54" s="5">
         <f t="shared" si="4"/>
@@ -8774,41 +8813,41 @@
       </c>
       <c r="S54" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}m</v>
+        <v>@m${1}h</v>
       </c>
       <c r="T54" s="25"/>
       <c r="U54" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@am(\d)/@a${1}m/</v>
+        <v xml:space="preserve">    - xform/@mh(\d)/@m${1}h/</v>
       </c>
     </row>
     <row r="55" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A55" s="19">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>287</v>
+        <v>383</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>287</v>
+        <v>384</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>287</v>
+        <v>384</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>287</v>
+        <v>384</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>287</v>
+        <v>384</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>287</v>
+        <v>384</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>288</v>
+        <v>385</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="J55" s="19"/>
       <c r="K55" s="23">
@@ -8818,18 +8857,18 @@
       <c r="L55" s="24"/>
       <c r="M55" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>an</v>
+        <v>ng</v>
       </c>
       <c r="N55" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>an</v>
+        <v>ng</v>
       </c>
       <c r="P55" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>an(\d)</v>
+        <v>ng(\d)</v>
       </c>
       <c r="Q55" s="5" t="str">
-        <v>a</v>
+        <v>n</v>
       </c>
       <c r="R55" s="5">
         <f t="shared" si="4"/>
@@ -8837,62 +8876,62 @@
       </c>
       <c r="S55" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}n</v>
+        <v>@n${1}g</v>
       </c>
       <c r="T55" s="25"/>
       <c r="U55" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@an(\d)/@a${1}n/</v>
+        <v xml:space="preserve">    - xform/@ng(\d)/@n${1}g/</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A56" s="19">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="G56" s="22" t="s">
-        <v>291</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="I56" s="19" t="s">
-        <v>293</v>
+        <v>277</v>
+      </c>
+      <c r="D56" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="E56" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="F56" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="G56" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="H56" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="I56" s="34" t="s">
+        <v>279</v>
       </c>
       <c r="J56" s="19"/>
       <c r="K56" s="23">
         <f>LEN(E56)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L56" s="24"/>
       <c r="M56" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ap</v>
+        <v>ngh</v>
       </c>
       <c r="N56" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ap</v>
+        <v>ngh</v>
       </c>
       <c r="P56" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ap(\d)</v>
+        <v>ngh(\d)</v>
       </c>
       <c r="Q56" s="5" t="str">
-        <v>a</v>
+        <v>n</v>
       </c>
       <c r="R56" s="5">
         <f t="shared" si="4"/>
@@ -8900,41 +8939,41 @@
       </c>
       <c r="S56" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}p</v>
+        <v>@n${1}gh</v>
       </c>
       <c r="T56" s="25"/>
       <c r="U56" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ap(\d)/@a${1}p/</v>
+        <v xml:space="preserve">    - xform/@ngh(\d)/@n${1}gh/</v>
       </c>
     </row>
     <row r="57" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A57" s="19">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="I57" s="19" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="J57" s="19"/>
       <c r="K57" s="23">
@@ -8944,18 +8983,18 @@
       <c r="L57" s="24"/>
       <c r="M57" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>at</v>
+        <v>ok</v>
       </c>
       <c r="N57" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>at</v>
+        <v>ok</v>
       </c>
       <c r="P57" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>at(\d)</v>
+        <v>ok(\d)</v>
       </c>
       <c r="Q57" s="5" t="str">
-        <v>a</v>
+        <v>o</v>
       </c>
       <c r="R57" s="5">
         <f t="shared" si="4"/>
@@ -8963,62 +9002,62 @@
       </c>
       <c r="S57" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}t</v>
+        <v>@o${1}k</v>
       </c>
       <c r="T57" s="25"/>
       <c r="U57" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@at(\d)/@a${1}t/</v>
+        <v xml:space="preserve">    - xform/@ok(\d)/@o${1}k/</v>
       </c>
     </row>
     <row r="58" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A58" s="19">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>301</v>
+        <v>247</v>
       </c>
       <c r="J58" s="19"/>
       <c r="K58" s="23">
         <f>LEN(E58)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" s="24"/>
       <c r="M58" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ak</v>
+        <v>ong</v>
       </c>
       <c r="N58" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ak</v>
+        <v>ong</v>
       </c>
       <c r="P58" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ak(\d)</v>
+        <v>ong(\d)</v>
       </c>
       <c r="Q58" s="5" t="str">
-        <v>a</v>
+        <v>o</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="4"/>
@@ -9026,104 +9065,106 @@
       </c>
       <c r="S58" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}k</v>
+        <v>@o${1}ng</v>
       </c>
       <c r="T58" s="25"/>
       <c r="U58" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ak(\d)/@a${1}k/</v>
+        <v xml:space="preserve">    - xform/@ong(\d)/@o${1}ng/</v>
       </c>
     </row>
     <row r="59" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A59" s="19">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>302</v>
+        <v>98</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>303</v>
+        <v>99</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>303</v>
+        <v>100</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>303</v>
+        <v>99</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>303</v>
+        <v>101</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="I59" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="J59" s="19"/>
+        <v>103</v>
+      </c>
+      <c r="J59" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K59" s="23">
         <f>LEN(E59)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L59" s="24"/>
       <c r="M59" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ai</v>
+        <v>onnh</v>
       </c>
       <c r="N59" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ai</v>
+        <v>niuh</v>
       </c>
       <c r="P59" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ai(\d)</v>
+        <v>onnh(\d)</v>
       </c>
       <c r="Q59" s="5" t="str">
-        <v>a</v>
+        <v>i</v>
       </c>
       <c r="R59" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S59" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}i</v>
+        <v>n@i${1}uh</v>
       </c>
       <c r="T59" s="25"/>
       <c r="U59" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ai(\d)/@a${1}i/</v>
+        <v xml:space="preserve">    - xform/@onnh(\d)/n@i${1}uh/</v>
       </c>
     </row>
     <row r="60" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A60" s="19">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>306</v>
+        <v>348</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>307</v>
+        <v>349</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c r="I60" s="19" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="J60" s="19"/>
       <c r="K60" s="23">
@@ -9133,18 +9174,18 @@
       <c r="L60" s="24"/>
       <c r="M60" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>au</v>
+        <v>oo</v>
       </c>
       <c r="N60" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ao</v>
+        <v>oo</v>
       </c>
       <c r="P60" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>au(\d)</v>
+        <v>oo(\d)</v>
       </c>
       <c r="Q60" s="5" t="str">
-        <v>a</v>
+        <v>o</v>
       </c>
       <c r="R60" s="5">
         <f t="shared" si="4"/>
@@ -9152,62 +9193,62 @@
       </c>
       <c r="S60" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@a${1}o</v>
+        <v>@o${1}o</v>
       </c>
       <c r="T60" s="25"/>
       <c r="U60" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@au(\d)/@a${1}o/</v>
+        <v xml:space="preserve">    - xform/@oo(\d)/@o${1}o/</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A61" s="19">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="D61" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="H61" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="I61" s="19" t="s">
-        <v>313</v>
+        <v>235</v>
+      </c>
+      <c r="D61" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="E61" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="F61" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="G61" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="H61" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="I61" s="34" t="s">
+        <v>238</v>
       </c>
       <c r="J61" s="19"/>
       <c r="K61" s="23">
         <f>LEN(E61)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L61" s="24"/>
       <c r="M61" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>eh</v>
+        <v>ooh</v>
       </c>
       <c r="N61" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>eh</v>
+        <v>ooh</v>
       </c>
       <c r="P61" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>eh(\d)</v>
+        <v>ooh(\d)</v>
       </c>
       <c r="Q61" s="5" t="str">
-        <v>e</v>
+        <v>o</v>
       </c>
       <c r="R61" s="5">
         <f t="shared" si="4"/>
@@ -9215,62 +9256,62 @@
       </c>
       <c r="S61" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@e${1}h</v>
+        <v>@o${1}oh</v>
       </c>
       <c r="T61" s="25"/>
       <c r="U61" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@eh(\d)/@e${1}h/</v>
+        <v xml:space="preserve">    - xform/@ooh(\d)/@o${1}oh/</v>
       </c>
     </row>
     <row r="62" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A62" s="19">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>314</v>
+        <v>239</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>315</v>
+        <v>241</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="G62" s="22" t="s">
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>316</v>
+        <v>242</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>317</v>
+        <v>243</v>
       </c>
       <c r="J62" s="19"/>
       <c r="K62" s="23">
         <f>LEN(E62)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" s="24"/>
       <c r="M62" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ih</v>
+        <v>oom</v>
       </c>
       <c r="N62" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ih</v>
+        <v>om</v>
       </c>
       <c r="P62" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ih(\d)</v>
+        <v>oom(\d)</v>
       </c>
       <c r="Q62" s="5" t="str">
-        <v>i</v>
+        <v>o</v>
       </c>
       <c r="R62" s="5">
         <f t="shared" si="4"/>
@@ -9278,125 +9319,125 @@
       </c>
       <c r="S62" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@i${1}h</v>
+        <v>@o${1}m</v>
       </c>
       <c r="T62" s="25"/>
       <c r="U62" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ih(\d)/@i${1}h/</v>
+        <v xml:space="preserve">    - xform/@oom(\d)/@o${1}m/</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A63" s="19">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>318</v>
+        <v>149</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>318</v>
+        <v>150</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>318</v>
+        <v>150</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>318</v>
+        <v>151</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>318</v>
+        <v>152</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>318</v>
+        <v>153</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>319</v>
+        <v>154</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>320</v>
+        <v>155</v>
       </c>
       <c r="J63" s="19"/>
       <c r="K63" s="23">
         <f>LEN(E63)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L63" s="24"/>
       <c r="M63" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>im</v>
+        <v>oonn</v>
       </c>
       <c r="N63" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>im</v>
+        <v>noo</v>
       </c>
       <c r="P63" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>im(\d)</v>
+        <v>oonn(\d)</v>
       </c>
       <c r="Q63" s="5" t="str">
-        <v>i</v>
+        <v>o</v>
       </c>
       <c r="R63" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S63" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@i${1}m</v>
+        <v>n@o${1}o</v>
       </c>
       <c r="T63" s="25"/>
       <c r="U63" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@im(\d)/@i${1}m/</v>
+        <v xml:space="preserve">    - xform/@oonn(\d)/n@o${1}o/</v>
       </c>
     </row>
     <row r="64" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A64" s="19">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>321</v>
+        <v>248</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>321</v>
+        <v>250</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>322</v>
+        <v>251</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="J64" s="19"/>
       <c r="K64" s="23">
         <f>LEN(E64)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" s="24"/>
       <c r="M64" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>in</v>
+        <v>oop</v>
       </c>
       <c r="N64" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>in</v>
+        <v>op</v>
       </c>
       <c r="P64" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>in(\d)</v>
+        <v>oop(\d)</v>
       </c>
       <c r="Q64" s="5" t="str">
-        <v>i</v>
+        <v>o</v>
       </c>
       <c r="R64" s="5">
         <f t="shared" si="4"/>
@@ -9404,41 +9445,41 @@
       </c>
       <c r="S64" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@i${1}n</v>
+        <v>@o${1}p</v>
       </c>
       <c r="T64" s="25"/>
       <c r="U64" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@in(\d)/@i${1}n/</v>
+        <v xml:space="preserve">    - xform/@oop(\d)/@o${1}p/</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A65" s="19">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="H65" s="23" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="J65" s="19"/>
       <c r="K65" s="23">
@@ -9448,18 +9489,18 @@
       <c r="L65" s="24"/>
       <c r="M65" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ip</v>
+        <v>or</v>
       </c>
       <c r="N65" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>ip</v>
+        <v>o</v>
       </c>
       <c r="P65" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ip(\d)</v>
+        <v>or(\d)</v>
       </c>
       <c r="Q65" s="5" t="str">
-        <v>i</v>
+        <v>o</v>
       </c>
       <c r="R65" s="5">
         <f t="shared" si="4"/>
@@ -9467,62 +9508,62 @@
       </c>
       <c r="S65" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@i${1}p</v>
+        <v>@o${1}</v>
       </c>
       <c r="T65" s="25"/>
       <c r="U65" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ip(\d)/@i${1}p/</v>
+        <v xml:space="preserve">    - xform/@or(\d)/@o${1}/</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A66" s="19">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>328</v>
+        <v>229</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>329</v>
+        <v>230</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>329</v>
+        <v>230</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>329</v>
+        <v>231</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>329</v>
+        <v>230</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>329</v>
+        <v>230</v>
       </c>
       <c r="H66" s="23" t="s">
-        <v>330</v>
+        <v>232</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>331</v>
+        <v>233</v>
       </c>
       <c r="J66" s="19"/>
       <c r="K66" s="23">
         <f>LEN(E66)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" s="24"/>
       <c r="M66" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>it</v>
+        <v>orh</v>
       </c>
       <c r="N66" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>it</v>
+        <v>oh</v>
       </c>
       <c r="P66" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>it(\d)</v>
+        <v>orh(\d)</v>
       </c>
       <c r="Q66" s="5" t="str">
-        <v>i</v>
+        <v>o</v>
       </c>
       <c r="R66" s="5">
         <f t="shared" si="4"/>
@@ -9530,62 +9571,62 @@
       </c>
       <c r="S66" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@i${1}t</v>
+        <v>@o${1}h</v>
       </c>
       <c r="T66" s="25"/>
       <c r="U66" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@it(\d)/@i${1}t/</v>
+        <v xml:space="preserve">    - xform/@orh(\d)/@o${1}h/</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A67" s="19">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>332</v>
+        <v>43</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>333</v>
+        <v>43</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>333</v>
+        <v>43</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>333</v>
+        <v>43</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>333</v>
+        <v>43</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>334</v>
+        <v>43</v>
       </c>
       <c r="H67" s="23" t="s">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="J67" s="19"/>
       <c r="K67" s="23">
         <f>LEN(E67)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" s="24"/>
       <c r="M67" s="11" t="str">
         <f t="shared" ref="M67:N85" si="8">E67</f>
-        <v>ik</v>
+        <v>u</v>
       </c>
       <c r="N67" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ik</v>
+        <v>u</v>
       </c>
       <c r="P67" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ik(\d)</v>
+        <v>u(\d)</v>
       </c>
       <c r="Q67" s="5" t="str">
-        <v>i</v>
+        <v>u</v>
       </c>
       <c r="R67" s="5">
         <f t="shared" si="4"/>
@@ -9593,41 +9634,41 @@
       </c>
       <c r="S67" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>@i${1}k</v>
+        <v>@u${1}</v>
       </c>
       <c r="T67" s="25"/>
       <c r="U67" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ik(\d)/@i${1}k/</v>
+        <v xml:space="preserve">    - xform/@u(\d)/@u${1}/</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A68" s="19">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="H68" s="23" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="J68" s="19"/>
       <c r="K68" s="23">
@@ -9637,15 +9678,15 @@
       <c r="L68" s="24"/>
       <c r="M68" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ia</v>
+        <v>ua</v>
       </c>
       <c r="N68" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ia</v>
+        <v>ua</v>
       </c>
       <c r="P68" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>ia(\d)</v>
+        <v>ua(\d)</v>
       </c>
       <c r="Q68" s="5" t="str">
         <v>a</v>
@@ -9656,566 +9697,570 @@
       </c>
       <c r="S68" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>i@a${1}</v>
+        <v>u@a${1}</v>
       </c>
       <c r="T68" s="25"/>
       <c r="U68" s="26" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/@ia(\d)/i@a${1}/</v>
+        <v xml:space="preserve">    - xform/@ua(\d)/u@a${1}/</v>
       </c>
     </row>
     <row r="69" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A69" s="19">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>341</v>
+        <v>253</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>341</v>
+        <v>254</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>341</v>
+        <v>254</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>341</v>
+        <v>254</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>341</v>
+        <v>254</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>341</v>
+        <v>255</v>
       </c>
       <c r="H69" s="23" t="s">
-        <v>342</v>
+        <v>256</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>343</v>
+        <v>257</v>
       </c>
       <c r="J69" s="19"/>
       <c r="K69" s="23">
         <f>LEN(E69)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="24"/>
       <c r="M69" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>iu</v>
+        <v>uah</v>
       </c>
       <c r="N69" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>iu</v>
+        <v>uah</v>
       </c>
       <c r="P69" s="3" t="str">
         <f t="shared" ref="P69:P85" si="9">_xlfn.CONCAT(M69, "(\d)")</f>
-        <v>iu(\d)</v>
+        <v>uah(\d)</v>
       </c>
       <c r="Q69" s="5" t="str">
-        <v>i</v>
+        <v>a</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" ref="R69:R86" si="10">IFERROR( IF(Q69="", "", SEARCH(Q69, $N69)), "")</f>
-        <v>1</v>
+        <f t="shared" ref="R69:R85" si="10">IFERROR( IF(Q69="", "", SEARCH(Q69, $N69)), "")</f>
+        <v>2</v>
       </c>
       <c r="S69" s="3" t="str">
         <f t="shared" ref="S69:S85" si="11">IFERROR( _xlfn.CONCAT(LEFT(N69,R69-1), "@", MID(N69,R69,1), "${1}", RIGHT(N69, LEN(N69)-R69)), "" )</f>
-        <v>@i${1}u</v>
+        <v>u@a${1}h</v>
       </c>
       <c r="T69" s="25"/>
       <c r="U69" s="26" t="str">
         <f t="shared" ref="U69:U85" si="12">IF(AND(N69&lt;&gt;"", M69&lt;&gt;""), "    - xform/@" &amp; P69 &amp;  "/"  &amp; S69 &amp;  "/", "")</f>
-        <v xml:space="preserve">    - xform/@iu(\d)/@i${1}u/</v>
+        <v xml:space="preserve">    - xform/@uah(\d)/u@a${1}h/</v>
       </c>
     </row>
     <row r="70" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A70" s="19">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>344</v>
+        <v>267</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>58</v>
+        <v>267</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>58</v>
+        <v>267</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>58</v>
+        <v>267</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>58</v>
+        <v>268</v>
       </c>
       <c r="H70" s="23" t="s">
-        <v>346</v>
+        <v>269</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
       <c r="J70" s="19"/>
       <c r="K70" s="23">
         <f>LEN(E70)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" s="24"/>
       <c r="M70" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>or</v>
+        <v>uai</v>
       </c>
       <c r="N70" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>o</v>
+        <v>uai</v>
       </c>
       <c r="P70" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>or(\d)</v>
+        <v>uai(\d)</v>
       </c>
       <c r="Q70" s="5" t="str">
-        <v>o</v>
+        <v>a</v>
       </c>
       <c r="R70" s="5">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S70" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@o${1}</v>
+        <v>u@a${1}i</v>
       </c>
       <c r="T70" s="25"/>
       <c r="U70" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@or(\d)/@o${1}/</v>
+        <v xml:space="preserve">    - xform/@uai(\d)/u@a${1}i/</v>
       </c>
     </row>
     <row r="71" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A71" s="19">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>348</v>
+        <v>167</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>349</v>
+        <v>168</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>349</v>
+        <v>168</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>349</v>
+        <v>168</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>349</v>
+        <v>168</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>350</v>
+        <v>169</v>
       </c>
       <c r="H71" s="23" t="s">
-        <v>351</v>
+        <v>170</v>
       </c>
       <c r="I71" s="19" t="s">
-        <v>352</v>
+        <v>171</v>
       </c>
       <c r="J71" s="19"/>
       <c r="K71" s="23">
         <f>LEN(E71)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L71" s="24"/>
       <c r="M71" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>oo</v>
+        <v>uaih</v>
       </c>
       <c r="N71" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>oo</v>
+        <v>uaih</v>
       </c>
       <c r="P71" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>oo(\d)</v>
+        <v>uaih(\d)</v>
       </c>
       <c r="Q71" s="5" t="str">
-        <v>o</v>
+        <v>a</v>
       </c>
       <c r="R71" s="5">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S71" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@o${1}o</v>
+        <v>u@a${1}ih</v>
       </c>
       <c r="T71" s="25"/>
       <c r="U71" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@oo(\d)/@o${1}o/</v>
+        <v xml:space="preserve">    - xform/@uaih(\d)/u@a${1}ih/</v>
       </c>
     </row>
     <row r="72" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A72" s="19">
+        <v>71</v>
+      </c>
+      <c r="B72" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B72" s="20" t="s">
-        <v>353</v>
-      </c>
       <c r="C72" s="21" t="s">
-        <v>354</v>
+        <v>60</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>354</v>
+        <v>60</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>354</v>
+        <v>60</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>354</v>
+        <v>61</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>354</v>
+        <v>62</v>
       </c>
       <c r="H72" s="23" t="s">
-        <v>355</v>
+        <v>63</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="J72" s="19"/>
+        <v>64</v>
+      </c>
+      <c r="J72" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K72" s="23">
         <f>LEN(E72)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L72" s="24"/>
       <c r="M72" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ok</v>
+        <v>uainn</v>
       </c>
       <c r="N72" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ok</v>
+        <v>nuai</v>
       </c>
       <c r="P72" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>ok(\d)</v>
+        <v>uainn(\d)</v>
       </c>
       <c r="Q72" s="5" t="str">
-        <v>o</v>
+        <v>a</v>
       </c>
       <c r="R72" s="5">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S72" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@o${1}k</v>
+        <v>nu@a${1}i</v>
       </c>
       <c r="T72" s="25"/>
       <c r="U72" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@ok(\d)/@o${1}k/</v>
+        <v xml:space="preserve">    - xform/@uainn(\d)/nu@a${1}i/</v>
       </c>
     </row>
     <row r="73" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A73" s="19">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>358</v>
+        <v>22</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>358</v>
+        <v>23</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="F73" s="19" t="s">
-        <v>358</v>
+        <v>22</v>
+      </c>
+      <c r="F73" s="31" t="s">
+        <v>24</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>358</v>
+        <v>25</v>
       </c>
       <c r="H73" s="23" t="s">
-        <v>359</v>
+        <v>26</v>
       </c>
       <c r="I73" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="J73" s="19"/>
+        <v>27</v>
+      </c>
+      <c r="J73" s="29" t="s">
+        <v>28</v>
+      </c>
       <c r="K73" s="23">
         <f>LEN(E73)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L73" s="24"/>
       <c r="M73" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>uh</v>
+        <v>uainnh</v>
       </c>
       <c r="N73" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>uh</v>
+        <v>nuaih</v>
       </c>
       <c r="P73" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>uh(\d)</v>
+        <v>uainnh(\d)</v>
       </c>
       <c r="Q73" s="5" t="str">
-        <v>u</v>
+        <v>a</v>
       </c>
       <c r="R73" s="5">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S73" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@u${1}h</v>
+        <v>nu@a${1}ih</v>
       </c>
       <c r="T73" s="25"/>
       <c r="U73" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@uh(\d)/@u${1}h/</v>
+        <v xml:space="preserve">    - xform/@uainnh(\d)/nu@a${1}ih/</v>
       </c>
     </row>
     <row r="74" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A74" s="19">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>361</v>
+        <v>258</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>361</v>
+        <v>258</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>361</v>
+        <v>258</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>361</v>
+        <v>258</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>361</v>
+        <v>258</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>361</v>
+        <v>259</v>
       </c>
       <c r="H74" s="23" t="s">
-        <v>362</v>
+        <v>260</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>363</v>
+        <v>261</v>
       </c>
       <c r="J74" s="19"/>
       <c r="K74" s="23">
         <f>LEN(E74)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L74" s="24"/>
       <c r="M74" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>un</v>
+        <v>uan</v>
       </c>
       <c r="N74" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>un</v>
+        <v>uan</v>
       </c>
       <c r="P74" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>un(\d)</v>
+        <v>uan(\d)</v>
       </c>
       <c r="Q74" s="5" t="str">
-        <v>u</v>
+        <v>a</v>
       </c>
       <c r="R74" s="5">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S74" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@u${1}n</v>
+        <v>u@a${1}n</v>
       </c>
       <c r="T74" s="25"/>
       <c r="U74" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@un(\d)/@u${1}n/</v>
+        <v xml:space="preserve">    - xform/@uan(\d)/u@a${1}n/</v>
       </c>
     </row>
     <row r="75" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A75" s="19">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>364</v>
+        <v>162</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>365</v>
+        <v>163</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>365</v>
+        <v>163</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>365</v>
+        <v>163</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>365</v>
+        <v>163</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="H75" s="23" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
       <c r="I75" s="19" t="s">
-        <v>367</v>
+        <v>166</v>
       </c>
       <c r="J75" s="19"/>
       <c r="K75" s="23">
         <f>LEN(E75)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L75" s="24"/>
       <c r="M75" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ut</v>
+        <v>uang</v>
       </c>
       <c r="N75" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ut</v>
+        <v>uang</v>
       </c>
       <c r="P75" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>ut(\d)</v>
+        <v>uang(\d)</v>
       </c>
       <c r="Q75" s="5" t="str">
-        <v>u</v>
+        <v>a</v>
       </c>
       <c r="R75" s="5">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S75" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@u${1}t</v>
+        <v>u@a${1}ng</v>
       </c>
       <c r="T75" s="25"/>
       <c r="U75" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@ut(\d)/@u${1}t/</v>
+        <v xml:space="preserve">    - xform/@uang(\d)/u@a${1}ng/</v>
       </c>
     </row>
     <row r="76" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A76" s="19">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B76" s="20" t="s">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>368</v>
+        <v>157</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>368</v>
+        <v>157</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>368</v>
+        <v>157</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>368</v>
+        <v>158</v>
       </c>
       <c r="G76" s="22" t="s">
-        <v>369</v>
+        <v>159</v>
       </c>
       <c r="H76" s="23" t="s">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="I76" s="19" t="s">
-        <v>371</v>
+        <v>161</v>
       </c>
       <c r="J76" s="19"/>
       <c r="K76" s="23">
         <f>LEN(E76)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L76" s="24"/>
       <c r="M76" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ua</v>
+        <v>uann</v>
       </c>
       <c r="N76" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ua</v>
+        <v>nua</v>
       </c>
       <c r="P76" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>ua(\d)</v>
+        <v>uann(\d)</v>
       </c>
       <c r="Q76" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R76" s="5">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>u@a${1}</v>
+        <v>nu@a${1}</v>
       </c>
       <c r="T76" s="25"/>
       <c r="U76" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@ua(\d)/u@a${1}/</v>
+        <v xml:space="preserve">    - xform/@uann(\d)/nu@a${1}/</v>
       </c>
     </row>
     <row r="77" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A77" s="19">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>372</v>
+        <v>262</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>372</v>
+        <v>263</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>372</v>
+        <v>263</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>372</v>
+        <v>263</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>372</v>
+        <v>263</v>
       </c>
       <c r="G77" s="22" t="s">
-        <v>373</v>
+        <v>264</v>
       </c>
       <c r="H77" s="23" t="s">
-        <v>374</v>
+        <v>265</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>375</v>
+        <v>266</v>
       </c>
       <c r="J77" s="19"/>
       <c r="K77" s="23">
         <f>LEN(E77)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" s="24"/>
       <c r="M77" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ue</v>
+        <v>uat</v>
       </c>
       <c r="N77" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ue</v>
+        <v>uat</v>
       </c>
       <c r="P77" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>ue(\d)</v>
+        <v>uat(\d)</v>
       </c>
       <c r="Q77" s="5" t="str">
-        <v>e</v>
+        <v>a</v>
       </c>
       <c r="R77" s="5">
         <f t="shared" si="10"/>
@@ -10223,41 +10268,41 @@
       </c>
       <c r="S77" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>u@e${1}</v>
+        <v>u@a${1}t</v>
       </c>
       <c r="T77" s="25"/>
       <c r="U77" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@ue(\d)/u@e${1}/</v>
+        <v xml:space="preserve">    - xform/@uat(\d)/u@a${1}t/</v>
       </c>
     </row>
     <row r="78" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A78" s="19">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G78" s="22" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H78" s="23" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J78" s="19"/>
       <c r="K78" s="23">
@@ -10267,123 +10312,123 @@
       <c r="L78" s="24"/>
       <c r="M78" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ui</v>
+        <v>ue</v>
       </c>
       <c r="N78" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ui</v>
+        <v>ue</v>
       </c>
       <c r="P78" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>ui(\d)</v>
+        <v>ue(\d)</v>
       </c>
       <c r="Q78" s="5" t="str">
-        <v>u</v>
+        <v>e</v>
       </c>
       <c r="R78" s="5">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S78" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@u${1}i</v>
+        <v>u@e${1}</v>
       </c>
       <c r="T78" s="25"/>
       <c r="U78" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@ui(\d)/@u${1}i/</v>
+        <v xml:space="preserve">    - xform/@ue(\d)/u@e${1}/</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A79" s="19">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>379</v>
+        <v>271</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>380</v>
-      </c>
-      <c r="D79" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="E79" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="F79" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="G79" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="H79" s="35" t="s">
-        <v>381</v>
-      </c>
-      <c r="I79" s="34" t="s">
-        <v>382</v>
+        <v>272</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="G79" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="H79" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="I79" s="19" t="s">
+        <v>275</v>
       </c>
       <c r="J79" s="19"/>
       <c r="K79" s="23">
         <f>LEN(E79)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L79" s="24"/>
       <c r="M79" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>mh</v>
+        <v>ueh</v>
       </c>
       <c r="N79" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>mh</v>
+        <v>ueh</v>
       </c>
       <c r="P79" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>mh(\d)</v>
+        <v>ueh(\d)</v>
       </c>
       <c r="Q79" s="5" t="str">
-        <v>m</v>
+        <v>e</v>
       </c>
       <c r="R79" s="5">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S79" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@m${1}h</v>
+        <v>u@e${1}h</v>
       </c>
       <c r="T79" s="25"/>
       <c r="U79" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@mh(\d)/@m${1}h/</v>
+        <v xml:space="preserve">    - xform/@ueh(\d)/u@e${1}h/</v>
       </c>
     </row>
     <row r="80" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A80" s="19">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="G80" s="22" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="H80" s="23" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="J80" s="19"/>
       <c r="K80" s="23">
@@ -10393,18 +10438,18 @@
       <c r="L80" s="24"/>
       <c r="M80" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ng</v>
+        <v>uh</v>
       </c>
       <c r="N80" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>ng</v>
+        <v>uh</v>
       </c>
       <c r="P80" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>ng(\d)</v>
+        <v>uh(\d)</v>
       </c>
       <c r="Q80" s="5" t="str">
-        <v>n</v>
+        <v>u</v>
       </c>
       <c r="R80" s="5">
         <f t="shared" si="10"/>
@@ -10412,62 +10457,62 @@
       </c>
       <c r="S80" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@n${1}g</v>
+        <v>@u${1}h</v>
       </c>
       <c r="T80" s="25"/>
       <c r="U80" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@ng(\d)/@n${1}g/</v>
+        <v xml:space="preserve">    - xform/@uh(\d)/@u${1}h/</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A81" s="19">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>29</v>
+        <v>376</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>29</v>
+        <v>376</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>29</v>
+        <v>376</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>29</v>
+        <v>376</v>
       </c>
       <c r="F81" s="19" t="s">
-        <v>29</v>
+        <v>376</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>29</v>
+        <v>376</v>
       </c>
       <c r="H81" s="23" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="J81" s="19"/>
       <c r="K81" s="23">
         <f>LEN(E81)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="24"/>
       <c r="M81" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>a</v>
+        <v>ui</v>
       </c>
       <c r="N81" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>a</v>
+        <v>ui</v>
       </c>
       <c r="P81" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>a(\d)</v>
+        <v>ui(\d)</v>
       </c>
       <c r="Q81" s="5" t="str">
-        <v>a</v>
+        <v>u</v>
       </c>
       <c r="R81" s="5">
         <f t="shared" si="10"/>
@@ -10475,62 +10520,62 @@
       </c>
       <c r="S81" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@a${1}</v>
+        <v>@u${1}i</v>
       </c>
       <c r="T81" s="25"/>
       <c r="U81" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@a(\d)/@a${1}/</v>
+        <v xml:space="preserve">    - xform/@ui(\d)/@u${1}i/</v>
       </c>
     </row>
     <row r="82" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A82" s="19">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D82" s="19" t="s">
-        <v>389</v>
-      </c>
-      <c r="E82" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F82" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G82" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H82" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="I82" s="19" t="s">
-        <v>391</v>
-      </c>
-      <c r="J82" s="19"/>
+        <v>123</v>
+      </c>
+      <c r="D82" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E82" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F82" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G82" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H82" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="I82" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="J82" s="29"/>
       <c r="K82" s="23">
         <f>LEN(E82)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L82" s="24"/>
       <c r="M82" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>e</v>
+        <v>uih</v>
       </c>
       <c r="N82" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>e</v>
+        <v>uih</v>
       </c>
       <c r="P82" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>e(\d)</v>
+        <v>uih(\d)</v>
       </c>
       <c r="Q82" s="5" t="str">
-        <v>e</v>
+        <v>u</v>
       </c>
       <c r="R82" s="5">
         <f t="shared" si="10"/>
@@ -10538,122 +10583,122 @@
       </c>
       <c r="S82" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@e${1}</v>
+        <v>@u${1}ih</v>
       </c>
       <c r="T82" s="25"/>
       <c r="U82" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@e(\d)/@e${1}/</v>
+        <v xml:space="preserve">    - xform/@uih(\d)/@u${1}ih/</v>
       </c>
     </row>
     <row r="83" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A83" s="19">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>36</v>
+        <v>172</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>36</v>
+        <v>174</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="H83" s="23" t="s">
-        <v>392</v>
+        <v>176</v>
       </c>
       <c r="I83" s="19" t="s">
-        <v>393</v>
+        <v>177</v>
       </c>
       <c r="J83" s="19"/>
       <c r="K83" s="23">
         <f>LEN(E83)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L83" s="24"/>
       <c r="M83" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>i</v>
+        <v>uinn</v>
       </c>
       <c r="N83" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>i</v>
+        <v>nui</v>
       </c>
       <c r="P83" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>i(\d)</v>
+        <v>uinn(\d)</v>
       </c>
       <c r="Q83" s="5" t="str">
-        <v>i</v>
+        <v>u</v>
       </c>
       <c r="R83" s="5">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S83" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@i${1}</v>
+        <v>n@u${1}i</v>
       </c>
       <c r="T83" s="25"/>
       <c r="U83" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@i(\d)/@i${1}/</v>
+        <v xml:space="preserve">    - xform/@uinn(\d)/n@u${1}i/</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A84" s="19">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B84" s="20" t="s">
-        <v>43</v>
+        <v>361</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>43</v>
+        <v>361</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>43</v>
+        <v>361</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>43</v>
+        <v>361</v>
       </c>
       <c r="F84" s="19" t="s">
-        <v>43</v>
+        <v>361</v>
       </c>
       <c r="G84" s="22" t="s">
-        <v>43</v>
+        <v>361</v>
       </c>
       <c r="H84" s="23" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="J84" s="19"/>
       <c r="K84" s="23">
         <f>LEN(E84)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="24"/>
       <c r="M84" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>u</v>
+        <v>un</v>
       </c>
       <c r="N84" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>u</v>
+        <v>un</v>
       </c>
       <c r="P84" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>u(\d)</v>
+        <v>un(\d)</v>
       </c>
       <c r="Q84" s="5" t="str">
         <v>u</v>
@@ -10664,62 +10709,62 @@
       </c>
       <c r="S84" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@u${1}</v>
+        <v>@u${1}n</v>
       </c>
       <c r="T84" s="25"/>
       <c r="U84" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@u(\d)/@u${1}/</v>
+        <v xml:space="preserve">    - xform/@un(\d)/@u${1}n/</v>
       </c>
     </row>
     <row r="85" spans="1:21" ht="27.75" customHeight="1" thickBot="1">
       <c r="A85" s="19">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>65</v>
+        <v>365</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>65</v>
+        <v>365</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>65</v>
+        <v>365</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>65</v>
+        <v>365</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>65</v>
+        <v>365</v>
       </c>
       <c r="H85" s="23" t="s">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="J85" s="19"/>
       <c r="K85" s="23">
         <f>LEN(E85)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="24"/>
       <c r="M85" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>m</v>
+        <v>ut</v>
       </c>
       <c r="N85" s="11" t="str">
         <f t="shared" si="8"/>
-        <v>m</v>
+        <v>ut</v>
       </c>
       <c r="P85" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>m(\d)</v>
+        <v>ut(\d)</v>
       </c>
       <c r="Q85" s="5" t="str">
-        <v>m</v>
+        <v>u</v>
       </c>
       <c r="R85" s="5">
         <f t="shared" si="10"/>
@@ -10727,12 +10772,12 @@
       </c>
       <c r="S85" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>@m${1}</v>
+        <v>@u${1}t</v>
       </c>
       <c r="T85" s="25"/>
       <c r="U85" s="26" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    - xform/@m(\d)/@m${1}/</v>
+        <v xml:space="preserve">    - xform/@ut(\d)/@u${1}t/</v>
       </c>
     </row>
     <row r="86" spans="1:21" ht="27" customHeight="1" thickBot="1"/>
@@ -10820,13 +10865,12 @@
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="str">
         <f>"(""" &amp; _xlfn.TEXTJOIN(""",""",TRUE,F4:F85) &amp; """)"</f>
-        <v>("nuaih","niah","niao","nioo","niuh","nuai","nah","nai","neh","nia","niu","niuh","na","ne","ni","iang","iaoh","ioh","iong","iok","noo","nua","uang","uaih","nui","uih","ang","aih","aoh","ing","iah","iam","ian","iap","iat","iak","iao","io","oh","ooh","om","ong","op","uah","uan","uat","uai","ueh","ngh","ah","am","an","ap","at","ak","ai","ao","eh","ih","im","in","ip","it","ik","ia","iu","o","oo","ok","uh","un","ut","ua","ue","ui","mh","ng","a","e","i","u","m")</v>
+        <v>("a","ah","ai","aih","nai","ak","am","an","ang","na","nah","ap","at","ao","aoh","e","eh","ne","neh","i","ia","iah","iak","iam","ian","iang","nia","niah","iap","iat","iao","iaoh","niao","ih","ik","im","in","ing","ni","iong","iok","nioo","io","ioh","ip","it","iu","niu","niuh","m","mh","ng","ngh","ok","ong","niuh","oo","ooh","om","noo","op","o","oh","u","ua","uah","uai","uaih","nuai","nuaih","uan","uang","nua","uat","ue","ueh","uh","ui","uih","nui","un","ut")</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K85">
-    <sortCondition descending="1" ref="J4:J85"/>
-    <sortCondition descending="1" ref="K4:K85"/>
+    <sortCondition ref="E13:E85"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/103_RIME對照工具【台語注音二式】.xlsx
+++ b/docs/103_RIME對照工具【台語注音二式】.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF67B216-5A14-4C9C-A696-6AAC6E029705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54A46F4-70CA-4435-874B-D9DA266F5A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="聲調標置" sheetId="1" r:id="rId1"/>
     <sheet name="【聲】聲母對照表 (台語注音二式)" sheetId="2" r:id="rId2"/>
     <sheet name="【韻】韻母清單（台語注音二式==&gt;閩拼方案）" sheetId="8" r:id="rId3"/>
-    <sheet name="【韻】韻母清單（台語注音二式==&gt;閩拼方案）【右欄】" sheetId="4" r:id="rId4"/>
-    <sheet name="【韻】韻母清單 (台語注音二式)" sheetId="5" r:id="rId5"/>
-    <sheet name="【韻】韻母清單" sheetId="6" r:id="rId6"/>
-    <sheet name="【韻】韻母清單（拼音字母標聲調）" sheetId="7" r:id="rId7"/>
+    <sheet name="【韻】韻母清單（閩拼注音）【右欄】" sheetId="9" r:id="rId4"/>
+    <sheet name="【韻】韻母清單（台語注音二式==&gt;閩拼方案）【右欄】" sheetId="4" r:id="rId5"/>
+    <sheet name="【韻】韻母清單 (台語注音二式)" sheetId="5" r:id="rId6"/>
+    <sheet name="【韻】韻母清單" sheetId="6" r:id="rId7"/>
+    <sheet name="【韻】韻母清單（拼音字母標聲調）" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -106,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4353" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5062" uniqueCount="628">
   <si>
     <t>響度優先次第： a &gt; oo &gt; (e = o) &gt; (i = u)〈低元音 &gt; 高元音 &gt; 無擦通音 &gt; 擦音 &gt; 塞音〉</t>
   </si>
@@ -3007,6 +3008,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
@@ -5011,7 +5015,7 @@
       </c>
       <c r="J4" s="19"/>
       <c r="K4" s="23">
-        <f>LEN(E4)</f>
+        <f t="shared" ref="K4:K35" si="1">LEN(E4)</f>
         <v>1</v>
       </c>
       <c r="L4" s="24"/>
@@ -5048,83 +5052,83 @@
         <v>29</v>
       </c>
       <c r="X4" s="27" t="str">
-        <f t="shared" ref="X4:AG10" si="1">_xlfn.CONCAT($W4, IF(X$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(X$3,4)))))</f>
+        <f t="shared" ref="X4:AG10" si="2">_xlfn.CONCAT($W4, IF(X$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(X$3,4)))))</f>
         <v>a</v>
       </c>
       <c r="Y4" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>á</v>
       </c>
       <c r="Z4" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>à</v>
       </c>
       <c r="AA4" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>a</v>
       </c>
       <c r="AB4" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ǎ</v>
       </c>
       <c r="AC4" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>á</v>
       </c>
       <c r="AD4" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ā</v>
       </c>
       <c r="AE4" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>a̍</v>
       </c>
       <c r="AF4" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>a̋</v>
       </c>
       <c r="AG4" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>å</v>
       </c>
       <c r="AI4" s="28" t="str">
-        <f t="shared" ref="AI4:AR10" si="2">_xlfn.CONCAT("    - xform/》", $W4, X$2, "/", X4, "/")</f>
+        <f t="shared" ref="AI4:AR10" si="3">_xlfn.CONCAT("    - xform/》", $W4, X$2, "/", X4, "/")</f>
         <v xml:space="preserve">    - xform/》a1/a/</v>
       </c>
       <c r="AJ4" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》a2/á/</v>
       </c>
       <c r="AK4" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》a3/à/</v>
       </c>
       <c r="AL4" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》a4/a/</v>
       </c>
       <c r="AM4" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》a5/ǎ/</v>
       </c>
       <c r="AN4" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》a6/á/</v>
       </c>
       <c r="AO4" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》a7/ā/</v>
       </c>
       <c r="AP4" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》a8/a̍/</v>
       </c>
       <c r="AQ4" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》a9/a̋/</v>
       </c>
       <c r="AR4" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》a9/å/</v>
       </c>
       <c r="AS4" s="27"/>
@@ -5161,7 +5165,7 @@
       </c>
       <c r="J5" s="19"/>
       <c r="K5" s="23">
-        <f>LEN(E5)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L5" s="24"/>
@@ -5174,106 +5178,106 @@
         <v>ah</v>
       </c>
       <c r="P5" s="3" t="str">
-        <f t="shared" ref="P5:P68" si="3">_xlfn.CONCAT(M5, "(\d)")</f>
+        <f t="shared" ref="P5:P68" si="4">_xlfn.CONCAT(M5, "(\d)")</f>
         <v>ah(\d)</v>
       </c>
       <c r="Q5" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R5" s="5">
-        <f t="shared" ref="R5:R68" si="4">IFERROR( IF(Q5="", "", SEARCH(Q5, $N5)), "")</f>
+        <f t="shared" ref="R5:R68" si="5">IFERROR( IF(Q5="", "", SEARCH(Q5, $N5)), "")</f>
         <v>1</v>
       </c>
       <c r="S5" s="3" t="str">
-        <f t="shared" ref="S5:S68" si="5">IFERROR( _xlfn.CONCAT(LEFT(N5,R5-1), "@", MID(N5,R5,1), "${1}", RIGHT(N5, LEN(N5)-R5)), "" )</f>
+        <f t="shared" ref="S5:S68" si="6">IFERROR( _xlfn.CONCAT(LEFT(N5,R5-1), "@", MID(N5,R5,1), "${1}", RIGHT(N5, LEN(N5)-R5)), "" )</f>
         <v>@a${1}h</v>
       </c>
       <c r="T5" s="25"/>
       <c r="U5" s="26" t="str">
-        <f t="shared" ref="U5:U68" si="6">IF(AND(N5&lt;&gt;"", M5&lt;&gt;""), "    - xform/@" &amp; P5 &amp;  "/"  &amp; S5 &amp;  "/", "")</f>
+        <f t="shared" ref="U5:U68" si="7">IF(AND(N5&lt;&gt;"", M5&lt;&gt;""), "    - xform/@" &amp; P5 &amp;  "/"  &amp; S5 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/@ah(\d)/@a${1}h/</v>
       </c>
       <c r="W5" s="7" t="s">
         <v>36</v>
       </c>
       <c r="X5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>i</v>
       </c>
       <c r="Y5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>í</v>
       </c>
       <c r="Z5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ì</v>
       </c>
       <c r="AA5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>i</v>
       </c>
       <c r="AB5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ǐ</v>
       </c>
       <c r="AC5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>í</v>
       </c>
       <c r="AD5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ī</v>
       </c>
       <c r="AE5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>i̍</v>
       </c>
       <c r="AF5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>i̋</v>
       </c>
       <c r="AG5" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>i̊</v>
       </c>
       <c r="AI5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i1/i/</v>
       </c>
       <c r="AJ5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i2/í/</v>
       </c>
       <c r="AK5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i3/ì/</v>
       </c>
       <c r="AL5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i4/i/</v>
       </c>
       <c r="AM5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i5/ǐ/</v>
       </c>
       <c r="AN5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i6/í/</v>
       </c>
       <c r="AO5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i7/ī/</v>
       </c>
       <c r="AP5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i8/i̍/</v>
       </c>
       <c r="AQ5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i9/i̋/</v>
       </c>
       <c r="AR5" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》i9/i̊/</v>
       </c>
       <c r="AS5" s="27"/>
@@ -5310,7 +5314,7 @@
       </c>
       <c r="J6" s="19"/>
       <c r="K6" s="23">
-        <f>LEN(E6)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L6" s="24"/>
@@ -5323,106 +5327,106 @@
         <v>ai</v>
       </c>
       <c r="P6" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ai(\d)</v>
       </c>
       <c r="Q6" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R6" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S6" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}i</v>
       </c>
       <c r="T6" s="25"/>
       <c r="U6" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ai(\d)/@a${1}i/</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>43</v>
       </c>
       <c r="X6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>u</v>
       </c>
       <c r="Y6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ú</v>
       </c>
       <c r="Z6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ù</v>
       </c>
       <c r="AA6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>u</v>
       </c>
       <c r="AB6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ǔ</v>
       </c>
       <c r="AC6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ú</v>
       </c>
       <c r="AD6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ū</v>
       </c>
       <c r="AE6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>u̍</v>
       </c>
       <c r="AF6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ű</v>
       </c>
       <c r="AG6" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ů</v>
       </c>
       <c r="AI6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u1/u/</v>
       </c>
       <c r="AJ6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u2/ú/</v>
       </c>
       <c r="AK6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u3/ù/</v>
       </c>
       <c r="AL6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u4/u/</v>
       </c>
       <c r="AM6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u5/ǔ/</v>
       </c>
       <c r="AN6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u6/ú/</v>
       </c>
       <c r="AO6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u7/ū/</v>
       </c>
       <c r="AP6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u8/u̍/</v>
       </c>
       <c r="AQ6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u9/ű/</v>
       </c>
       <c r="AR6" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》u9/ů/</v>
       </c>
       <c r="AS6" s="27"/>
@@ -5459,7 +5463,7 @@
       </c>
       <c r="J7" s="19"/>
       <c r="K7" s="23">
-        <f>LEN(E7)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L7" s="24"/>
@@ -5472,106 +5476,106 @@
         <v>aih</v>
       </c>
       <c r="P7" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>aih(\d)</v>
       </c>
       <c r="Q7" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R7" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S7" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}ih</v>
       </c>
       <c r="T7" s="25"/>
       <c r="U7" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@aih(\d)/@a${1}ih/</v>
       </c>
       <c r="W7" s="7" t="s">
         <v>51</v>
       </c>
       <c r="X7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>e</v>
       </c>
       <c r="Y7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>é</v>
       </c>
       <c r="Z7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>è</v>
       </c>
       <c r="AA7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>e</v>
       </c>
       <c r="AB7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ě</v>
       </c>
       <c r="AC7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>é</v>
       </c>
       <c r="AD7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ē</v>
       </c>
       <c r="AE7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>e̍</v>
       </c>
       <c r="AF7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>e̋</v>
       </c>
       <c r="AG7" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>e̊</v>
       </c>
       <c r="AI7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e1/e/</v>
       </c>
       <c r="AJ7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e2/é/</v>
       </c>
       <c r="AK7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e3/è/</v>
       </c>
       <c r="AL7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e4/e/</v>
       </c>
       <c r="AM7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e5/ě/</v>
       </c>
       <c r="AN7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e6/é/</v>
       </c>
       <c r="AO7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e7/ē/</v>
       </c>
       <c r="AP7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e8/e̍/</v>
       </c>
       <c r="AQ7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e9/e̋/</v>
       </c>
       <c r="AR7" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》e9/e̊/</v>
       </c>
       <c r="AS7" s="27"/>
@@ -5610,7 +5614,7 @@
         <v>28</v>
       </c>
       <c r="K8" s="23">
-        <f>LEN(E8)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L8" s="24"/>
@@ -5623,106 +5627,106 @@
         <v>nai</v>
       </c>
       <c r="P8" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ainn(\d)</v>
       </c>
       <c r="Q8" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R8" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S8" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@a${1}i</v>
       </c>
       <c r="T8" s="25"/>
       <c r="U8" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ainn(\d)/n@a${1}i/</v>
       </c>
       <c r="W8" s="7" t="s">
         <v>58</v>
       </c>
       <c r="X8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>o</v>
       </c>
       <c r="Y8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ó</v>
       </c>
       <c r="Z8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ò</v>
       </c>
       <c r="AA8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>o</v>
       </c>
       <c r="AB8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ǒ</v>
       </c>
       <c r="AC8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ó</v>
       </c>
       <c r="AD8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ō</v>
       </c>
       <c r="AE8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>o̍</v>
       </c>
       <c r="AF8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ő</v>
       </c>
       <c r="AG8" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>o̊</v>
       </c>
       <c r="AI8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o1/o/</v>
       </c>
       <c r="AJ8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o2/ó/</v>
       </c>
       <c r="AK8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o3/ò/</v>
       </c>
       <c r="AL8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o4/o/</v>
       </c>
       <c r="AM8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o5/ǒ/</v>
       </c>
       <c r="AN8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o6/ó/</v>
       </c>
       <c r="AO8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o7/ō/</v>
       </c>
       <c r="AP8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o8/o̍/</v>
       </c>
       <c r="AQ8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o9/ő/</v>
       </c>
       <c r="AR8" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》o9/o̊/</v>
       </c>
       <c r="AS8" s="27"/>
@@ -5759,7 +5763,7 @@
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="23">
-        <f>LEN(E9)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L9" s="24"/>
@@ -5772,106 +5776,106 @@
         <v>ak</v>
       </c>
       <c r="P9" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ak(\d)</v>
       </c>
       <c r="Q9" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R9" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S9" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}k</v>
       </c>
       <c r="T9" s="25"/>
       <c r="U9" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ak(\d)/@a${1}k/</v>
       </c>
       <c r="W9" s="7" t="s">
         <v>65</v>
       </c>
       <c r="X9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="Y9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ḿ</v>
       </c>
       <c r="Z9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>m̀</v>
       </c>
       <c r="AA9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="AB9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>m̌</v>
       </c>
       <c r="AC9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ḿ</v>
       </c>
       <c r="AD9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>m̄</v>
       </c>
       <c r="AE9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>m̍</v>
       </c>
       <c r="AF9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>m̋</v>
       </c>
       <c r="AG9" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>m̊</v>
       </c>
       <c r="AI9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m1/m/</v>
       </c>
       <c r="AJ9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m2/ḿ/</v>
       </c>
       <c r="AK9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m3/m̀/</v>
       </c>
       <c r="AL9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m4/m/</v>
       </c>
       <c r="AM9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m5/m̌/</v>
       </c>
       <c r="AN9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m6/ḿ/</v>
       </c>
       <c r="AO9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m7/m̄/</v>
       </c>
       <c r="AP9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m8/m̍/</v>
       </c>
       <c r="AQ9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m9/m̋/</v>
       </c>
       <c r="AR9" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》m9/m̊/</v>
       </c>
       <c r="AS9" s="27"/>
@@ -5908,7 +5912,7 @@
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="23">
-        <f>LEN(E10)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L10" s="24"/>
@@ -5921,106 +5925,106 @@
         <v>am</v>
       </c>
       <c r="P10" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>am(\d)</v>
       </c>
       <c r="Q10" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S10" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}m</v>
       </c>
       <c r="T10" s="25"/>
       <c r="U10" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@am(\d)/@a${1}m/</v>
       </c>
       <c r="W10" s="7" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>n</v>
       </c>
       <c r="Y10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ń</v>
       </c>
       <c r="Z10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ǹ</v>
       </c>
       <c r="AA10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>n</v>
       </c>
       <c r="AB10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ň</v>
       </c>
       <c r="AC10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ń</v>
       </c>
       <c r="AD10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>n̄</v>
       </c>
       <c r="AE10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>n̍</v>
       </c>
       <c r="AF10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>n̋</v>
       </c>
       <c r="AG10" s="27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>n̊</v>
       </c>
       <c r="AI10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n1/n/</v>
       </c>
       <c r="AJ10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n2/ń/</v>
       </c>
       <c r="AK10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n3/ǹ/</v>
       </c>
       <c r="AL10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n4/n/</v>
       </c>
       <c r="AM10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n5/ň/</v>
       </c>
       <c r="AN10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n6/ń/</v>
       </c>
       <c r="AO10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n7/n̄/</v>
       </c>
       <c r="AP10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n8/n̍/</v>
       </c>
       <c r="AQ10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n9/n̋/</v>
       </c>
       <c r="AR10" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    - xform/》n9/n̊/</v>
       </c>
       <c r="AS10" s="27"/>
@@ -6057,7 +6061,7 @@
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="23">
-        <f>LEN(E11)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L11" s="24"/>
@@ -6070,23 +6074,23 @@
         <v>an</v>
       </c>
       <c r="P11" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>an(\d)</v>
       </c>
       <c r="Q11" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S11" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}n</v>
       </c>
       <c r="T11" s="25"/>
       <c r="U11" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@an(\d)/@a${1}n/</v>
       </c>
     </row>
@@ -6120,7 +6124,7 @@
       </c>
       <c r="J12" s="19"/>
       <c r="K12" s="23">
-        <f>LEN(E12)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L12" s="24"/>
@@ -6133,23 +6137,23 @@
         <v>ang</v>
       </c>
       <c r="P12" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ang(\d)</v>
       </c>
       <c r="Q12" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R12" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S12" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}ng</v>
       </c>
       <c r="T12" s="25"/>
       <c r="U12" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ang(\d)/@a${1}ng/</v>
       </c>
     </row>
@@ -6185,7 +6189,7 @@
         <v>28</v>
       </c>
       <c r="K13" s="23">
-        <f>LEN(E13)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L13" s="24"/>
@@ -6198,23 +6202,23 @@
         <v>na</v>
       </c>
       <c r="P13" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ann(\d)</v>
       </c>
       <c r="Q13" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R13" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S13" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@a${1}</v>
       </c>
       <c r="T13" s="25"/>
       <c r="U13" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ann(\d)/n@a${1}/</v>
       </c>
     </row>
@@ -6250,7 +6254,7 @@
         <v>28</v>
       </c>
       <c r="K14" s="23">
-        <f>LEN(E14)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L14" s="24"/>
@@ -6263,23 +6267,23 @@
         <v>nah</v>
       </c>
       <c r="P14" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>annh(\d)</v>
       </c>
       <c r="Q14" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R14" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S14" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@a${1}h</v>
       </c>
       <c r="T14" s="25"/>
       <c r="U14" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@annh(\d)/n@a${1}h/</v>
       </c>
     </row>
@@ -6313,7 +6317,7 @@
       </c>
       <c r="J15" s="19"/>
       <c r="K15" s="23">
-        <f>LEN(E15)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L15" s="24"/>
@@ -6326,23 +6330,23 @@
         <v>ap</v>
       </c>
       <c r="P15" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ap(\d)</v>
       </c>
       <c r="Q15" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S15" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}p</v>
       </c>
       <c r="T15" s="25"/>
       <c r="U15" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ap(\d)/@a${1}p/</v>
       </c>
     </row>
@@ -6376,7 +6380,7 @@
       </c>
       <c r="J16" s="19"/>
       <c r="K16" s="23">
-        <f>LEN(E16)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L16" s="24"/>
@@ -6389,23 +6393,23 @@
         <v>at</v>
       </c>
       <c r="P16" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>at(\d)</v>
       </c>
       <c r="Q16" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S16" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}t</v>
       </c>
       <c r="T16" s="25"/>
       <c r="U16" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@at(\d)/@a${1}t/</v>
       </c>
     </row>
@@ -6439,7 +6443,7 @@
       </c>
       <c r="J17" s="19"/>
       <c r="K17" s="23">
-        <f>LEN(E17)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L17" s="24"/>
@@ -6452,23 +6456,23 @@
         <v>ao</v>
       </c>
       <c r="P17" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>au(\d)</v>
       </c>
       <c r="Q17" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R17" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S17" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}o</v>
       </c>
       <c r="T17" s="25"/>
       <c r="U17" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@au(\d)/@a${1}o/</v>
       </c>
     </row>
@@ -6502,7 +6506,7 @@
       </c>
       <c r="J18" s="19"/>
       <c r="K18" s="23">
-        <f>LEN(E18)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L18" s="24"/>
@@ -6515,23 +6519,23 @@
         <v>aoh</v>
       </c>
       <c r="P18" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>auh(\d)</v>
       </c>
       <c r="Q18" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R18" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S18" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@a${1}oh</v>
       </c>
       <c r="T18" s="25"/>
       <c r="U18" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@auh(\d)/@a${1}oh/</v>
       </c>
     </row>
@@ -6565,7 +6569,7 @@
       </c>
       <c r="J19" s="19"/>
       <c r="K19" s="23">
-        <f>LEN(E19)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L19" s="24"/>
@@ -6578,23 +6582,23 @@
         <v>e</v>
       </c>
       <c r="P19" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>e(\d)</v>
       </c>
       <c r="Q19" s="5" t="str">
         <v>e</v>
       </c>
       <c r="R19" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S19" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@e${1}</v>
       </c>
       <c r="T19" s="25"/>
       <c r="U19" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@e(\d)/@e${1}/</v>
       </c>
     </row>
@@ -6628,7 +6632,7 @@
       </c>
       <c r="J20" s="19"/>
       <c r="K20" s="23">
-        <f>LEN(E20)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L20" s="24"/>
@@ -6641,23 +6645,23 @@
         <v>eh</v>
       </c>
       <c r="P20" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>eh(\d)</v>
       </c>
       <c r="Q20" s="5" t="str">
         <v>e</v>
       </c>
       <c r="R20" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S20" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@e${1}h</v>
       </c>
       <c r="T20" s="25"/>
       <c r="U20" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@eh(\d)/@e${1}h/</v>
       </c>
     </row>
@@ -6693,7 +6697,7 @@
         <v>28</v>
       </c>
       <c r="K21" s="23">
-        <f>LEN(E21)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L21" s="24"/>
@@ -6706,23 +6710,23 @@
         <v>ne</v>
       </c>
       <c r="P21" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enn(\d)</v>
       </c>
       <c r="Q21" s="5" t="str">
         <v>e</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S21" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@e${1}</v>
       </c>
       <c r="T21" s="25"/>
       <c r="U21" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@enn(\d)/n@e${1}/</v>
       </c>
     </row>
@@ -6758,7 +6762,7 @@
         <v>28</v>
       </c>
       <c r="K22" s="23">
-        <f>LEN(E22)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L22" s="24"/>
@@ -6771,23 +6775,23 @@
         <v>neh</v>
       </c>
       <c r="P22" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ennh(\d)</v>
       </c>
       <c r="Q22" s="5" t="str">
         <v>e</v>
       </c>
       <c r="R22" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S22" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@e${1}h</v>
       </c>
       <c r="T22" s="25"/>
       <c r="U22" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ennh(\d)/n@e${1}h/</v>
       </c>
     </row>
@@ -6821,7 +6825,7 @@
       </c>
       <c r="J23" s="19"/>
       <c r="K23" s="23">
-        <f>LEN(E23)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L23" s="24"/>
@@ -6834,23 +6838,23 @@
         <v>i</v>
       </c>
       <c r="P23" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>i(\d)</v>
       </c>
       <c r="Q23" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R23" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S23" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@i${1}</v>
       </c>
       <c r="T23" s="25"/>
       <c r="U23" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@i(\d)/@i${1}/</v>
       </c>
     </row>
@@ -6884,7 +6888,7 @@
       </c>
       <c r="J24" s="19"/>
       <c r="K24" s="23">
-        <f>LEN(E24)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L24" s="24"/>
@@ -6897,23 +6901,23 @@
         <v>ia</v>
       </c>
       <c r="P24" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ia(\d)</v>
       </c>
       <c r="Q24" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R24" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S24" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}</v>
       </c>
       <c r="T24" s="25"/>
       <c r="U24" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ia(\d)/i@a${1}/</v>
       </c>
     </row>
@@ -6947,7 +6951,7 @@
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="23">
-        <f>LEN(E25)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L25" s="24"/>
@@ -6960,23 +6964,23 @@
         <v>iah</v>
       </c>
       <c r="P25" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iah(\d)</v>
       </c>
       <c r="Q25" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S25" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}h</v>
       </c>
       <c r="T25" s="25"/>
       <c r="U25" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iah(\d)/i@a${1}h/</v>
       </c>
     </row>
@@ -7010,7 +7014,7 @@
       </c>
       <c r="J26" s="19"/>
       <c r="K26" s="23">
-        <f>LEN(E26)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L26" s="24"/>
@@ -7023,23 +7027,23 @@
         <v>iak</v>
       </c>
       <c r="P26" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iak(\d)</v>
       </c>
       <c r="Q26" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R26" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S26" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}k</v>
       </c>
       <c r="T26" s="25"/>
       <c r="U26" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iak(\d)/i@a${1}k/</v>
       </c>
     </row>
@@ -7073,7 +7077,7 @@
       </c>
       <c r="J27" s="19"/>
       <c r="K27" s="23">
-        <f>LEN(E27)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L27" s="24"/>
@@ -7086,23 +7090,23 @@
         <v>iam</v>
       </c>
       <c r="P27" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iam(\d)</v>
       </c>
       <c r="Q27" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R27" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S27" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}m</v>
       </c>
       <c r="T27" s="25"/>
       <c r="U27" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iam(\d)/i@a${1}m/</v>
       </c>
     </row>
@@ -7136,7 +7140,7 @@
       </c>
       <c r="J28" s="19"/>
       <c r="K28" s="23">
-        <f>LEN(E28)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L28" s="24"/>
@@ -7149,23 +7153,23 @@
         <v>ian</v>
       </c>
       <c r="P28" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ian(\d)</v>
       </c>
       <c r="Q28" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R28" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S28" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}n</v>
       </c>
       <c r="T28" s="25"/>
       <c r="U28" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ian(\d)/i@a${1}n/</v>
       </c>
     </row>
@@ -7199,7 +7203,7 @@
       </c>
       <c r="J29" s="19"/>
       <c r="K29" s="23">
-        <f>LEN(E29)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L29" s="24"/>
@@ -7212,23 +7216,23 @@
         <v>iang</v>
       </c>
       <c r="P29" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iang(\d)</v>
       </c>
       <c r="Q29" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R29" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S29" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}ng</v>
       </c>
       <c r="T29" s="25"/>
       <c r="U29" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iang(\d)/i@a${1}ng/</v>
       </c>
     </row>
@@ -7264,7 +7268,7 @@
         <v>28</v>
       </c>
       <c r="K30" s="23">
-        <f>LEN(E30)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L30" s="24"/>
@@ -7277,23 +7281,23 @@
         <v>nia</v>
       </c>
       <c r="P30" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iann(\d)</v>
       </c>
       <c r="Q30" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R30" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S30" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ni@a${1}</v>
       </c>
       <c r="T30" s="25"/>
       <c r="U30" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iann(\d)/ni@a${1}/</v>
       </c>
     </row>
@@ -7329,7 +7333,7 @@
         <v>28</v>
       </c>
       <c r="K31" s="23">
-        <f>LEN(E31)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="L31" s="24"/>
@@ -7342,23 +7346,23 @@
         <v>niah</v>
       </c>
       <c r="P31" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iannh(\d)</v>
       </c>
       <c r="Q31" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S31" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ni@a${1}h</v>
       </c>
       <c r="T31" s="25"/>
       <c r="U31" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iannh(\d)/ni@a${1}h/</v>
       </c>
     </row>
@@ -7392,7 +7396,7 @@
       </c>
       <c r="J32" s="19"/>
       <c r="K32" s="23">
-        <f>LEN(E32)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L32" s="24"/>
@@ -7405,23 +7409,23 @@
         <v>iap</v>
       </c>
       <c r="P32" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iap(\d)</v>
       </c>
       <c r="Q32" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R32" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S32" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}p</v>
       </c>
       <c r="T32" s="25"/>
       <c r="U32" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iap(\d)/i@a${1}p/</v>
       </c>
     </row>
@@ -7455,7 +7459,7 @@
       </c>
       <c r="J33" s="19"/>
       <c r="K33" s="23">
-        <f>LEN(E33)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L33" s="24"/>
@@ -7468,23 +7472,23 @@
         <v>iat</v>
       </c>
       <c r="P33" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iat(\d)</v>
       </c>
       <c r="Q33" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R33" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S33" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}t</v>
       </c>
       <c r="T33" s="25"/>
       <c r="U33" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iat(\d)/i@a${1}t/</v>
       </c>
     </row>
@@ -7518,7 +7522,7 @@
       </c>
       <c r="J34" s="19"/>
       <c r="K34" s="23">
-        <f>LEN(E34)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L34" s="24"/>
@@ -7531,23 +7535,23 @@
         <v>iao</v>
       </c>
       <c r="P34" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iau(\d)</v>
       </c>
       <c r="Q34" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S34" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}o</v>
       </c>
       <c r="T34" s="25"/>
       <c r="U34" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iau(\d)/i@a${1}o/</v>
       </c>
     </row>
@@ -7581,36 +7585,36 @@
       </c>
       <c r="J35" s="19"/>
       <c r="K35" s="23">
-        <f>LEN(E35)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L35" s="24"/>
       <c r="M35" s="11" t="str">
-        <f t="shared" ref="M35:N66" si="7">E35</f>
+        <f t="shared" ref="M35:N66" si="8">E35</f>
         <v>iauh</v>
       </c>
       <c r="N35" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iaoh</v>
       </c>
       <c r="P35" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iauh(\d)</v>
       </c>
       <c r="Q35" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R35" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S35" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@a${1}oh</v>
       </c>
       <c r="T35" s="25"/>
       <c r="U35" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iauh(\d)/i@a${1}oh/</v>
       </c>
     </row>
@@ -7646,36 +7650,36 @@
         <v>28</v>
       </c>
       <c r="K36" s="23">
-        <f>LEN(E36)</f>
+        <f t="shared" ref="K36:K67" si="9">LEN(E36)</f>
         <v>5</v>
       </c>
       <c r="L36" s="24"/>
       <c r="M36" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iaunn</v>
       </c>
       <c r="N36" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>niao</v>
       </c>
       <c r="P36" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iaunn(\d)</v>
       </c>
       <c r="Q36" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R36" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S36" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ni@a${1}o</v>
       </c>
       <c r="T36" s="25"/>
       <c r="U36" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iaunn(\d)/ni@a${1}o/</v>
       </c>
     </row>
@@ -7709,36 +7713,36 @@
       </c>
       <c r="J37" s="19"/>
       <c r="K37" s="23">
-        <f>LEN(E37)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L37" s="24"/>
       <c r="M37" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ih</v>
       </c>
       <c r="N37" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ih</v>
       </c>
       <c r="P37" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ih(\d)</v>
       </c>
       <c r="Q37" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S37" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@i${1}h</v>
       </c>
       <c r="T37" s="25"/>
       <c r="U37" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ih(\d)/@i${1}h/</v>
       </c>
     </row>
@@ -7772,36 +7776,36 @@
       </c>
       <c r="J38" s="19"/>
       <c r="K38" s="23">
-        <f>LEN(E38)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L38" s="24"/>
       <c r="M38" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ik</v>
       </c>
       <c r="N38" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ik</v>
       </c>
       <c r="P38" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ik(\d)</v>
       </c>
       <c r="Q38" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S38" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@i${1}k</v>
       </c>
       <c r="T38" s="25"/>
       <c r="U38" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ik(\d)/@i${1}k/</v>
       </c>
     </row>
@@ -7835,36 +7839,36 @@
       </c>
       <c r="J39" s="19"/>
       <c r="K39" s="23">
-        <f>LEN(E39)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L39" s="24"/>
       <c r="M39" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>im</v>
       </c>
       <c r="N39" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>im</v>
       </c>
       <c r="P39" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>im(\d)</v>
       </c>
       <c r="Q39" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S39" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@i${1}m</v>
       </c>
       <c r="T39" s="25"/>
       <c r="U39" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@im(\d)/@i${1}m/</v>
       </c>
     </row>
@@ -7898,36 +7902,36 @@
       </c>
       <c r="J40" s="19"/>
       <c r="K40" s="23">
-        <f>LEN(E40)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L40" s="24"/>
       <c r="M40" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>in</v>
       </c>
       <c r="N40" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>in</v>
       </c>
       <c r="P40" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>in(\d)</v>
       </c>
       <c r="Q40" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R40" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S40" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@i${1}n</v>
       </c>
       <c r="T40" s="25"/>
       <c r="U40" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@in(\d)/@i${1}n/</v>
       </c>
     </row>
@@ -7961,36 +7965,36 @@
       </c>
       <c r="J41" s="19"/>
       <c r="K41" s="23">
-        <f>LEN(E41)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L41" s="24"/>
       <c r="M41" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ing</v>
       </c>
       <c r="N41" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ing</v>
       </c>
       <c r="P41" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ing(\d)</v>
       </c>
       <c r="Q41" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R41" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S41" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@i${1}ng</v>
       </c>
       <c r="T41" s="25"/>
       <c r="U41" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ing(\d)/@i${1}ng/</v>
       </c>
     </row>
@@ -8026,36 +8030,36 @@
         <v>28</v>
       </c>
       <c r="K42" s="23">
-        <f>LEN(E42)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L42" s="24"/>
       <c r="M42" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>inn</v>
       </c>
       <c r="N42" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ni</v>
       </c>
       <c r="P42" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>inn(\d)</v>
       </c>
       <c r="Q42" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R42" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S42" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@i${1}</v>
       </c>
       <c r="T42" s="25"/>
       <c r="U42" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@inn(\d)/n@i${1}/</v>
       </c>
     </row>
@@ -8089,36 +8093,36 @@
       </c>
       <c r="J43" s="19"/>
       <c r="K43" s="23">
-        <f>LEN(E43)</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="L43" s="24"/>
       <c r="M43" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iong</v>
       </c>
       <c r="N43" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iong</v>
       </c>
       <c r="P43" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iong(\d)</v>
       </c>
       <c r="Q43" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R43" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S43" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@o${1}ng</v>
       </c>
       <c r="T43" s="25"/>
       <c r="U43" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iong(\d)/i@o${1}ng/</v>
       </c>
     </row>
@@ -8152,36 +8156,36 @@
       </c>
       <c r="J44" s="19"/>
       <c r="K44" s="23">
-        <f>LEN(E44)</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="L44" s="24"/>
       <c r="M44" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iook</v>
       </c>
       <c r="N44" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iok</v>
       </c>
       <c r="P44" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iook(\d)</v>
       </c>
       <c r="Q44" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R44" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S44" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@o${1}k</v>
       </c>
       <c r="T44" s="25"/>
       <c r="U44" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iook(\d)/i@o${1}k/</v>
       </c>
     </row>
@@ -8217,36 +8221,36 @@
         <v>28</v>
       </c>
       <c r="K45" s="23">
-        <f>LEN(E45)</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="L45" s="24"/>
       <c r="M45" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ioonn</v>
       </c>
       <c r="N45" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>nioo</v>
       </c>
       <c r="P45" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ioonn(\d)</v>
       </c>
       <c r="Q45" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R45" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S45" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ni@o${1}o</v>
       </c>
       <c r="T45" s="25"/>
       <c r="U45" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ioonn(\d)/ni@o${1}o/</v>
       </c>
     </row>
@@ -8280,36 +8284,36 @@
       </c>
       <c r="J46" s="19"/>
       <c r="K46" s="23">
-        <f>LEN(E46)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L46" s="24"/>
       <c r="M46" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ior</v>
       </c>
       <c r="N46" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>io</v>
       </c>
       <c r="P46" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ior(\d)</v>
       </c>
       <c r="Q46" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R46" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S46" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@o${1}</v>
       </c>
       <c r="T46" s="25"/>
       <c r="U46" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ior(\d)/i@o${1}/</v>
       </c>
     </row>
@@ -8343,36 +8347,36 @@
       </c>
       <c r="J47" s="19"/>
       <c r="K47" s="23">
-        <f>LEN(E47)</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="L47" s="24"/>
       <c r="M47" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iorh</v>
       </c>
       <c r="N47" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ioh</v>
       </c>
       <c r="P47" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iorh(\d)</v>
       </c>
       <c r="Q47" s="49" t="str">
         <v>o</v>
       </c>
       <c r="R47" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S47" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i@o${1}h</v>
       </c>
       <c r="T47" s="25"/>
       <c r="U47" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iorh(\d)/i@o${1}h/</v>
       </c>
     </row>
@@ -8406,36 +8410,36 @@
       </c>
       <c r="J48" s="19"/>
       <c r="K48" s="23">
-        <f>LEN(E48)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L48" s="24"/>
       <c r="M48" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ip</v>
       </c>
       <c r="N48" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ip</v>
       </c>
       <c r="P48" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ip(\d)</v>
       </c>
       <c r="Q48" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R48" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S48" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@i${1}p</v>
       </c>
       <c r="T48" s="25"/>
       <c r="U48" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ip(\d)/@i${1}p/</v>
       </c>
     </row>
@@ -8469,36 +8473,36 @@
       </c>
       <c r="J49" s="19"/>
       <c r="K49" s="23">
-        <f>LEN(E49)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L49" s="24"/>
       <c r="M49" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>it</v>
       </c>
       <c r="N49" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>it</v>
       </c>
       <c r="P49" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>it(\d)</v>
       </c>
       <c r="Q49" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R49" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S49" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@i${1}t</v>
       </c>
       <c r="T49" s="25"/>
       <c r="U49" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@it(\d)/@i${1}t/</v>
       </c>
     </row>
@@ -8532,36 +8536,36 @@
       </c>
       <c r="J50" s="19"/>
       <c r="K50" s="23">
-        <f>LEN(E50)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L50" s="24"/>
       <c r="M50" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iu</v>
       </c>
       <c r="N50" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iu</v>
       </c>
       <c r="P50" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iu(\d)</v>
       </c>
       <c r="Q50" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R50" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S50" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@i${1}u</v>
       </c>
       <c r="T50" s="25"/>
       <c r="U50" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iu(\d)/@i${1}u/</v>
       </c>
     </row>
@@ -8597,36 +8601,36 @@
         <v>28</v>
       </c>
       <c r="K51" s="23">
-        <f>LEN(E51)</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="L51" s="24"/>
       <c r="M51" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iunn</v>
       </c>
       <c r="N51" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>niu</v>
       </c>
       <c r="P51" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iunn(\d)</v>
       </c>
       <c r="Q51" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R51" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S51" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@i${1}u</v>
       </c>
       <c r="T51" s="25"/>
       <c r="U51" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iunn(\d)/n@i${1}u/</v>
       </c>
     </row>
@@ -8662,36 +8666,36 @@
         <v>28</v>
       </c>
       <c r="K52" s="23">
-        <f>LEN(E52)</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="L52" s="24"/>
       <c r="M52" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>iunnh</v>
       </c>
       <c r="N52" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>niuh</v>
       </c>
       <c r="P52" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>iunnh(\d)</v>
       </c>
       <c r="Q52" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R52" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S52" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@i${1}uh</v>
       </c>
       <c r="T52" s="25"/>
       <c r="U52" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@iunnh(\d)/n@i${1}uh/</v>
       </c>
     </row>
@@ -8725,36 +8729,36 @@
       </c>
       <c r="J53" s="19"/>
       <c r="K53" s="23">
-        <f>LEN(E53)</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L53" s="24"/>
       <c r="M53" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>m</v>
       </c>
       <c r="N53" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>m</v>
       </c>
       <c r="P53" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>m(\d)</v>
       </c>
       <c r="Q53" s="5" t="str">
         <v>m</v>
       </c>
       <c r="R53" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S53" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@m${1}</v>
       </c>
       <c r="T53" s="25"/>
       <c r="U53" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@m(\d)/@m${1}/</v>
       </c>
     </row>
@@ -8788,36 +8792,36 @@
       </c>
       <c r="J54" s="19"/>
       <c r="K54" s="23">
-        <f>LEN(E54)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L54" s="24"/>
       <c r="M54" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>mh</v>
       </c>
       <c r="N54" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>mh</v>
       </c>
       <c r="P54" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>mh(\d)</v>
       </c>
       <c r="Q54" s="5" t="str">
         <v>m</v>
       </c>
       <c r="R54" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S54" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@m${1}h</v>
       </c>
       <c r="T54" s="25"/>
       <c r="U54" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@mh(\d)/@m${1}h/</v>
       </c>
     </row>
@@ -8851,36 +8855,36 @@
       </c>
       <c r="J55" s="19"/>
       <c r="K55" s="23">
-        <f>LEN(E55)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L55" s="24"/>
       <c r="M55" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ng</v>
       </c>
       <c r="N55" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ng</v>
       </c>
       <c r="P55" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ng(\d)</v>
       </c>
       <c r="Q55" s="5" t="str">
         <v>n</v>
       </c>
       <c r="R55" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S55" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@n${1}g</v>
       </c>
       <c r="T55" s="25"/>
       <c r="U55" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ng(\d)/@n${1}g/</v>
       </c>
     </row>
@@ -8914,36 +8918,36 @@
       </c>
       <c r="J56" s="19"/>
       <c r="K56" s="23">
-        <f>LEN(E56)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L56" s="24"/>
       <c r="M56" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ngh</v>
       </c>
       <c r="N56" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ngh</v>
       </c>
       <c r="P56" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ngh(\d)</v>
       </c>
       <c r="Q56" s="5" t="str">
         <v>n</v>
       </c>
       <c r="R56" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S56" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@n${1}gh</v>
       </c>
       <c r="T56" s="25"/>
       <c r="U56" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ngh(\d)/@n${1}gh/</v>
       </c>
     </row>
@@ -8977,36 +8981,36 @@
       </c>
       <c r="J57" s="19"/>
       <c r="K57" s="23">
-        <f>LEN(E57)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L57" s="24"/>
       <c r="M57" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ok</v>
       </c>
       <c r="N57" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ok</v>
       </c>
       <c r="P57" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ok(\d)</v>
       </c>
       <c r="Q57" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R57" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S57" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@o${1}k</v>
       </c>
       <c r="T57" s="25"/>
       <c r="U57" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ok(\d)/@o${1}k/</v>
       </c>
     </row>
@@ -9040,36 +9044,36 @@
       </c>
       <c r="J58" s="19"/>
       <c r="K58" s="23">
-        <f>LEN(E58)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L58" s="24"/>
       <c r="M58" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ong</v>
       </c>
       <c r="N58" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ong</v>
       </c>
       <c r="P58" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ong(\d)</v>
       </c>
       <c r="Q58" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R58" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S58" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@o${1}ng</v>
       </c>
       <c r="T58" s="25"/>
       <c r="U58" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ong(\d)/@o${1}ng/</v>
       </c>
     </row>
@@ -9105,36 +9109,36 @@
         <v>28</v>
       </c>
       <c r="K59" s="23">
-        <f>LEN(E59)</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="L59" s="24"/>
       <c r="M59" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>onnh</v>
       </c>
       <c r="N59" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>niuh</v>
       </c>
       <c r="P59" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>onnh(\d)</v>
       </c>
       <c r="Q59" s="5" t="str">
         <v>i</v>
       </c>
       <c r="R59" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S59" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@i${1}uh</v>
       </c>
       <c r="T59" s="25"/>
       <c r="U59" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@onnh(\d)/n@i${1}uh/</v>
       </c>
     </row>
@@ -9168,36 +9172,36 @@
       </c>
       <c r="J60" s="19"/>
       <c r="K60" s="23">
-        <f>LEN(E60)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L60" s="24"/>
       <c r="M60" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>oo</v>
       </c>
       <c r="N60" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>oo</v>
       </c>
       <c r="P60" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>oo(\d)</v>
       </c>
       <c r="Q60" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R60" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S60" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@o${1}o</v>
       </c>
       <c r="T60" s="25"/>
       <c r="U60" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@oo(\d)/@o${1}o/</v>
       </c>
     </row>
@@ -9231,36 +9235,36 @@
       </c>
       <c r="J61" s="19"/>
       <c r="K61" s="23">
-        <f>LEN(E61)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L61" s="24"/>
       <c r="M61" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ooh</v>
       </c>
       <c r="N61" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ooh</v>
       </c>
       <c r="P61" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ooh(\d)</v>
       </c>
       <c r="Q61" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R61" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S61" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@o${1}oh</v>
       </c>
       <c r="T61" s="25"/>
       <c r="U61" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ooh(\d)/@o${1}oh/</v>
       </c>
     </row>
@@ -9294,36 +9298,36 @@
       </c>
       <c r="J62" s="19"/>
       <c r="K62" s="23">
-        <f>LEN(E62)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L62" s="24"/>
       <c r="M62" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>oom</v>
       </c>
       <c r="N62" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>om</v>
       </c>
       <c r="P62" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>oom(\d)</v>
       </c>
       <c r="Q62" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R62" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S62" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@o${1}m</v>
       </c>
       <c r="T62" s="25"/>
       <c r="U62" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@oom(\d)/@o${1}m/</v>
       </c>
     </row>
@@ -9357,36 +9361,36 @@
       </c>
       <c r="J63" s="19"/>
       <c r="K63" s="23">
-        <f>LEN(E63)</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="L63" s="24"/>
       <c r="M63" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>oonn</v>
       </c>
       <c r="N63" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>noo</v>
       </c>
       <c r="P63" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>oonn(\d)</v>
       </c>
       <c r="Q63" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R63" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S63" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>n@o${1}o</v>
       </c>
       <c r="T63" s="25"/>
       <c r="U63" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@oonn(\d)/n@o${1}o/</v>
       </c>
     </row>
@@ -9420,36 +9424,36 @@
       </c>
       <c r="J64" s="19"/>
       <c r="K64" s="23">
-        <f>LEN(E64)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L64" s="24"/>
       <c r="M64" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>oop</v>
       </c>
       <c r="N64" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>op</v>
       </c>
       <c r="P64" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>oop(\d)</v>
       </c>
       <c r="Q64" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R64" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S64" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@o${1}p</v>
       </c>
       <c r="T64" s="25"/>
       <c r="U64" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@oop(\d)/@o${1}p/</v>
       </c>
     </row>
@@ -9483,36 +9487,36 @@
       </c>
       <c r="J65" s="19"/>
       <c r="K65" s="23">
-        <f>LEN(E65)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="L65" s="24"/>
       <c r="M65" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>or</v>
       </c>
       <c r="N65" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>o</v>
       </c>
       <c r="P65" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>or(\d)</v>
       </c>
       <c r="Q65" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R65" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S65" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@o${1}</v>
       </c>
       <c r="T65" s="25"/>
       <c r="U65" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@or(\d)/@o${1}/</v>
       </c>
     </row>
@@ -9546,36 +9550,36 @@
       </c>
       <c r="J66" s="19"/>
       <c r="K66" s="23">
-        <f>LEN(E66)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L66" s="24"/>
       <c r="M66" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>orh</v>
       </c>
       <c r="N66" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>oh</v>
       </c>
       <c r="P66" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>orh(\d)</v>
       </c>
       <c r="Q66" s="5" t="str">
         <v>o</v>
       </c>
       <c r="R66" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S66" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@o${1}h</v>
       </c>
       <c r="T66" s="25"/>
       <c r="U66" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@orh(\d)/@o${1}h/</v>
       </c>
     </row>
@@ -9609,36 +9613,36 @@
       </c>
       <c r="J67" s="19"/>
       <c r="K67" s="23">
-        <f>LEN(E67)</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L67" s="24"/>
       <c r="M67" s="11" t="str">
-        <f t="shared" ref="M67:N85" si="8">E67</f>
+        <f t="shared" ref="M67:N85" si="10">E67</f>
         <v>u</v>
       </c>
       <c r="N67" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>u</v>
       </c>
       <c r="P67" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>u(\d)</v>
       </c>
       <c r="Q67" s="5" t="str">
         <v>u</v>
       </c>
       <c r="R67" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S67" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>@u${1}</v>
       </c>
       <c r="T67" s="25"/>
       <c r="U67" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@u(\d)/@u${1}/</v>
       </c>
     </row>
@@ -9672,36 +9676,36 @@
       </c>
       <c r="J68" s="19"/>
       <c r="K68" s="23">
-        <f>LEN(E68)</f>
+        <f t="shared" ref="K68:K85" si="11">LEN(E68)</f>
         <v>2</v>
       </c>
       <c r="L68" s="24"/>
       <c r="M68" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ua</v>
       </c>
       <c r="N68" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ua</v>
       </c>
       <c r="P68" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ua(\d)</v>
       </c>
       <c r="Q68" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S68" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>u@a${1}</v>
       </c>
       <c r="T68" s="25"/>
       <c r="U68" s="26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/@ua(\d)/u@a${1}/</v>
       </c>
     </row>
@@ -9735,36 +9739,36 @@
       </c>
       <c r="J69" s="19"/>
       <c r="K69" s="23">
-        <f>LEN(E69)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="L69" s="24"/>
       <c r="M69" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uah</v>
       </c>
       <c r="N69" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uah</v>
       </c>
       <c r="P69" s="3" t="str">
-        <f t="shared" ref="P69:P85" si="9">_xlfn.CONCAT(M69, "(\d)")</f>
+        <f t="shared" ref="P69:P85" si="12">_xlfn.CONCAT(M69, "(\d)")</f>
         <v>uah(\d)</v>
       </c>
       <c r="Q69" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" ref="R69:R85" si="10">IFERROR( IF(Q69="", "", SEARCH(Q69, $N69)), "")</f>
+        <f t="shared" ref="R69:R85" si="13">IFERROR( IF(Q69="", "", SEARCH(Q69, $N69)), "")</f>
         <v>2</v>
       </c>
       <c r="S69" s="3" t="str">
-        <f t="shared" ref="S69:S85" si="11">IFERROR( _xlfn.CONCAT(LEFT(N69,R69-1), "@", MID(N69,R69,1), "${1}", RIGHT(N69, LEN(N69)-R69)), "" )</f>
+        <f t="shared" ref="S69:S85" si="14">IFERROR( _xlfn.CONCAT(LEFT(N69,R69-1), "@", MID(N69,R69,1), "${1}", RIGHT(N69, LEN(N69)-R69)), "" )</f>
         <v>u@a${1}h</v>
       </c>
       <c r="T69" s="25"/>
       <c r="U69" s="26" t="str">
-        <f t="shared" ref="U69:U85" si="12">IF(AND(N69&lt;&gt;"", M69&lt;&gt;""), "    - xform/@" &amp; P69 &amp;  "/"  &amp; S69 &amp;  "/", "")</f>
+        <f t="shared" ref="U69:U85" si="15">IF(AND(N69&lt;&gt;"", M69&lt;&gt;""), "    - xform/@" &amp; P69 &amp;  "/"  &amp; S69 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/@uah(\d)/u@a${1}h/</v>
       </c>
     </row>
@@ -9798,36 +9802,36 @@
       </c>
       <c r="J70" s="19"/>
       <c r="K70" s="23">
-        <f>LEN(E70)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="L70" s="24"/>
       <c r="M70" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uai</v>
       </c>
       <c r="N70" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uai</v>
       </c>
       <c r="P70" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uai(\d)</v>
       </c>
       <c r="Q70" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R70" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="S70" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>u@a${1}i</v>
       </c>
       <c r="T70" s="25"/>
       <c r="U70" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uai(\d)/u@a${1}i/</v>
       </c>
     </row>
@@ -9861,36 +9865,36 @@
       </c>
       <c r="J71" s="19"/>
       <c r="K71" s="23">
-        <f>LEN(E71)</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="L71" s="24"/>
       <c r="M71" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uaih</v>
       </c>
       <c r="N71" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uaih</v>
       </c>
       <c r="P71" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uaih(\d)</v>
       </c>
       <c r="Q71" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R71" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="S71" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>u@a${1}ih</v>
       </c>
       <c r="T71" s="25"/>
       <c r="U71" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uaih(\d)/u@a${1}ih/</v>
       </c>
     </row>
@@ -9926,36 +9930,36 @@
         <v>28</v>
       </c>
       <c r="K72" s="23">
-        <f>LEN(E72)</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="L72" s="24"/>
       <c r="M72" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uainn</v>
       </c>
       <c r="N72" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>nuai</v>
       </c>
       <c r="P72" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uainn(\d)</v>
       </c>
       <c r="Q72" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R72" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="S72" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>nu@a${1}i</v>
       </c>
       <c r="T72" s="25"/>
       <c r="U72" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uainn(\d)/nu@a${1}i/</v>
       </c>
     </row>
@@ -9991,36 +9995,36 @@
         <v>28</v>
       </c>
       <c r="K73" s="23">
-        <f>LEN(E73)</f>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="L73" s="24"/>
       <c r="M73" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uainnh</v>
       </c>
       <c r="N73" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>nuaih</v>
       </c>
       <c r="P73" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uainnh(\d)</v>
       </c>
       <c r="Q73" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R73" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="S73" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>nu@a${1}ih</v>
       </c>
       <c r="T73" s="25"/>
       <c r="U73" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uainnh(\d)/nu@a${1}ih/</v>
       </c>
     </row>
@@ -10054,36 +10058,36 @@
       </c>
       <c r="J74" s="19"/>
       <c r="K74" s="23">
-        <f>LEN(E74)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="L74" s="24"/>
       <c r="M74" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uan</v>
       </c>
       <c r="N74" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uan</v>
       </c>
       <c r="P74" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uan(\d)</v>
       </c>
       <c r="Q74" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R74" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="S74" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>u@a${1}n</v>
       </c>
       <c r="T74" s="25"/>
       <c r="U74" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uan(\d)/u@a${1}n/</v>
       </c>
     </row>
@@ -10117,36 +10121,36 @@
       </c>
       <c r="J75" s="19"/>
       <c r="K75" s="23">
-        <f>LEN(E75)</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="L75" s="24"/>
       <c r="M75" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uang</v>
       </c>
       <c r="N75" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uang</v>
       </c>
       <c r="P75" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uang(\d)</v>
       </c>
       <c r="Q75" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R75" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="S75" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>u@a${1}ng</v>
       </c>
       <c r="T75" s="25"/>
       <c r="U75" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uang(\d)/u@a${1}ng/</v>
       </c>
     </row>
@@ -10180,36 +10184,36 @@
       </c>
       <c r="J76" s="19"/>
       <c r="K76" s="23">
-        <f>LEN(E76)</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="L76" s="24"/>
       <c r="M76" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uann</v>
       </c>
       <c r="N76" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>nua</v>
       </c>
       <c r="P76" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uann(\d)</v>
       </c>
       <c r="Q76" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R76" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="S76" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>nu@a${1}</v>
       </c>
       <c r="T76" s="25"/>
       <c r="U76" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uann(\d)/nu@a${1}/</v>
       </c>
     </row>
@@ -10243,36 +10247,36 @@
       </c>
       <c r="J77" s="19"/>
       <c r="K77" s="23">
-        <f>LEN(E77)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="L77" s="24"/>
       <c r="M77" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uat</v>
       </c>
       <c r="N77" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uat</v>
       </c>
       <c r="P77" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uat(\d)</v>
       </c>
       <c r="Q77" s="5" t="str">
         <v>a</v>
       </c>
       <c r="R77" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="S77" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>u@a${1}t</v>
       </c>
       <c r="T77" s="25"/>
       <c r="U77" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uat(\d)/u@a${1}t/</v>
       </c>
     </row>
@@ -10306,36 +10310,36 @@
       </c>
       <c r="J78" s="19"/>
       <c r="K78" s="23">
-        <f>LEN(E78)</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="L78" s="24"/>
       <c r="M78" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ue</v>
       </c>
       <c r="N78" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ue</v>
       </c>
       <c r="P78" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>ue(\d)</v>
       </c>
       <c r="Q78" s="5" t="str">
         <v>e</v>
       </c>
       <c r="R78" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="S78" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>u@e${1}</v>
       </c>
       <c r="T78" s="25"/>
       <c r="U78" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@ue(\d)/u@e${1}/</v>
       </c>
     </row>
@@ -10369,36 +10373,36 @@
       </c>
       <c r="J79" s="19"/>
       <c r="K79" s="23">
-        <f>LEN(E79)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="L79" s="24"/>
       <c r="M79" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ueh</v>
       </c>
       <c r="N79" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ueh</v>
       </c>
       <c r="P79" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>ueh(\d)</v>
       </c>
       <c r="Q79" s="5" t="str">
         <v>e</v>
       </c>
       <c r="R79" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="S79" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>u@e${1}h</v>
       </c>
       <c r="T79" s="25"/>
       <c r="U79" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@ueh(\d)/u@e${1}h/</v>
       </c>
     </row>
@@ -10432,36 +10436,36 @@
       </c>
       <c r="J80" s="19"/>
       <c r="K80" s="23">
-        <f>LEN(E80)</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="L80" s="24"/>
       <c r="M80" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uh</v>
       </c>
       <c r="N80" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uh</v>
       </c>
       <c r="P80" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uh(\d)</v>
       </c>
       <c r="Q80" s="5" t="str">
         <v>u</v>
       </c>
       <c r="R80" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="S80" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>@u${1}h</v>
       </c>
       <c r="T80" s="25"/>
       <c r="U80" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uh(\d)/@u${1}h/</v>
       </c>
     </row>
@@ -10495,36 +10499,36 @@
       </c>
       <c r="J81" s="19"/>
       <c r="K81" s="23">
-        <f>LEN(E81)</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="L81" s="24"/>
       <c r="M81" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ui</v>
       </c>
       <c r="N81" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ui</v>
       </c>
       <c r="P81" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>ui(\d)</v>
       </c>
       <c r="Q81" s="5" t="str">
         <v>u</v>
       </c>
       <c r="R81" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="S81" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>@u${1}i</v>
       </c>
       <c r="T81" s="25"/>
       <c r="U81" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@ui(\d)/@u${1}i/</v>
       </c>
     </row>
@@ -10558,36 +10562,36 @@
       </c>
       <c r="J82" s="29"/>
       <c r="K82" s="23">
-        <f>LEN(E82)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="L82" s="24"/>
       <c r="M82" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uih</v>
       </c>
       <c r="N82" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uih</v>
       </c>
       <c r="P82" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uih(\d)</v>
       </c>
       <c r="Q82" s="5" t="str">
         <v>u</v>
       </c>
       <c r="R82" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="S82" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>@u${1}ih</v>
       </c>
       <c r="T82" s="25"/>
       <c r="U82" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uih(\d)/@u${1}ih/</v>
       </c>
     </row>
@@ -10621,36 +10625,36 @@
       </c>
       <c r="J83" s="19"/>
       <c r="K83" s="23">
-        <f>LEN(E83)</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="L83" s="24"/>
       <c r="M83" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>uinn</v>
       </c>
       <c r="N83" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>nui</v>
       </c>
       <c r="P83" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>uinn(\d)</v>
       </c>
       <c r="Q83" s="5" t="str">
         <v>u</v>
       </c>
       <c r="R83" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="S83" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>n@u${1}i</v>
       </c>
       <c r="T83" s="25"/>
       <c r="U83" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@uinn(\d)/n@u${1}i/</v>
       </c>
     </row>
@@ -10684,36 +10688,36 @@
       </c>
       <c r="J84" s="19"/>
       <c r="K84" s="23">
-        <f>LEN(E84)</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="L84" s="24"/>
       <c r="M84" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>un</v>
       </c>
       <c r="N84" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>un</v>
       </c>
       <c r="P84" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>un(\d)</v>
       </c>
       <c r="Q84" s="5" t="str">
         <v>u</v>
       </c>
       <c r="R84" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="S84" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>@u${1}n</v>
       </c>
       <c r="T84" s="25"/>
       <c r="U84" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@un(\d)/@u${1}n/</v>
       </c>
     </row>
@@ -10747,36 +10751,36 @@
       </c>
       <c r="J85" s="19"/>
       <c r="K85" s="23">
-        <f>LEN(E85)</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="L85" s="24"/>
       <c r="M85" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ut</v>
       </c>
       <c r="N85" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ut</v>
       </c>
       <c r="P85" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>ut(\d)</v>
       </c>
       <c r="Q85" s="5" t="str">
         <v>u</v>
       </c>
       <c r="R85" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="S85" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>@u${1}t</v>
       </c>
       <c r="T85" s="25"/>
       <c r="U85" s="26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">    - xform/@ut(\d)/@u${1}t/</v>
       </c>
     </row>
@@ -10878,6 +10882,5486 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B5019B8-7CC4-4BC2-B766-A37AA32AD17E}">
+  <dimension ref="A1:AS97"/>
+  <sheetFormatPr defaultRowHeight="26.25" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="8.375" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.375" style="2" customWidth="1"/>
+    <col min="5" max="8" width="15.375" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="10" width="15.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.25" style="2" customWidth="1"/>
+    <col min="13" max="14" width="15.125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="2.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15.75" style="3" customWidth="1"/>
+    <col min="17" max="17" width="16.75" style="3" customWidth="1"/>
+    <col min="18" max="18" width="4.5" style="2" customWidth="1"/>
+    <col min="19" max="19" width="51.75" style="6" customWidth="1"/>
+    <col min="20" max="20" width="9" style="2" customWidth="1"/>
+    <col min="21" max="32" width="7.5" style="7" customWidth="1"/>
+    <col min="33" max="38" width="19.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="39" max="41" width="19.875" style="8" customWidth="1"/>
+    <col min="42" max="42" width="19.875" style="2" customWidth="1"/>
+    <col min="43" max="44" width="9" style="2" customWidth="1"/>
+    <col min="45" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:45" ht="27" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="S1" s="10"/>
+      <c r="V1" s="7">
+        <v>1</v>
+      </c>
+      <c r="W1" s="7">
+        <v>2</v>
+      </c>
+      <c r="X1" s="7">
+        <v>3</v>
+      </c>
+      <c r="Y1" s="7">
+        <v>4</v>
+      </c>
+      <c r="Z1" s="7">
+        <v>5</v>
+      </c>
+      <c r="AA1" s="7">
+        <v>6</v>
+      </c>
+      <c r="AB1" s="7">
+        <v>7</v>
+      </c>
+      <c r="AC1" s="7">
+        <v>8</v>
+      </c>
+      <c r="AD1" s="7">
+        <v>9</v>
+      </c>
+      <c r="AE1" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" ht="27" thickBot="1">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:45" ht="54.75" customHeight="1" thickBot="1">
+      <c r="A3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="13"/>
+      <c r="M3" s="11" t="str">
+        <f>F3</f>
+        <v>閩拼方案</v>
+      </c>
+      <c r="N3" s="11" t="str">
+        <f>I3</f>
+        <v>方音符號</v>
+      </c>
+      <c r="P3" s="11" t="str">
+        <f>_xlfn.CONCAT(M3, "+調號")</f>
+        <v>閩拼方案+調號</v>
+      </c>
+      <c r="Q3" s="11" t="str">
+        <f>N3</f>
+        <v>方音符號</v>
+      </c>
+      <c r="S3" s="14"/>
+      <c r="U3" s="16"/>
+      <c r="W3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="X3" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF3" s="18"/>
+    </row>
+    <row r="4" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A4" s="19">
+        <v>73</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="23">
+        <f>LEN(F4)</f>
+        <v>5</v>
+      </c>
+      <c r="L4" s="24"/>
+      <c r="M4" s="11" t="str">
+        <f t="shared" ref="M4:M67" si="0">F4</f>
+        <v>nuaih</v>
+      </c>
+      <c r="N4" s="11" t="str">
+        <f t="shared" ref="N4:N67" si="1">I4</f>
+        <v>ㄨㆮㆷ</v>
+      </c>
+      <c r="P4" s="3" t="str">
+        <f>_xlfn.CONCAT(M4, "(\d)")</f>
+        <v>nuaih(\d)</v>
+      </c>
+      <c r="Q4" s="3" t="str">
+        <f>IFERROR( _xlfn.CONCAT(N4, "》", "${1}"), "")</f>
+        <v>ㄨㆮㆷ》${1}</v>
+      </c>
+      <c r="R4" s="25"/>
+      <c r="S4" s="26" t="str">
+        <f>IF(AND(N4&lt;&gt;"", M4&lt;&gt;""), "    - xform/》" &amp; P4 &amp;  "/"  &amp; Q4 &amp;  "/", "")</f>
+        <v xml:space="preserve">    - xform/》nuaih(\d)/ㄨㆮㆷ》${1}/</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="V4" s="27" t="str">
+        <f t="shared" ref="V4:AE10" si="2">_xlfn.CONCAT($U4, IF(V$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(V$3,4)))))</f>
+        <v>a</v>
+      </c>
+      <c r="W4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>á</v>
+      </c>
+      <c r="X4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>à</v>
+      </c>
+      <c r="Y4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>a</v>
+      </c>
+      <c r="Z4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ǎ</v>
+      </c>
+      <c r="AA4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>á</v>
+      </c>
+      <c r="AB4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ā</v>
+      </c>
+      <c r="AC4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>a̍</v>
+      </c>
+      <c r="AD4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>a̋</v>
+      </c>
+      <c r="AE4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>å</v>
+      </c>
+      <c r="AG4" s="28" t="str">
+        <f t="shared" ref="AG4:AP10" si="3">_xlfn.CONCAT("    - xform/》", $U4, V$1, "/", V4, "/")</f>
+        <v xml:space="preserve">    - xform/》a1/a/</v>
+      </c>
+      <c r="AH4" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》a2/á/</v>
+      </c>
+      <c r="AI4" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》a3/à/</v>
+      </c>
+      <c r="AJ4" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》a4/a/</v>
+      </c>
+      <c r="AK4" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》a5/ǎ/</v>
+      </c>
+      <c r="AL4" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》a6/á/</v>
+      </c>
+      <c r="AM4" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》a7/ā/</v>
+      </c>
+      <c r="AN4" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》a8/a̍/</v>
+      </c>
+      <c r="AO4" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》a9/a̋/</v>
+      </c>
+      <c r="AP4" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》a9/å/</v>
+      </c>
+      <c r="AQ4" s="27"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="7"/>
+    </row>
+    <row r="5" spans="1:45" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A5" s="19">
+        <v>32</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="23">
+        <f>LEN(F5)</f>
+        <v>4</v>
+      </c>
+      <c r="L5" s="24"/>
+      <c r="M5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>niah</v>
+      </c>
+      <c r="N5" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆩㆷ</v>
+      </c>
+      <c r="P5" s="3" t="str">
+        <f t="shared" ref="P5:P68" si="4">_xlfn.CONCAT(M5, "(\d)")</f>
+        <v>niah(\d)</v>
+      </c>
+      <c r="Q5" s="3" t="str">
+        <f t="shared" ref="Q5:Q68" si="5">IFERROR( _xlfn.CONCAT(N5, "》", "${1}"), "")</f>
+        <v>ㄧㆩㆷ》${1}</v>
+      </c>
+      <c r="R5" s="25"/>
+      <c r="S5" s="26" t="str">
+        <f t="shared" ref="S5:S68" si="6">IF(AND(N5&lt;&gt;"", M5&lt;&gt;""), "    - xform/》" &amp; P5 &amp;  "/"  &amp; Q5 &amp;  "/", "")</f>
+        <v xml:space="preserve">    - xform/》niah(\d)/ㄧㆩㆷ》${1}/</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="V5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>i</v>
+      </c>
+      <c r="W5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>í</v>
+      </c>
+      <c r="X5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ì</v>
+      </c>
+      <c r="Y5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>i</v>
+      </c>
+      <c r="Z5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ǐ</v>
+      </c>
+      <c r="AA5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>í</v>
+      </c>
+      <c r="AB5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ī</v>
+      </c>
+      <c r="AC5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>i̍</v>
+      </c>
+      <c r="AD5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>i̋</v>
+      </c>
+      <c r="AE5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>i̊</v>
+      </c>
+      <c r="AG5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i1/i/</v>
+      </c>
+      <c r="AH5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i2/í/</v>
+      </c>
+      <c r="AI5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i3/ì/</v>
+      </c>
+      <c r="AJ5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i4/i/</v>
+      </c>
+      <c r="AK5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i5/ǐ/</v>
+      </c>
+      <c r="AL5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i6/í/</v>
+      </c>
+      <c r="AM5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i7/ī/</v>
+      </c>
+      <c r="AN5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i8/i̍/</v>
+      </c>
+      <c r="AO5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i9/i̋/</v>
+      </c>
+      <c r="AP5" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》i9/i̊/</v>
+      </c>
+      <c r="AQ5" s="27"/>
+      <c r="AR5" s="27"/>
+      <c r="AS5" s="7"/>
+    </row>
+    <row r="6" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A6" s="19">
+        <v>40</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="23">
+        <f>LEN(F6)</f>
+        <v>4</v>
+      </c>
+      <c r="L6" s="24"/>
+      <c r="M6" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>niao</v>
+      </c>
+      <c r="N6" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆯ</v>
+      </c>
+      <c r="P6" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>niao(\d)</v>
+      </c>
+      <c r="Q6" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆯ》${1}</v>
+      </c>
+      <c r="R6" s="25"/>
+      <c r="S6" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》niao(\d)/ㄧㆯ》${1}/</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>u</v>
+      </c>
+      <c r="W6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ú</v>
+      </c>
+      <c r="X6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ù</v>
+      </c>
+      <c r="Y6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>u</v>
+      </c>
+      <c r="Z6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ǔ</v>
+      </c>
+      <c r="AA6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ú</v>
+      </c>
+      <c r="AB6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ū</v>
+      </c>
+      <c r="AC6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>u̍</v>
+      </c>
+      <c r="AD6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ű</v>
+      </c>
+      <c r="AE6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ů</v>
+      </c>
+      <c r="AG6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u1/u/</v>
+      </c>
+      <c r="AH6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u2/ú/</v>
+      </c>
+      <c r="AI6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u3/ù/</v>
+      </c>
+      <c r="AJ6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u4/u/</v>
+      </c>
+      <c r="AK6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u5/ǔ/</v>
+      </c>
+      <c r="AL6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u6/ú/</v>
+      </c>
+      <c r="AM6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u7/ū/</v>
+      </c>
+      <c r="AN6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u8/u̍/</v>
+      </c>
+      <c r="AO6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u9/ű/</v>
+      </c>
+      <c r="AP6" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》u9/ů/</v>
+      </c>
+      <c r="AQ6" s="27"/>
+      <c r="AR6" s="27"/>
+      <c r="AS6" s="7"/>
+    </row>
+    <row r="7" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A7" s="19">
+        <v>43</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="23">
+        <f>LEN(F7)</f>
+        <v>4</v>
+      </c>
+      <c r="L7" s="24"/>
+      <c r="M7" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>nioo</v>
+      </c>
+      <c r="N7" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆧ</v>
+      </c>
+      <c r="P7" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>nioo(\d)</v>
+      </c>
+      <c r="Q7" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆧ》${1}</v>
+      </c>
+      <c r="R7" s="25"/>
+      <c r="S7" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》nioo(\d)/ㄧㆧ》${1}/</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="V7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>e</v>
+      </c>
+      <c r="W7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>é</v>
+      </c>
+      <c r="X7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>è</v>
+      </c>
+      <c r="Y7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>e</v>
+      </c>
+      <c r="Z7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ě</v>
+      </c>
+      <c r="AA7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>é</v>
+      </c>
+      <c r="AB7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ē</v>
+      </c>
+      <c r="AC7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>e̍</v>
+      </c>
+      <c r="AD7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>e̋</v>
+      </c>
+      <c r="AE7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>e̊</v>
+      </c>
+      <c r="AG7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e1/e/</v>
+      </c>
+      <c r="AH7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e2/é/</v>
+      </c>
+      <c r="AI7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e3/è/</v>
+      </c>
+      <c r="AJ7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e4/e/</v>
+      </c>
+      <c r="AK7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e5/ě/</v>
+      </c>
+      <c r="AL7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e6/é/</v>
+      </c>
+      <c r="AM7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e7/ē/</v>
+      </c>
+      <c r="AN7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e8/e̍/</v>
+      </c>
+      <c r="AO7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e9/e̋/</v>
+      </c>
+      <c r="AP7" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》e9/e̊/</v>
+      </c>
+      <c r="AQ7" s="27"/>
+      <c r="AR7" s="27"/>
+      <c r="AS7" s="7"/>
+    </row>
+    <row r="8" spans="1:45" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A8" s="19">
+        <v>49</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="23">
+        <f>LEN(F8)</f>
+        <v>4</v>
+      </c>
+      <c r="L8" s="24"/>
+      <c r="M8" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>niuh</v>
+      </c>
+      <c r="N8" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆫㆷ</v>
+      </c>
+      <c r="P8" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>niuh(\d)</v>
+      </c>
+      <c r="Q8" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆫㆷ》${1}</v>
+      </c>
+      <c r="R8" s="25"/>
+      <c r="S8" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》niuh(\d)/ㄧㆫㆷ》${1}/</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="V8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>o</v>
+      </c>
+      <c r="W8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ó</v>
+      </c>
+      <c r="X8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ò</v>
+      </c>
+      <c r="Y8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>o</v>
+      </c>
+      <c r="Z8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ǒ</v>
+      </c>
+      <c r="AA8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ó</v>
+      </c>
+      <c r="AB8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ō</v>
+      </c>
+      <c r="AC8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>o̍</v>
+      </c>
+      <c r="AD8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ő</v>
+      </c>
+      <c r="AE8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>o̊</v>
+      </c>
+      <c r="AG8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o1/o/</v>
+      </c>
+      <c r="AH8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o2/ó/</v>
+      </c>
+      <c r="AI8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o3/ò/</v>
+      </c>
+      <c r="AJ8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o4/o/</v>
+      </c>
+      <c r="AK8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o5/ǒ/</v>
+      </c>
+      <c r="AL8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o6/ó/</v>
+      </c>
+      <c r="AM8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o7/ō/</v>
+      </c>
+      <c r="AN8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o8/o̍/</v>
+      </c>
+      <c r="AO8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o9/ő/</v>
+      </c>
+      <c r="AP8" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》o9/o̊/</v>
+      </c>
+      <c r="AQ8" s="27"/>
+      <c r="AR8" s="27"/>
+      <c r="AS8" s="7"/>
+    </row>
+    <row r="9" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A9" s="19">
+        <v>55</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="23">
+        <f>LEN(F9)</f>
+        <v>4</v>
+      </c>
+      <c r="L9" s="24"/>
+      <c r="M9" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>niuh</v>
+      </c>
+      <c r="N9" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆧㆷ</v>
+      </c>
+      <c r="P9" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>niuh(\d)</v>
+      </c>
+      <c r="Q9" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆧㆷ》${1}</v>
+      </c>
+      <c r="R9" s="25"/>
+      <c r="S9" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》niuh(\d)/ㆧㆷ》${1}/</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="V9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>m</v>
+      </c>
+      <c r="W9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ḿ</v>
+      </c>
+      <c r="X9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>m̀</v>
+      </c>
+      <c r="Y9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>m</v>
+      </c>
+      <c r="Z9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>m̌</v>
+      </c>
+      <c r="AA9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ḿ</v>
+      </c>
+      <c r="AB9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>m̄</v>
+      </c>
+      <c r="AC9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>m̍</v>
+      </c>
+      <c r="AD9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>m̋</v>
+      </c>
+      <c r="AE9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>m̊</v>
+      </c>
+      <c r="AG9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m1/m/</v>
+      </c>
+      <c r="AH9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m2/ḿ/</v>
+      </c>
+      <c r="AI9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m3/m̀/</v>
+      </c>
+      <c r="AJ9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m4/m/</v>
+      </c>
+      <c r="AK9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m5/m̌/</v>
+      </c>
+      <c r="AL9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m6/ḿ/</v>
+      </c>
+      <c r="AM9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m7/m̄/</v>
+      </c>
+      <c r="AN9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m8/m̍/</v>
+      </c>
+      <c r="AO9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m9/m̋/</v>
+      </c>
+      <c r="AP9" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》m9/m̊/</v>
+      </c>
+      <c r="AQ9" s="27"/>
+      <c r="AR9" s="27"/>
+      <c r="AS9" s="7"/>
+    </row>
+    <row r="10" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A10" s="19">
+        <v>71</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="23">
+        <f>LEN(F10)</f>
+        <v>4</v>
+      </c>
+      <c r="L10" s="24"/>
+      <c r="M10" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>nuai</v>
+      </c>
+      <c r="N10" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㆮ</v>
+      </c>
+      <c r="P10" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>nuai(\d)</v>
+      </c>
+      <c r="Q10" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㆮ》${1}</v>
+      </c>
+      <c r="R10" s="25"/>
+      <c r="S10" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》nuai(\d)/ㄨㆮ》${1}/</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="V10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>n</v>
+      </c>
+      <c r="W10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ń</v>
+      </c>
+      <c r="X10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ǹ</v>
+      </c>
+      <c r="Y10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>n</v>
+      </c>
+      <c r="Z10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ň</v>
+      </c>
+      <c r="AA10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>ń</v>
+      </c>
+      <c r="AB10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>n̄</v>
+      </c>
+      <c r="AC10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>n̍</v>
+      </c>
+      <c r="AD10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>n̋</v>
+      </c>
+      <c r="AE10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>n̊</v>
+      </c>
+      <c r="AG10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n1/n/</v>
+      </c>
+      <c r="AH10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n2/ń/</v>
+      </c>
+      <c r="AI10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n3/ǹ/</v>
+      </c>
+      <c r="AJ10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n4/n/</v>
+      </c>
+      <c r="AK10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n5/ň/</v>
+      </c>
+      <c r="AL10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n6/ń/</v>
+      </c>
+      <c r="AM10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n7/n̄/</v>
+      </c>
+      <c r="AN10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n8/n̍/</v>
+      </c>
+      <c r="AO10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n9/n̋/</v>
+      </c>
+      <c r="AP10" s="28" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》n9/n̊/</v>
+      </c>
+      <c r="AQ10" s="27"/>
+      <c r="AR10" s="27"/>
+      <c r="AS10" s="7"/>
+    </row>
+    <row r="11" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A11" s="19">
+        <v>4</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="23">
+        <f>LEN(F11)</f>
+        <v>3</v>
+      </c>
+      <c r="L11" s="24"/>
+      <c r="M11" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>nah</v>
+      </c>
+      <c r="N11" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆩㆷ</v>
+      </c>
+      <c r="P11" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>nah(\d)</v>
+      </c>
+      <c r="Q11" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆩㆷ》${1}</v>
+      </c>
+      <c r="R11" s="25"/>
+      <c r="S11" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》nah(\d)/ㆩㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A12" s="19">
+        <v>12</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="23">
+        <f>LEN(F12)</f>
+        <v>3</v>
+      </c>
+      <c r="L12" s="24"/>
+      <c r="M12" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>nai</v>
+      </c>
+      <c r="N12" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆮ</v>
+      </c>
+      <c r="P12" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>nai(\d)</v>
+      </c>
+      <c r="Q12" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆮ》${1}</v>
+      </c>
+      <c r="R12" s="25"/>
+      <c r="S12" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》nai(\d)/ㆮ》${1}/</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A13" s="19">
+        <v>19</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="23">
+        <f>LEN(F13)</f>
+        <v>3</v>
+      </c>
+      <c r="L13" s="24"/>
+      <c r="M13" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>neh</v>
+      </c>
+      <c r="N13" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆥㆷ</v>
+      </c>
+      <c r="P13" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>neh(\d)</v>
+      </c>
+      <c r="Q13" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆥㆷ》${1}</v>
+      </c>
+      <c r="R13" s="25"/>
+      <c r="S13" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》neh(\d)/ㆥㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="14" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A14" s="19">
+        <v>30</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="23">
+        <f>LEN(F14)</f>
+        <v>3</v>
+      </c>
+      <c r="L14" s="24"/>
+      <c r="M14" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>nia</v>
+      </c>
+      <c r="N14" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆩ</v>
+      </c>
+      <c r="P14" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>nia(\d)</v>
+      </c>
+      <c r="Q14" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆩ》${1}</v>
+      </c>
+      <c r="R14" s="25"/>
+      <c r="S14" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》nia(\d)/ㄧㆩ》${1}/</v>
+      </c>
+    </row>
+    <row r="15" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A15" s="19">
+        <v>48</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" s="23">
+        <f>LEN(F15)</f>
+        <v>3</v>
+      </c>
+      <c r="L15" s="24"/>
+      <c r="M15" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>niu</v>
+      </c>
+      <c r="N15" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆫ</v>
+      </c>
+      <c r="P15" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>niu(\d)</v>
+      </c>
+      <c r="Q15" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆫ》${1}</v>
+      </c>
+      <c r="R15" s="25"/>
+      <c r="S15" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》niu(\d)/ㄧㆫ》${1}/</v>
+      </c>
+    </row>
+    <row r="16" spans="1:45" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A16" s="19">
+        <v>2</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="23">
+        <f>LEN(F16)</f>
+        <v>2</v>
+      </c>
+      <c r="L16" s="24"/>
+      <c r="M16" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>na</v>
+      </c>
+      <c r="N16" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆩ</v>
+      </c>
+      <c r="P16" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>na(\d)</v>
+      </c>
+      <c r="Q16" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆩ》${1}</v>
+      </c>
+      <c r="R16" s="25"/>
+      <c r="S16" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》na(\d)/ㆩ》${1}/</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A17" s="19">
+        <v>17</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="23">
+        <f>LEN(F17)</f>
+        <v>2</v>
+      </c>
+      <c r="L17" s="24"/>
+      <c r="M17" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ne</v>
+      </c>
+      <c r="N17" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆥ</v>
+      </c>
+      <c r="P17" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ne(\d)</v>
+      </c>
+      <c r="Q17" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆥ》${1}</v>
+      </c>
+      <c r="R17" s="25"/>
+      <c r="S17" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ne(\d)/ㆥ》${1}/</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A18" s="19">
+        <v>21</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="23">
+        <f>LEN(F18)</f>
+        <v>2</v>
+      </c>
+      <c r="L18" s="24"/>
+      <c r="M18" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ni</v>
+      </c>
+      <c r="N18" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆪ</v>
+      </c>
+      <c r="P18" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ni(\d)</v>
+      </c>
+      <c r="Q18" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆪ》${1}</v>
+      </c>
+      <c r="R18" s="25"/>
+      <c r="S18" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ni(\d)/ㆪ》${1}/</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A19" s="19">
+        <v>35</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="J19" s="19"/>
+      <c r="K19" s="23">
+        <f>LEN(F19)</f>
+        <v>4</v>
+      </c>
+      <c r="L19" s="24"/>
+      <c r="M19" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iang</v>
+      </c>
+      <c r="N19" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄤ</v>
+      </c>
+      <c r="P19" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iang(\d)</v>
+      </c>
+      <c r="Q19" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄤ》${1}</v>
+      </c>
+      <c r="R19" s="25"/>
+      <c r="S19" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iang(\d)/ㄧㄤ》${1}/</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A20" s="19">
+        <v>41</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="J20" s="19"/>
+      <c r="K20" s="23">
+        <f>LEN(F20)</f>
+        <v>4</v>
+      </c>
+      <c r="L20" s="24"/>
+      <c r="M20" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iaoh</v>
+      </c>
+      <c r="N20" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄠㆷ</v>
+      </c>
+      <c r="P20" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iaoh(\d)</v>
+      </c>
+      <c r="Q20" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄠㆷ》${1}</v>
+      </c>
+      <c r="R20" s="25"/>
+      <c r="S20" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iaoh(\d)/ㄧㄠㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A21" s="19">
+        <v>45</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="19"/>
+      <c r="K21" s="23">
+        <f>LEN(F21)</f>
+        <v>4</v>
+      </c>
+      <c r="L21" s="24"/>
+      <c r="M21" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iong</v>
+      </c>
+      <c r="N21" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆲ</v>
+      </c>
+      <c r="P21" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iong(\d)</v>
+      </c>
+      <c r="Q21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆲ》${1}</v>
+      </c>
+      <c r="R21" s="25"/>
+      <c r="S21" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iong(\d)/ㄧㆲ》${1}/</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A22" s="19">
+        <v>72</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="J22" s="19"/>
+      <c r="K22" s="23">
+        <f>LEN(F22)</f>
+        <v>4</v>
+      </c>
+      <c r="L22" s="24"/>
+      <c r="M22" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>uaih</v>
+      </c>
+      <c r="N22" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㄞㆷ</v>
+      </c>
+      <c r="P22" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>uaih(\d)</v>
+      </c>
+      <c r="Q22" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㄞㆷ》${1}</v>
+      </c>
+      <c r="R22" s="25"/>
+      <c r="S22" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》uaih(\d)/ㄨㄞㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A23" s="19">
+        <v>68</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="J23" s="19"/>
+      <c r="K23" s="23">
+        <f>LEN(F23)</f>
+        <v>4</v>
+      </c>
+      <c r="L23" s="24"/>
+      <c r="M23" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>uang</v>
+      </c>
+      <c r="N23" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㄤ</v>
+      </c>
+      <c r="P23" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>uang(\d)</v>
+      </c>
+      <c r="Q23" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㄤ》${1}</v>
+      </c>
+      <c r="R23" s="25"/>
+      <c r="S23" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》uang(\d)/ㄨㄤ》${1}/</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A24" s="19">
+        <v>13</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="I24" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="J24" s="19"/>
+      <c r="K24" s="23">
+        <f>LEN(F24)</f>
+        <v>3</v>
+      </c>
+      <c r="L24" s="24"/>
+      <c r="M24" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>aih</v>
+      </c>
+      <c r="N24" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄞㆷ</v>
+      </c>
+      <c r="P24" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>aih(\d)</v>
+      </c>
+      <c r="Q24" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄞㆷ》${1}</v>
+      </c>
+      <c r="R24" s="25"/>
+      <c r="S24" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》aih(\d)/ㄞㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A25" s="19">
+        <v>7</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="J25" s="19"/>
+      <c r="K25" s="23">
+        <f>LEN(F25)</f>
+        <v>3</v>
+      </c>
+      <c r="L25" s="24"/>
+      <c r="M25" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ang</v>
+      </c>
+      <c r="N25" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄤ</v>
+      </c>
+      <c r="P25" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ang(\d)</v>
+      </c>
+      <c r="Q25" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄤ》${1}</v>
+      </c>
+      <c r="R25" s="25"/>
+      <c r="S25" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ang(\d)/ㄤ》${1}/</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A26" s="19">
+        <v>15</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="J26" s="19"/>
+      <c r="K26" s="23">
+        <f>LEN(F26)</f>
+        <v>3</v>
+      </c>
+      <c r="L26" s="24"/>
+      <c r="M26" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>aoh</v>
+      </c>
+      <c r="N26" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄠㆷ</v>
+      </c>
+      <c r="P26" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>aoh(\d)</v>
+      </c>
+      <c r="Q26" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄠㆷ》${1}</v>
+      </c>
+      <c r="R26" s="25"/>
+      <c r="S26" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》aoh(\d)/ㄠㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A27" s="19">
+        <v>31</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="J27" s="19"/>
+      <c r="K27" s="23">
+        <f>LEN(F27)</f>
+        <v>3</v>
+      </c>
+      <c r="L27" s="24"/>
+      <c r="M27" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iah</v>
+      </c>
+      <c r="N27" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄚㆷ</v>
+      </c>
+      <c r="P27" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iah(\d)</v>
+      </c>
+      <c r="Q27" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄚㆷ》${1}</v>
+      </c>
+      <c r="R27" s="25"/>
+      <c r="S27" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iah(\d)/ㄧㄚㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A28" s="19">
+        <v>38</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="J28" s="19"/>
+      <c r="K28" s="23">
+        <f>LEN(F28)</f>
+        <v>3</v>
+      </c>
+      <c r="L28" s="24"/>
+      <c r="M28" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iak</v>
+      </c>
+      <c r="N28" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄚㆻ</v>
+      </c>
+      <c r="P28" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iak(\d)</v>
+      </c>
+      <c r="Q28" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄚㆻ》${1}</v>
+      </c>
+      <c r="R28" s="25"/>
+      <c r="S28" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iak(\d)/ㄧㄚㆻ》${1}/</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A29" s="19">
+        <v>33</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="J29" s="19"/>
+      <c r="K29" s="23">
+        <f>LEN(F29)</f>
+        <v>3</v>
+      </c>
+      <c r="L29" s="24"/>
+      <c r="M29" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iam</v>
+      </c>
+      <c r="N29" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆰ</v>
+      </c>
+      <c r="P29" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iam(\d)</v>
+      </c>
+      <c r="Q29" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆰ》${1}</v>
+      </c>
+      <c r="R29" s="25"/>
+      <c r="S29" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iam(\d)/ㄧㆰ》${1}/</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A30" s="19">
+        <v>34</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="H30" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="J30" s="19"/>
+      <c r="K30" s="23">
+        <f>LEN(F30)</f>
+        <v>3</v>
+      </c>
+      <c r="L30" s="24"/>
+      <c r="M30" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ian</v>
+      </c>
+      <c r="N30" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄢ</v>
+      </c>
+      <c r="P30" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ian(\d)</v>
+      </c>
+      <c r="Q30" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄢ》${1}</v>
+      </c>
+      <c r="R30" s="25"/>
+      <c r="S30" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ian(\d)/ㄧㄢ》${1}/</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A31" s="19">
+        <v>39</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="I31" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="J31" s="19"/>
+      <c r="K31" s="23">
+        <f>LEN(F31)</f>
+        <v>3</v>
+      </c>
+      <c r="L31" s="24"/>
+      <c r="M31" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iao</v>
+      </c>
+      <c r="N31" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄠ</v>
+      </c>
+      <c r="P31" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iao(\d)</v>
+      </c>
+      <c r="Q31" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄠ》${1}</v>
+      </c>
+      <c r="R31" s="25"/>
+      <c r="S31" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iao(\d)/ㄧㄠ》${1}/</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A32" s="19">
+        <v>36</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="J32" s="19"/>
+      <c r="K32" s="23">
+        <f>LEN(F32)</f>
+        <v>3</v>
+      </c>
+      <c r="L32" s="24"/>
+      <c r="M32" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iap</v>
+      </c>
+      <c r="N32" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄚㆴ</v>
+      </c>
+      <c r="P32" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iap(\d)</v>
+      </c>
+      <c r="Q32" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄚㆴ》${1}</v>
+      </c>
+      <c r="R32" s="25"/>
+      <c r="S32" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iap(\d)/ㄧㄚㆴ》${1}/</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A33" s="19">
+        <v>37</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="J33" s="19"/>
+      <c r="K33" s="23">
+        <f>LEN(F33)</f>
+        <v>3</v>
+      </c>
+      <c r="L33" s="24"/>
+      <c r="M33" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iat</v>
+      </c>
+      <c r="N33" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄚㆵ</v>
+      </c>
+      <c r="P33" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iat(\d)</v>
+      </c>
+      <c r="Q33" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄚㆵ》${1}</v>
+      </c>
+      <c r="R33" s="25"/>
+      <c r="S33" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iat(\d)/ㄧㄚㆵ》${1}/</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A34" s="19">
+        <v>25</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="J34" s="19"/>
+      <c r="K34" s="23">
+        <f>LEN(F34)</f>
+        <v>3</v>
+      </c>
+      <c r="L34" s="24"/>
+      <c r="M34" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ing</v>
+      </c>
+      <c r="N34" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄥ</v>
+      </c>
+      <c r="P34" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ing(\d)</v>
+      </c>
+      <c r="Q34" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄥ》${1}</v>
+      </c>
+      <c r="R34" s="25"/>
+      <c r="S34" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ing(\d)/ㄧㄥ》${1}/</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A35" s="19">
+        <v>44</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="J35" s="19"/>
+      <c r="K35" s="23">
+        <f>LEN(F35)</f>
+        <v>3</v>
+      </c>
+      <c r="L35" s="24"/>
+      <c r="M35" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ioh</v>
+      </c>
+      <c r="N35" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄜㆷ</v>
+      </c>
+      <c r="P35" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ioh(\d)</v>
+      </c>
+      <c r="Q35" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄜㆷ》${1}</v>
+      </c>
+      <c r="R35" s="25"/>
+      <c r="S35" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ioh(\d)/ㄧㄜㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A36" s="19">
+        <v>46</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="J36" s="19"/>
+      <c r="K36" s="23">
+        <f>LEN(F36)</f>
+        <v>3</v>
+      </c>
+      <c r="L36" s="24"/>
+      <c r="M36" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iok</v>
+      </c>
+      <c r="N36" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆦㆻ</v>
+      </c>
+      <c r="P36" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iok(\d)</v>
+      </c>
+      <c r="Q36" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆦㆻ》${1}</v>
+      </c>
+      <c r="R36" s="25"/>
+      <c r="S36" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iok(\d)/ㄧㆦㆻ》${1}/</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A37" s="19">
+        <v>82</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="D37" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="E37" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="F37" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="G37" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="I37" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="J37" s="19"/>
+      <c r="K37" s="23">
+        <f>LEN(F37)</f>
+        <v>3</v>
+      </c>
+      <c r="L37" s="24"/>
+      <c r="M37" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ngh</v>
+      </c>
+      <c r="N37" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆭㆷ</v>
+      </c>
+      <c r="P37" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ngh(\d)</v>
+      </c>
+      <c r="Q37" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆭㆷ》${1}</v>
+      </c>
+      <c r="R37" s="25"/>
+      <c r="S37" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ngh(\d)/ㆭㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A38" s="19">
+        <v>52</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="G38" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="H38" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="J38" s="19"/>
+      <c r="K38" s="23">
+        <f>LEN(F38)</f>
+        <v>3</v>
+      </c>
+      <c r="L38" s="24"/>
+      <c r="M38" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>noo</v>
+      </c>
+      <c r="N38" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆧ</v>
+      </c>
+      <c r="P38" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>noo(\d)</v>
+      </c>
+      <c r="Q38" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆧ》${1}</v>
+      </c>
+      <c r="R38" s="25"/>
+      <c r="S38" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》noo(\d)/ㆧ》${1}/</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A39" s="19">
+        <v>65</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="G39" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="H39" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" s="19"/>
+      <c r="K39" s="23">
+        <f>LEN(F39)</f>
+        <v>3</v>
+      </c>
+      <c r="L39" s="24"/>
+      <c r="M39" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>nua</v>
+      </c>
+      <c r="N39" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㆩ</v>
+      </c>
+      <c r="P39" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>nua(\d)</v>
+      </c>
+      <c r="Q39" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㆩ》${1}</v>
+      </c>
+      <c r="R39" s="25"/>
+      <c r="S39" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》nua(\d)/ㄨㆩ》${1}/</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A40" s="19">
+        <v>77</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G40" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="J40" s="19"/>
+      <c r="K40" s="23">
+        <f>LEN(F40)</f>
+        <v>3</v>
+      </c>
+      <c r="L40" s="24"/>
+      <c r="M40" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>nui</v>
+      </c>
+      <c r="N40" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㆪ</v>
+      </c>
+      <c r="P40" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>nui(\d)</v>
+      </c>
+      <c r="Q40" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㆪ》${1}</v>
+      </c>
+      <c r="R40" s="25"/>
+      <c r="S40" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》nui(\d)/ㄨㆪ》${1}/</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A41" s="19">
+        <v>57</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="G41" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="I41" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="J41" s="19"/>
+      <c r="K41" s="23">
+        <f>LEN(F41)</f>
+        <v>3</v>
+      </c>
+      <c r="L41" s="24"/>
+      <c r="M41" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ong</v>
+      </c>
+      <c r="N41" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆲ</v>
+      </c>
+      <c r="P41" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ong(\d)</v>
+      </c>
+      <c r="Q41" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆲ》${1}</v>
+      </c>
+      <c r="R41" s="25"/>
+      <c r="S41" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ong(\d)/ㆲ》${1}/</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A42" s="19">
+        <v>54</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="G42" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="H42" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="I42" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="J42" s="19"/>
+      <c r="K42" s="23">
+        <f>LEN(F42)</f>
+        <v>3</v>
+      </c>
+      <c r="L42" s="24"/>
+      <c r="M42" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ooh</v>
+      </c>
+      <c r="N42" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆦㆷ</v>
+      </c>
+      <c r="P42" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ooh(\d)</v>
+      </c>
+      <c r="Q42" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆦㆷ》${1}</v>
+      </c>
+      <c r="R42" s="25"/>
+      <c r="S42" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ooh(\d)/ㆦㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A43" s="19">
+        <v>66</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G43" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="H43" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="J43" s="19"/>
+      <c r="K43" s="23">
+        <f>LEN(F43)</f>
+        <v>3</v>
+      </c>
+      <c r="L43" s="24"/>
+      <c r="M43" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>uah</v>
+      </c>
+      <c r="N43" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㄚㆷ</v>
+      </c>
+      <c r="P43" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>uah(\d)</v>
+      </c>
+      <c r="Q43" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㄚㆷ》${1}</v>
+      </c>
+      <c r="R43" s="25"/>
+      <c r="S43" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》uah(\d)/ㄨㄚㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A44" s="19">
+        <v>70</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="G44" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="H44" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="I44" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="J44" s="19"/>
+      <c r="K44" s="23">
+        <f>LEN(F44)</f>
+        <v>3</v>
+      </c>
+      <c r="L44" s="24"/>
+      <c r="M44" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>uai</v>
+      </c>
+      <c r="N44" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㄞ</v>
+      </c>
+      <c r="P44" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>uai(\d)</v>
+      </c>
+      <c r="Q44" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㄞ》${1}</v>
+      </c>
+      <c r="R44" s="25"/>
+      <c r="S44" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》uai(\d)/ㄨㄞ》${1}/</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A45" s="19">
+        <v>67</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="G45" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="H45" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="I45" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="J45" s="19"/>
+      <c r="K45" s="23">
+        <f>LEN(F45)</f>
+        <v>3</v>
+      </c>
+      <c r="L45" s="24"/>
+      <c r="M45" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>uan</v>
+      </c>
+      <c r="N45" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㄢ</v>
+      </c>
+      <c r="P45" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>uan(\d)</v>
+      </c>
+      <c r="Q45" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㄢ》${1}</v>
+      </c>
+      <c r="R45" s="25"/>
+      <c r="S45" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》uan(\d)/ㄨㄢ》${1}/</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A46" s="19">
+        <v>69</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="G46" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="H46" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="I46" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="J46" s="19"/>
+      <c r="K46" s="23">
+        <f>LEN(F46)</f>
+        <v>3</v>
+      </c>
+      <c r="L46" s="24"/>
+      <c r="M46" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>uat</v>
+      </c>
+      <c r="N46" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㄚㆵ</v>
+      </c>
+      <c r="P46" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>uat(\d)</v>
+      </c>
+      <c r="Q46" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㄚㆵ》${1}</v>
+      </c>
+      <c r="R46" s="25"/>
+      <c r="S46" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》uat(\d)/ㄨㄚㆵ》${1}/</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A47" s="19">
+        <v>75</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="G47" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="H47" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="I47" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="J47" s="19"/>
+      <c r="K47" s="23">
+        <f>LEN(F47)</f>
+        <v>3</v>
+      </c>
+      <c r="L47" s="24"/>
+      <c r="M47" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ueh</v>
+      </c>
+      <c r="N47" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㆤㆷ</v>
+      </c>
+      <c r="P47" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ueh(\d)</v>
+      </c>
+      <c r="Q47" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㆤㆷ》${1}</v>
+      </c>
+      <c r="R47" s="25"/>
+      <c r="S47" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ueh(\d)/ㄨㆤㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A48" s="19">
+        <v>78</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F48" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H48" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="I48" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="J48" s="29"/>
+      <c r="K48" s="23">
+        <f>LEN(F48)</f>
+        <v>3</v>
+      </c>
+      <c r="L48" s="24"/>
+      <c r="M48" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>uih</v>
+      </c>
+      <c r="N48" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄨㄧㆷ</v>
+      </c>
+      <c r="P48" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>uih(\d)</v>
+      </c>
+      <c r="Q48" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄨㄧㆷ》${1}</v>
+      </c>
+      <c r="R48" s="25"/>
+      <c r="S48" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》uih(\d)/ㄨㄧㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A49" s="19">
+        <v>3</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G49" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H49" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="I49" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="J49" s="19"/>
+      <c r="K49" s="23">
+        <f>LEN(F49)</f>
+        <v>2</v>
+      </c>
+      <c r="L49" s="24"/>
+      <c r="M49" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ah</v>
+      </c>
+      <c r="N49" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄚㆷ</v>
+      </c>
+      <c r="P49" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ah(\d)</v>
+      </c>
+      <c r="Q49" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄚㆷ》${1}</v>
+      </c>
+      <c r="R49" s="25"/>
+      <c r="S49" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ah(\d)/ㄚㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A50" s="19">
+        <v>11</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="G50" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="H50" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="I50" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="J50" s="19"/>
+      <c r="K50" s="23">
+        <f>LEN(F50)</f>
+        <v>2</v>
+      </c>
+      <c r="L50" s="24"/>
+      <c r="M50" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ai</v>
+      </c>
+      <c r="N50" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄞ</v>
+      </c>
+      <c r="P50" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ai(\d)</v>
+      </c>
+      <c r="Q50" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄞ》${1}</v>
+      </c>
+      <c r="R50" s="25"/>
+      <c r="S50" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ai(\d)/ㄞ》${1}/</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A51" s="19">
+        <v>10</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="G51" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="H51" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="I51" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="J51" s="19"/>
+      <c r="K51" s="23">
+        <f>LEN(F51)</f>
+        <v>2</v>
+      </c>
+      <c r="L51" s="24"/>
+      <c r="M51" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ak</v>
+      </c>
+      <c r="N51" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄚㆻ</v>
+      </c>
+      <c r="P51" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ak(\d)</v>
+      </c>
+      <c r="Q51" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄚㆻ》${1}</v>
+      </c>
+      <c r="R51" s="25"/>
+      <c r="S51" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ak(\d)/ㄚㆻ》${1}/</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A52" s="19">
+        <v>5</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G52" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="H52" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="I52" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="J52" s="19"/>
+      <c r="K52" s="23">
+        <f>LEN(F52)</f>
+        <v>2</v>
+      </c>
+      <c r="L52" s="24"/>
+      <c r="M52" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>am</v>
+      </c>
+      <c r="N52" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆰ</v>
+      </c>
+      <c r="P52" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>am(\d)</v>
+      </c>
+      <c r="Q52" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆰ》${1}</v>
+      </c>
+      <c r="R52" s="25"/>
+      <c r="S52" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》am(\d)/ㆰ》${1}/</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A53" s="19">
+        <v>6</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="G53" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="H53" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="I53" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="J53" s="19"/>
+      <c r="K53" s="23">
+        <f>LEN(F53)</f>
+        <v>2</v>
+      </c>
+      <c r="L53" s="24"/>
+      <c r="M53" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>an</v>
+      </c>
+      <c r="N53" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄢ</v>
+      </c>
+      <c r="P53" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>an(\d)</v>
+      </c>
+      <c r="Q53" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄢ》${1}</v>
+      </c>
+      <c r="R53" s="25"/>
+      <c r="S53" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》an(\d)/ㄢ》${1}/</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A54" s="19">
+        <v>14</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="G54" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="H54" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="I54" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="J54" s="19"/>
+      <c r="K54" s="23">
+        <f>LEN(F54)</f>
+        <v>2</v>
+      </c>
+      <c r="L54" s="24"/>
+      <c r="M54" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ao</v>
+      </c>
+      <c r="N54" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄠ</v>
+      </c>
+      <c r="P54" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ao(\d)</v>
+      </c>
+      <c r="Q54" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄠ》${1}</v>
+      </c>
+      <c r="R54" s="25"/>
+      <c r="S54" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ao(\d)/ㄠ》${1}/</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A55" s="19">
+        <v>8</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="G55" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="H55" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="I55" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="J55" s="19"/>
+      <c r="K55" s="23">
+        <f>LEN(F55)</f>
+        <v>2</v>
+      </c>
+      <c r="L55" s="24"/>
+      <c r="M55" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ap</v>
+      </c>
+      <c r="N55" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄚㆴ</v>
+      </c>
+      <c r="P55" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ap(\d)</v>
+      </c>
+      <c r="Q55" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄚㆴ》${1}</v>
+      </c>
+      <c r="R55" s="25"/>
+      <c r="S55" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ap(\d)/ㄚㆴ》${1}/</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A56" s="19">
+        <v>9</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="G56" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="H56" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="I56" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="J56" s="19"/>
+      <c r="K56" s="23">
+        <f>LEN(F56)</f>
+        <v>2</v>
+      </c>
+      <c r="L56" s="24"/>
+      <c r="M56" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>at</v>
+      </c>
+      <c r="N56" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄚㆵ</v>
+      </c>
+      <c r="P56" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>at(\d)</v>
+      </c>
+      <c r="Q56" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄚㆵ》${1}</v>
+      </c>
+      <c r="R56" s="25"/>
+      <c r="S56" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》at(\d)/ㄚㆵ》${1}/</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A57" s="19">
+        <v>18</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="G57" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="H57" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="I57" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="J57" s="19"/>
+      <c r="K57" s="23">
+        <f>LEN(F57)</f>
+        <v>2</v>
+      </c>
+      <c r="L57" s="24"/>
+      <c r="M57" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>eh</v>
+      </c>
+      <c r="N57" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆤㆷ</v>
+      </c>
+      <c r="P57" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>eh(\d)</v>
+      </c>
+      <c r="Q57" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆤㆷ》${1}</v>
+      </c>
+      <c r="R57" s="25"/>
+      <c r="S57" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》eh(\d)/ㆤㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A58" s="19">
+        <v>29</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="G58" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="H58" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="I58" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="J58" s="19"/>
+      <c r="K58" s="23">
+        <f>LEN(F58)</f>
+        <v>2</v>
+      </c>
+      <c r="L58" s="24"/>
+      <c r="M58" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ia</v>
+      </c>
+      <c r="N58" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄚ</v>
+      </c>
+      <c r="P58" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ia(\d)</v>
+      </c>
+      <c r="Q58" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄚ》${1}</v>
+      </c>
+      <c r="R58" s="25"/>
+      <c r="S58" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ia(\d)/ㄧㄚ》${1}/</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A59" s="19">
+        <v>22</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="G59" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="H59" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="J59" s="19"/>
+      <c r="K59" s="23">
+        <f>LEN(F59)</f>
+        <v>2</v>
+      </c>
+      <c r="L59" s="24"/>
+      <c r="M59" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ih</v>
+      </c>
+      <c r="N59" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆷ</v>
+      </c>
+      <c r="P59" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ih(\d)</v>
+      </c>
+      <c r="Q59" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆷ》${1}</v>
+      </c>
+      <c r="R59" s="25"/>
+      <c r="S59" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ih(\d)/ㄧㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A60" s="19">
+        <v>28</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="G60" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="H60" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="I60" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="J60" s="19"/>
+      <c r="K60" s="23">
+        <f>LEN(F60)</f>
+        <v>2</v>
+      </c>
+      <c r="L60" s="24"/>
+      <c r="M60" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ik</v>
+      </c>
+      <c r="N60" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆻ</v>
+      </c>
+      <c r="P60" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ik(\d)</v>
+      </c>
+      <c r="Q60" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆻ》${1}</v>
+      </c>
+      <c r="R60" s="25"/>
+      <c r="S60" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ik(\d)/ㄧㆻ》${1}/</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A61" s="19">
+        <v>23</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="G61" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="H61" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="I61" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="J61" s="19"/>
+      <c r="K61" s="23">
+        <f>LEN(F61)</f>
+        <v>2</v>
+      </c>
+      <c r="L61" s="24"/>
+      <c r="M61" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>im</v>
+      </c>
+      <c r="N61" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆬ</v>
+      </c>
+      <c r="P61" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>im(\d)</v>
+      </c>
+      <c r="Q61" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆬ》${1}</v>
+      </c>
+      <c r="R61" s="25"/>
+      <c r="S61" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》im(\d)/ㄧㆬ》${1}/</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A62" s="19">
+        <v>24</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="G62" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="H62" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J62" s="19"/>
+      <c r="K62" s="23">
+        <f>LEN(F62)</f>
+        <v>2</v>
+      </c>
+      <c r="L62" s="24"/>
+      <c r="M62" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>in</v>
+      </c>
+      <c r="N62" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄣ</v>
+      </c>
+      <c r="P62" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>in(\d)</v>
+      </c>
+      <c r="Q62" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄣ》${1}</v>
+      </c>
+      <c r="R62" s="25"/>
+      <c r="S62" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》in(\d)/ㄧㄣ》${1}/</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A63" s="19">
+        <v>42</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="G63" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="H63" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="I63" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="J63" s="19"/>
+      <c r="K63" s="23">
+        <f>LEN(F63)</f>
+        <v>2</v>
+      </c>
+      <c r="L63" s="24"/>
+      <c r="M63" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>io</v>
+      </c>
+      <c r="N63" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄜ</v>
+      </c>
+      <c r="P63" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>io(\d)</v>
+      </c>
+      <c r="Q63" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄜ》${1}</v>
+      </c>
+      <c r="R63" s="25"/>
+      <c r="S63" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》io(\d)/ㄧㄜ》${1}/</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A64" s="19">
+        <v>26</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="G64" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="H64" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="I64" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="J64" s="19"/>
+      <c r="K64" s="23">
+        <f>LEN(F64)</f>
+        <v>2</v>
+      </c>
+      <c r="L64" s="24"/>
+      <c r="M64" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ip</v>
+      </c>
+      <c r="N64" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>一ㆴ</v>
+      </c>
+      <c r="P64" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ip(\d)</v>
+      </c>
+      <c r="Q64" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>一ㆴ》${1}</v>
+      </c>
+      <c r="R64" s="25"/>
+      <c r="S64" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ip(\d)/一ㆴ》${1}/</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A65" s="19">
+        <v>27</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="G65" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="H65" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="I65" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="J65" s="19"/>
+      <c r="K65" s="23">
+        <f>LEN(F65)</f>
+        <v>2</v>
+      </c>
+      <c r="L65" s="24"/>
+      <c r="M65" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>it</v>
+      </c>
+      <c r="N65" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㆵ</v>
+      </c>
+      <c r="P65" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>it(\d)</v>
+      </c>
+      <c r="Q65" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㆵ》${1}</v>
+      </c>
+      <c r="R65" s="25"/>
+      <c r="S65" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》it(\d)/ㄧㆵ》${1}/</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A66" s="19">
+        <v>47</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="F66" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="G66" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="H66" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="I66" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="J66" s="19"/>
+      <c r="K66" s="23">
+        <f>LEN(F66)</f>
+        <v>2</v>
+      </c>
+      <c r="L66" s="24"/>
+      <c r="M66" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>iu</v>
+      </c>
+      <c r="N66" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㄧㄨ</v>
+      </c>
+      <c r="P66" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>iu(\d)</v>
+      </c>
+      <c r="Q66" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄧㄨ》${1}</v>
+      </c>
+      <c r="R66" s="25"/>
+      <c r="S66" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》iu(\d)/ㄧㄨ》${1}/</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A67" s="19">
+        <v>80</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="D67" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="E67" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="F67" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="H67" s="35" t="s">
+        <v>381</v>
+      </c>
+      <c r="I67" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="J67" s="19"/>
+      <c r="K67" s="23">
+        <f>LEN(F67)</f>
+        <v>2</v>
+      </c>
+      <c r="L67" s="24"/>
+      <c r="M67" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>mh</v>
+      </c>
+      <c r="N67" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ㆬㆷ</v>
+      </c>
+      <c r="P67" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>mh(\d)</v>
+      </c>
+      <c r="Q67" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆬㆷ》${1}</v>
+      </c>
+      <c r="R67" s="25"/>
+      <c r="S67" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》mh(\d)/ㆬㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A68" s="19">
+        <v>81</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="G68" s="22" t="s">
+        <v>384</v>
+      </c>
+      <c r="H68" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="I68" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="J68" s="19"/>
+      <c r="K68" s="23">
+        <f>LEN(F68)</f>
+        <v>2</v>
+      </c>
+      <c r="L68" s="24"/>
+      <c r="M68" s="11" t="str">
+        <f t="shared" ref="M68:M85" si="7">F68</f>
+        <v>ng</v>
+      </c>
+      <c r="N68" s="11" t="str">
+        <f t="shared" ref="N68:N85" si="8">I68</f>
+        <v>ㆭ</v>
+      </c>
+      <c r="P68" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>ng(\d)</v>
+      </c>
+      <c r="Q68" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>ㆭ》${1}</v>
+      </c>
+      <c r="R68" s="25"/>
+      <c r="S68" s="26" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/》ng(\d)/ㆭ》${1}/</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A69" s="19">
+        <v>53</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="G69" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="H69" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="I69" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="J69" s="19"/>
+      <c r="K69" s="23">
+        <f>LEN(F69)</f>
+        <v>2</v>
+      </c>
+      <c r="L69" s="24"/>
+      <c r="M69" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>oh</v>
+      </c>
+      <c r="N69" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄜㆷ</v>
+      </c>
+      <c r="P69" s="3" t="str">
+        <f t="shared" ref="P69:P85" si="9">_xlfn.CONCAT(M69, "(\d)")</f>
+        <v>oh(\d)</v>
+      </c>
+      <c r="Q69" s="3" t="str">
+        <f t="shared" ref="Q69:Q85" si="10">IFERROR( _xlfn.CONCAT(N69, "》", "${1}"), "")</f>
+        <v>ㄜㆷ》${1}</v>
+      </c>
+      <c r="R69" s="25"/>
+      <c r="S69" s="26" t="str">
+        <f t="shared" ref="S69:S85" si="11">IF(AND(N69&lt;&gt;"", M69&lt;&gt;""), "    - xform/》" &amp; P69 &amp;  "/"  &amp; Q69 &amp;  "/", "")</f>
+        <v xml:space="preserve">    - xform/》oh(\d)/ㄜㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A70" s="19">
+        <v>59</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="F70" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="G70" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="H70" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="I70" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="J70" s="19"/>
+      <c r="K70" s="23">
+        <f>LEN(F70)</f>
+        <v>2</v>
+      </c>
+      <c r="L70" s="24"/>
+      <c r="M70" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>ok</v>
+      </c>
+      <c r="N70" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㆦㆻ</v>
+      </c>
+      <c r="P70" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>ok(\d)</v>
+      </c>
+      <c r="Q70" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㆦㆻ》${1}</v>
+      </c>
+      <c r="R70" s="25"/>
+      <c r="S70" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》ok(\d)/ㆦㆻ》${1}/</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A71" s="19">
+        <v>56</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="G71" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="H71" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="I71" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="J71" s="19"/>
+      <c r="K71" s="23">
+        <f>LEN(F71)</f>
+        <v>2</v>
+      </c>
+      <c r="L71" s="24"/>
+      <c r="M71" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>om</v>
+      </c>
+      <c r="N71" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㆱ</v>
+      </c>
+      <c r="P71" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>om(\d)</v>
+      </c>
+      <c r="Q71" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㆱ》${1}</v>
+      </c>
+      <c r="R71" s="25"/>
+      <c r="S71" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》om(\d)/ㆱ》${1}/</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A72" s="19">
+        <v>51</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="G72" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="H72" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="I72" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="J72" s="19"/>
+      <c r="K72" s="23">
+        <f>LEN(F72)</f>
+        <v>2</v>
+      </c>
+      <c r="L72" s="24"/>
+      <c r="M72" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>oo</v>
+      </c>
+      <c r="N72" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㆦ</v>
+      </c>
+      <c r="P72" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>oo(\d)</v>
+      </c>
+      <c r="Q72" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㆦ》${1}</v>
+      </c>
+      <c r="R72" s="25"/>
+      <c r="S72" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》oo(\d)/ㆦ》${1}/</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A73" s="19">
+        <v>58</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="D73" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G73" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="H73" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="I73" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="J73" s="19"/>
+      <c r="K73" s="23">
+        <f>LEN(F73)</f>
+        <v>2</v>
+      </c>
+      <c r="L73" s="24"/>
+      <c r="M73" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>op</v>
+      </c>
+      <c r="N73" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㆦㆴ</v>
+      </c>
+      <c r="P73" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>op(\d)</v>
+      </c>
+      <c r="Q73" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㆦㆴ》${1}</v>
+      </c>
+      <c r="R73" s="25"/>
+      <c r="S73" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》op(\d)/ㆦㆴ》${1}/</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A74" s="19">
+        <v>64</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="G74" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="H74" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="I74" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="J74" s="19"/>
+      <c r="K74" s="23">
+        <f>LEN(F74)</f>
+        <v>2</v>
+      </c>
+      <c r="L74" s="24"/>
+      <c r="M74" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>ua</v>
+      </c>
+      <c r="N74" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄨㄚ</v>
+      </c>
+      <c r="P74" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>ua(\d)</v>
+      </c>
+      <c r="Q74" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄨㄚ》${1}</v>
+      </c>
+      <c r="R74" s="25"/>
+      <c r="S74" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》ua(\d)/ㄨㄚ》${1}/</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A75" s="19">
+        <v>74</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="G75" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="H75" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="I75" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="J75" s="19"/>
+      <c r="K75" s="23">
+        <f>LEN(F75)</f>
+        <v>2</v>
+      </c>
+      <c r="L75" s="24"/>
+      <c r="M75" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>ue</v>
+      </c>
+      <c r="N75" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄨㆤ</v>
+      </c>
+      <c r="P75" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>ue(\d)</v>
+      </c>
+      <c r="Q75" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄨㆤ》${1}</v>
+      </c>
+      <c r="R75" s="25"/>
+      <c r="S75" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》ue(\d)/ㄨㆤ》${1}/</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A76" s="19">
+        <v>61</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="G76" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="H76" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="I76" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="J76" s="19"/>
+      <c r="K76" s="23">
+        <f>LEN(F76)</f>
+        <v>2</v>
+      </c>
+      <c r="L76" s="24"/>
+      <c r="M76" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>uh</v>
+      </c>
+      <c r="N76" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄨㆷ</v>
+      </c>
+      <c r="P76" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>uh(\d)</v>
+      </c>
+      <c r="Q76" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄨㆷ》${1}</v>
+      </c>
+      <c r="R76" s="25"/>
+      <c r="S76" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》uh(\d)/ㄨㆷ》${1}/</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A77" s="19">
+        <v>76</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="G77" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="H77" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="I77" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="J77" s="19"/>
+      <c r="K77" s="23">
+        <f>LEN(F77)</f>
+        <v>2</v>
+      </c>
+      <c r="L77" s="24"/>
+      <c r="M77" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>ui</v>
+      </c>
+      <c r="N77" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄨㄧ</v>
+      </c>
+      <c r="P77" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>ui(\d)</v>
+      </c>
+      <c r="Q77" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄨㄧ》${1}</v>
+      </c>
+      <c r="R77" s="25"/>
+      <c r="S77" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》ui(\d)/ㄨㄧ》${1}/</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A78" s="19">
+        <v>62</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="G78" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="H78" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="I78" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="J78" s="19"/>
+      <c r="K78" s="23">
+        <f>LEN(F78)</f>
+        <v>2</v>
+      </c>
+      <c r="L78" s="24"/>
+      <c r="M78" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>un</v>
+      </c>
+      <c r="N78" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄨㄣ</v>
+      </c>
+      <c r="P78" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>un(\d)</v>
+      </c>
+      <c r="Q78" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄨㄣ》${1}</v>
+      </c>
+      <c r="R78" s="25"/>
+      <c r="S78" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》un(\d)/ㄨㄣ》${1}/</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A79" s="19">
+        <v>63</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="G79" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="H79" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="I79" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="J79" s="19"/>
+      <c r="K79" s="23">
+        <f>LEN(F79)</f>
+        <v>2</v>
+      </c>
+      <c r="L79" s="24"/>
+      <c r="M79" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>ut</v>
+      </c>
+      <c r="N79" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄨㆵ</v>
+      </c>
+      <c r="P79" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>ut(\d)</v>
+      </c>
+      <c r="Q79" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄨㆵ》${1}</v>
+      </c>
+      <c r="R79" s="25"/>
+      <c r="S79" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》ut(\d)/ㄨㆵ》${1}/</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A80" s="19">
+        <v>1</v>
+      </c>
+      <c r="B80" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G80" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H80" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="I80" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="J80" s="19"/>
+      <c r="K80" s="23">
+        <f>LEN(F80)</f>
+        <v>1</v>
+      </c>
+      <c r="L80" s="24"/>
+      <c r="M80" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>a</v>
+      </c>
+      <c r="N80" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄚ</v>
+      </c>
+      <c r="P80" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>a(\d)</v>
+      </c>
+      <c r="Q80" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄚ》${1}</v>
+      </c>
+      <c r="R80" s="25"/>
+      <c r="S80" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》a(\d)/ㄚ》${1}/</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A81" s="19">
+        <v>16</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G81" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H81" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="I81" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="J81" s="19"/>
+      <c r="K81" s="23">
+        <f>LEN(F81)</f>
+        <v>1</v>
+      </c>
+      <c r="L81" s="24"/>
+      <c r="M81" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>e</v>
+      </c>
+      <c r="N81" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㆤ</v>
+      </c>
+      <c r="P81" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>e(\d)</v>
+      </c>
+      <c r="Q81" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㆤ》${1}</v>
+      </c>
+      <c r="R81" s="25"/>
+      <c r="S81" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》e(\d)/ㆤ》${1}/</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A82" s="19">
+        <v>20</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G82" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H82" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="I82" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="J82" s="19"/>
+      <c r="K82" s="23">
+        <f>LEN(F82)</f>
+        <v>1</v>
+      </c>
+      <c r="L82" s="24"/>
+      <c r="M82" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>i</v>
+      </c>
+      <c r="N82" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄧ</v>
+      </c>
+      <c r="P82" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>i(\d)</v>
+      </c>
+      <c r="Q82" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄧ》${1}</v>
+      </c>
+      <c r="R82" s="25"/>
+      <c r="S82" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》i(\d)/ㄧ》${1}/</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A83" s="19">
+        <v>79</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D83" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G83" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="H83" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="I83" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="J83" s="19"/>
+      <c r="K83" s="23">
+        <f>LEN(F83)</f>
+        <v>1</v>
+      </c>
+      <c r="L83" s="24"/>
+      <c r="M83" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>m</v>
+      </c>
+      <c r="N83" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㆬ</v>
+      </c>
+      <c r="P83" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>m(\d)</v>
+      </c>
+      <c r="Q83" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㆬ》${1}</v>
+      </c>
+      <c r="R83" s="25"/>
+      <c r="S83" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》m(\d)/ㆬ》${1}/</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A84" s="19">
+        <v>50</v>
+      </c>
+      <c r="B84" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G84" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H84" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="I84" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="J84" s="19"/>
+      <c r="K84" s="23">
+        <f>LEN(F84)</f>
+        <v>1</v>
+      </c>
+      <c r="L84" s="24"/>
+      <c r="M84" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>o</v>
+      </c>
+      <c r="N84" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄜ</v>
+      </c>
+      <c r="P84" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>o(\d)</v>
+      </c>
+      <c r="Q84" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄜ》${1}</v>
+      </c>
+      <c r="R84" s="25"/>
+      <c r="S84" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》o(\d)/ㄜ》${1}/</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="A85" s="19">
+        <v>60</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D85" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G85" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H85" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="I85" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="J85" s="19"/>
+      <c r="K85" s="23">
+        <f>LEN(F85)</f>
+        <v>1</v>
+      </c>
+      <c r="L85" s="24"/>
+      <c r="M85" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>u</v>
+      </c>
+      <c r="N85" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>ㄨ</v>
+      </c>
+      <c r="P85" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>u(\d)</v>
+      </c>
+      <c r="Q85" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>ㄨ》${1}</v>
+      </c>
+      <c r="R85" s="25"/>
+      <c r="S85" s="26" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/》u(\d)/ㄨ》${1}/</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="27" customHeight="1" thickBot="1"/>
+    <row r="87" spans="1:19" ht="48.75" customHeight="1" thickBot="1">
+      <c r="B87" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="B88" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="C88" s="19">
+        <f>HEX2DEC(VALUE(RIGHT(B88,4)))</f>
+        <v>771</v>
+      </c>
+      <c r="D88" s="19" t="str">
+        <f>_xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(B88,4))))</f>
+        <v>ã</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="27.75" customHeight="1" thickBot="1">
+      <c r="B89" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="C89" s="19">
+        <f>HEX2DEC(VALUE(RIGHT(B89,4)))</f>
+        <v>660</v>
+      </c>
+      <c r="D89" s="19" t="str">
+        <f>_xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(B89,4))))</f>
+        <v>aʔ</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" ht="27" customHeight="1" thickBot="1"/>
+    <row r="91" spans="1:19" ht="27" customHeight="1" thickBot="1">
+      <c r="B91" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="C91" s="11">
+        <f>HEX2DEC(VALUE(RIGHT(B91,4)))</f>
+        <v>2134</v>
+      </c>
+      <c r="D91" s="11" t="str">
+        <f>_xlfn.CONCAT("o", _xlfn.UNICHAR( RIGHT(B91,4)))</f>
+        <v>o͘</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="27" customHeight="1" thickBot="1">
+      <c r="B92" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="C92" s="11">
+        <f>_xlfn.UNICODE( RIGHT(B92,1) )</f>
+        <v>856</v>
+      </c>
+      <c r="D92" s="11" t="str">
+        <f>_xlfn.CONCAT("o", _xlfn.UNICHAR(C92))</f>
+        <v>o͘</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" ht="27" customHeight="1" thickBot="1"/>
+    <row r="94" spans="1:19" ht="27" customHeight="1" thickBot="1">
+      <c r="B94" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" ht="27" customHeight="1" thickBot="1">
+      <c r="B95" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="1" t="str">
+        <f>"(""" &amp; _xlfn.TEXTJOIN(""",""",TRUE,F4:F85) &amp; """)"</f>
+        <v>("nuaih","niah","niao","nioo","niuh","niuh","nuai","nah","nai","neh","nia","niu","na","ne","ni","iang","iaoh","iong","uaih","uang","aih","ang","aoh","iah","iak","iam","ian","iao","iap","iat","ing","ioh","iok","ngh","noo","nua","nui","ong","ooh","uah","uai","uan","uat","ueh","uih","ah","ai","ak","am","an","ao","ap","at","eh","ia","ih","ik","im","in","io","ip","it","iu","mh","ng","oh","ok","om","oo","op","ua","ue","uh","ui","un","ut","a","e","i","m","o","u")</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K85">
+    <sortCondition descending="1" ref="J4:J85"/>
+    <sortCondition descending="1" ref="K4:K85"/>
+    <sortCondition ref="F4:F85"/>
+  </sortState>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AS97"/>
   <sheetFormatPr defaultRowHeight="26.25" outlineLevelCol="1"/>
@@ -16352,7 +21836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AV97"/>
   <sheetFormatPr defaultRowHeight="26.25" outlineLevelCol="1"/>
@@ -22592,7 +28076,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AU97"/>
   <sheetFormatPr defaultRowHeight="26.25" outlineLevelCol="1"/>
@@ -28583,7 +34067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AU97"/>
   <sheetFormatPr defaultRowHeight="26.25" outlineLevelCol="1"/>
